--- a/selenium-tests/reports/selenium-test-report-400.xlsx
+++ b/selenium-tests/reports/selenium-test-report-400.xlsx
@@ -425,7 +425,7 @@
         <v>Passed Cases (Expected matches Actual)</v>
       </c>
       <c r="B3">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         <v>Failed / Unexpected Cases</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>Overall Pass Rate (%)</v>
       </c>
       <c r="B5" t="str">
-        <v>100.00%</v>
+        <v>99.25%</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>Total Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>4.52</v>
+        <v>359.95</v>
       </c>
     </row>
     <row r="7">
@@ -465,7 +465,7 @@
         <v>Executed At</v>
       </c>
       <c r="B8" t="str">
-        <v>31/7/2026, 4:48:33 pm</v>
+        <v>4/8/2026, 12:19:49 am</v>
       </c>
     </row>
   </sheetData>
@@ -523,7 +523,7 @@
         <v>Timestamp</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>TC-001</v>
       </c>
@@ -540,20 +540,19 @@
         <v>success</v>
       </c>
       <c r="F2" t="str">
-        <v>success</v>
+        <v>failure</v>
       </c>
       <c r="G2" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="H2">
-        <v>4513</v>
-      </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
-  (Session info: chrome=150.0.7871.187)</v>
+        <v>1507</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-07-31T11:18:33.058Z</v>
+        <v>2026-08-03T18:43:51.179Z</v>
       </c>
     </row>
     <row r="3">
@@ -573,19 +572,19 @@
         <v>success</v>
       </c>
       <c r="F3" t="str">
-        <v>success</v>
+        <v>failure</v>
       </c>
       <c r="G3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:43:52.012Z</v>
       </c>
     </row>
     <row r="4">
@@ -605,19 +604,19 @@
         <v>success</v>
       </c>
       <c r="F4" t="str">
-        <v>success</v>
+        <v>failure</v>
       </c>
       <c r="G4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:43:52.827Z</v>
       </c>
     </row>
     <row r="5">
@@ -643,13 +642,13 @@
         <v>PASS</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3753</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:43:56.580Z</v>
       </c>
     </row>
     <row r="6">
@@ -675,13 +674,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3594</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:00.175Z</v>
       </c>
     </row>
     <row r="7">
@@ -707,13 +706,13 @@
         <v>PASS</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3553</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:03.728Z</v>
       </c>
     </row>
     <row r="8">
@@ -739,13 +738,13 @@
         <v>PASS</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1210</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:04.938Z</v>
       </c>
     </row>
     <row r="9">
@@ -771,13 +770,13 @@
         <v>PASS</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3704</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:08.642Z</v>
       </c>
     </row>
     <row r="10">
@@ -803,13 +802,13 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3727</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:12.369Z</v>
       </c>
     </row>
     <row r="11">
@@ -835,13 +834,13 @@
         <v>PASS</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1308</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:13.678Z</v>
       </c>
     </row>
     <row r="12">
@@ -867,13 +866,13 @@
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:14.815Z</v>
       </c>
     </row>
     <row r="13">
@@ -899,13 +898,13 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1607</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:16.422Z</v>
       </c>
     </row>
     <row r="14">
@@ -931,13 +930,13 @@
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:17.409Z</v>
       </c>
     </row>
     <row r="15">
@@ -948,7 +947,7 @@
         <v>Fuzzing with database query snippets (5)</v>
       </c>
       <c r="C15" t="str">
-        <v>sql_fuzz_5_kv3e@test.com</v>
+        <v>sql_fuzz_5_b60v@test.com</v>
       </c>
       <c r="D15" t="str">
         <v>'; DROP TABLE u...</v>
@@ -963,13 +962,13 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1074</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:18.483Z</v>
       </c>
     </row>
     <row r="16">
@@ -995,13 +994,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>995</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:19.478Z</v>
       </c>
     </row>
     <row r="17">
@@ -1027,13 +1026,13 @@
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:20.289Z</v>
       </c>
     </row>
     <row r="18">
@@ -1059,13 +1058,13 @@
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:21.163Z</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1090,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:22.113Z</v>
       </c>
     </row>
     <row r="20">
@@ -1123,13 +1122,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:22.835Z</v>
       </c>
     </row>
     <row r="21">
@@ -1140,7 +1139,7 @@
         <v>Fuzzing with database query snippets (11)</v>
       </c>
       <c r="C21" t="str">
-        <v>sql_fuzz_11_9wzx@test.com</v>
+        <v>sql_fuzz_11_3ne4@test.com</v>
       </c>
       <c r="D21" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1155,13 +1154,13 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:23.860Z</v>
       </c>
     </row>
     <row r="22">
@@ -1187,13 +1186,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Email address does not exist.</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:24.790Z</v>
       </c>
     </row>
     <row r="23">
@@ -1219,13 +1218,13 @@
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>665</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:25.455Z</v>
       </c>
     </row>
     <row r="24">
@@ -1251,13 +1250,13 @@
         <v>PASS</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:26.171Z</v>
       </c>
     </row>
     <row r="25">
@@ -1283,13 +1282,13 @@
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:27.153Z</v>
       </c>
     </row>
     <row r="26">
@@ -1315,13 +1314,13 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:27.928Z</v>
       </c>
     </row>
     <row r="27">
@@ -1332,7 +1331,7 @@
         <v>Fuzzing with database query snippets (17)</v>
       </c>
       <c r="C27" t="str">
-        <v>sql_fuzz_17_6efg@test.com</v>
+        <v>sql_fuzz_17_inl7@test.com</v>
       </c>
       <c r="D27" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1347,13 +1346,13 @@
         <v>PASS</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:29.014Z</v>
       </c>
     </row>
     <row r="28">
@@ -1379,13 +1378,13 @@
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:29.861Z</v>
       </c>
     </row>
     <row r="29">
@@ -1411,13 +1410,13 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:30.521Z</v>
       </c>
     </row>
     <row r="30">
@@ -1443,13 +1442,13 @@
         <v>PASS</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>959</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:31.480Z</v>
       </c>
     </row>
     <row r="31">
@@ -1475,13 +1474,13 @@
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:32.440Z</v>
       </c>
     </row>
     <row r="32">
@@ -1507,13 +1506,13 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:33.317Z</v>
       </c>
     </row>
     <row r="33">
@@ -1524,7 +1523,7 @@
         <v>Fuzzing with database query snippets (23)</v>
       </c>
       <c r="C33" t="str">
-        <v>sql_fuzz_23_3kxg@test.com</v>
+        <v>sql_fuzz_23_1ggr@test.com</v>
       </c>
       <c r="D33" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1539,13 +1538,13 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>789</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:34.106Z</v>
       </c>
     </row>
     <row r="34">
@@ -1571,13 +1570,13 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:34.995Z</v>
       </c>
     </row>
     <row r="35">
@@ -1603,13 +1602,13 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:35.584Z</v>
       </c>
     </row>
     <row r="36">
@@ -1635,13 +1634,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:36.282Z</v>
       </c>
     </row>
     <row r="37">
@@ -1667,13 +1666,13 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:37.069Z</v>
       </c>
     </row>
     <row r="38">
@@ -1699,13 +1698,13 @@
         <v>PASS</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>662</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:37.731Z</v>
       </c>
     </row>
     <row r="39">
@@ -1716,7 +1715,7 @@
         <v>Fuzzing with database query snippets (29)</v>
       </c>
       <c r="C39" t="str">
-        <v>sql_fuzz_29_km18@test.com</v>
+        <v>sql_fuzz_29_ci2k@test.com</v>
       </c>
       <c r="D39" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1731,13 +1730,13 @@
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:38.706Z</v>
       </c>
     </row>
     <row r="40">
@@ -1763,13 +1762,13 @@
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>917</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:39.623Z</v>
       </c>
     </row>
     <row r="41">
@@ -1795,13 +1794,13 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:40.477Z</v>
       </c>
     </row>
     <row r="42">
@@ -1827,13 +1826,13 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:41.405Z</v>
       </c>
     </row>
     <row r="43">
@@ -1859,13 +1858,13 @@
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:42.387Z</v>
       </c>
     </row>
     <row r="44">
@@ -1891,13 +1890,13 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:43.288Z</v>
       </c>
     </row>
     <row r="45">
@@ -1908,7 +1907,7 @@
         <v>Fuzzing with database query snippets (35)</v>
       </c>
       <c r="C45" t="str">
-        <v>sql_fuzz_35_rymi@test.com</v>
+        <v>sql_fuzz_35_u65j@test.com</v>
       </c>
       <c r="D45" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1923,13 +1922,13 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:44.256Z</v>
       </c>
     </row>
     <row r="46">
@@ -1955,13 +1954,13 @@
         <v>PASS</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:44.915Z</v>
       </c>
     </row>
     <row r="47">
@@ -1987,13 +1986,13 @@
         <v>PASS</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:45.768Z</v>
       </c>
     </row>
     <row r="48">
@@ -2019,13 +2018,13 @@
         <v>PASS</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:46.691Z</v>
       </c>
     </row>
     <row r="49">
@@ -2051,13 +2050,13 @@
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:47.722Z</v>
       </c>
     </row>
     <row r="50">
@@ -2083,13 +2082,13 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:48.345Z</v>
       </c>
     </row>
     <row r="51">
@@ -2100,7 +2099,7 @@
         <v>Fuzzing with database query snippets (41)</v>
       </c>
       <c r="C51" t="str">
-        <v>sql_fuzz_41_5mbu@test.com</v>
+        <v>sql_fuzz_41_j6zl@test.com</v>
       </c>
       <c r="D51" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2115,13 +2114,13 @@
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:49.104Z</v>
       </c>
     </row>
     <row r="52">
@@ -2147,13 +2146,13 @@
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:49.986Z</v>
       </c>
     </row>
     <row r="53">
@@ -2179,13 +2178,13 @@
         <v>PASS</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:50.824Z</v>
       </c>
     </row>
     <row r="54">
@@ -2211,13 +2210,13 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:51.735Z</v>
       </c>
     </row>
     <row r="55">
@@ -2243,13 +2242,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:52.800Z</v>
       </c>
     </row>
     <row r="56">
@@ -2275,13 +2274,13 @@
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:53.750Z</v>
       </c>
     </row>
     <row r="57">
@@ -2292,7 +2291,7 @@
         <v>Fuzzing with database query snippets (47)</v>
       </c>
       <c r="C57" t="str">
-        <v>sql_fuzz_47_a3x5@test.com</v>
+        <v>sql_fuzz_47_th2t@test.com</v>
       </c>
       <c r="D57" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2307,13 +2306,13 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:54.555Z</v>
       </c>
     </row>
     <row r="58">
@@ -2339,13 +2338,13 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:55.283Z</v>
       </c>
     </row>
     <row r="59">
@@ -2371,13 +2370,13 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:56.027Z</v>
       </c>
     </row>
     <row r="60">
@@ -2403,13 +2402,13 @@
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:56.708Z</v>
       </c>
     </row>
     <row r="61">
@@ -2435,13 +2434,13 @@
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:57.482Z</v>
       </c>
     </row>
     <row r="62">
@@ -2467,13 +2466,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:58.138Z</v>
       </c>
     </row>
     <row r="63">
@@ -2484,7 +2483,7 @@
         <v>Fuzzing with database query snippets (53)</v>
       </c>
       <c r="C63" t="str">
-        <v>sql_fuzz_53_aacs@test.com</v>
+        <v>sql_fuzz_53_efas@test.com</v>
       </c>
       <c r="D63" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2499,13 +2498,13 @@
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1253</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:44:59.391Z</v>
       </c>
     </row>
     <row r="64">
@@ -2531,13 +2530,13 @@
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:00.317Z</v>
       </c>
     </row>
     <row r="65">
@@ -2563,13 +2562,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>923</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:01.240Z</v>
       </c>
     </row>
     <row r="66">
@@ -2595,13 +2594,13 @@
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:01.850Z</v>
       </c>
     </row>
     <row r="67">
@@ -2627,13 +2626,13 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:02.935Z</v>
       </c>
     </row>
     <row r="68">
@@ -2659,13 +2658,13 @@
         <v>PASS</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:03.565Z</v>
       </c>
     </row>
     <row r="69">
@@ -2676,7 +2675,7 @@
         <v>Fuzzing with database query snippets (59)</v>
       </c>
       <c r="C69" t="str">
-        <v>sql_fuzz_59_365i@test.com</v>
+        <v>sql_fuzz_59_bmy5@test.com</v>
       </c>
       <c r="D69" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2691,13 +2690,13 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>986</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:04.551Z</v>
       </c>
     </row>
     <row r="70">
@@ -2723,13 +2722,13 @@
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:05.207Z</v>
       </c>
     </row>
     <row r="71">
@@ -2755,13 +2754,13 @@
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:06.089Z</v>
       </c>
     </row>
     <row r="72">
@@ -2787,13 +2786,13 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>904</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:06.993Z</v>
       </c>
     </row>
     <row r="73">
@@ -2819,13 +2818,13 @@
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:07.904Z</v>
       </c>
     </row>
     <row r="74">
@@ -2851,13 +2850,13 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:08.960Z</v>
       </c>
     </row>
     <row r="75">
@@ -2868,7 +2867,7 @@
         <v>Fuzzing with database query snippets (65)</v>
       </c>
       <c r="C75" t="str">
-        <v>sql_fuzz_65_n7ab@test.com</v>
+        <v>sql_fuzz_65_bk5m@test.com</v>
       </c>
       <c r="D75" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2883,13 +2882,13 @@
         <v>PASS</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:09.881Z</v>
       </c>
     </row>
     <row r="76">
@@ -2915,13 +2914,13 @@
         <v>PASS</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:10.891Z</v>
       </c>
     </row>
     <row r="77">
@@ -2947,13 +2946,13 @@
         <v>PASS</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-03T18:45:11.504Z</v>
       </c>
     </row>
     <row r="78">
@@ -2979,13 +2978,13 @@
         <v>PASS</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:12.170Z</v>
       </c>
     </row>
     <row r="79">
@@ -3011,13 +3010,13 @@
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:13.223Z</v>
       </c>
     </row>
     <row r="80">
@@ -3043,13 +3042,13 @@
         <v>PASS</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:14.141Z</v>
       </c>
     </row>
     <row r="81">
@@ -3060,7 +3059,7 @@
         <v>Fuzzing with database query snippets (71)</v>
       </c>
       <c r="C81" t="str">
-        <v>sql_fuzz_71_sbl0@test.com</v>
+        <v>sql_fuzz_71_ostr@test.com</v>
       </c>
       <c r="D81" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3075,13 +3074,13 @@
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1115</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:15.256Z</v>
       </c>
     </row>
     <row r="82">
@@ -3107,13 +3106,13 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:16.372Z</v>
       </c>
     </row>
     <row r="83">
@@ -3139,13 +3138,13 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:17.288Z</v>
       </c>
     </row>
     <row r="84">
@@ -3171,13 +3170,13 @@
         <v>PASS</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:18.118Z</v>
       </c>
     </row>
     <row r="85">
@@ -3203,13 +3202,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1138</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:19.256Z</v>
       </c>
     </row>
     <row r="86">
@@ -3235,13 +3234,13 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>923</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:20.179Z</v>
       </c>
     </row>
     <row r="87">
@@ -3252,7 +3251,7 @@
         <v>Fuzzing with database query snippets (77)</v>
       </c>
       <c r="C87" t="str">
-        <v>sql_fuzz_77_icbn@test.com</v>
+        <v>sql_fuzz_77_zxfx@test.com</v>
       </c>
       <c r="D87" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3267,13 +3266,13 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:21.068Z</v>
       </c>
     </row>
     <row r="88">
@@ -3299,13 +3298,13 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:22.019Z</v>
       </c>
     </row>
     <row r="89">
@@ -3331,13 +3330,13 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:22.911Z</v>
       </c>
     </row>
     <row r="90">
@@ -3363,13 +3362,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:23.762Z</v>
       </c>
     </row>
     <row r="91">
@@ -3395,13 +3394,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1063</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:24.825Z</v>
       </c>
     </row>
     <row r="92">
@@ -3427,13 +3426,13 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:25.483Z</v>
       </c>
     </row>
     <row r="93">
@@ -3444,7 +3443,7 @@
         <v>Fuzzing with database query snippets (83)</v>
       </c>
       <c r="C93" t="str">
-        <v>sql_fuzz_83_uzps@test.com</v>
+        <v>sql_fuzz_83_p7oy@test.com</v>
       </c>
       <c r="D93" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3459,13 +3458,13 @@
         <v>PASS</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:26.578Z</v>
       </c>
     </row>
     <row r="94">
@@ -3491,13 +3490,13 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:27.234Z</v>
       </c>
     </row>
     <row r="95">
@@ -3523,13 +3522,13 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:28.092Z</v>
       </c>
     </row>
     <row r="96">
@@ -3555,13 +3554,13 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>633</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:28.725Z</v>
       </c>
     </row>
     <row r="97">
@@ -3587,13 +3586,13 @@
         <v>PASS</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:29.879Z</v>
       </c>
     </row>
     <row r="98">
@@ -3619,13 +3618,13 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:30.817Z</v>
       </c>
     </row>
     <row r="99">
@@ -3636,7 +3635,7 @@
         <v>Fuzzing with database query snippets (89)</v>
       </c>
       <c r="C99" t="str">
-        <v>sql_fuzz_89_83ks@test.com</v>
+        <v>sql_fuzz_89_6iv0@test.com</v>
       </c>
       <c r="D99" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3651,13 +3650,13 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:31.918Z</v>
       </c>
     </row>
     <row r="100">
@@ -3683,13 +3682,13 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:32.936Z</v>
       </c>
     </row>
     <row r="101">
@@ -3715,13 +3714,13 @@
         <v>PASS</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:33.889Z</v>
       </c>
     </row>
     <row r="102">
@@ -3747,13 +3746,13 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:34.923Z</v>
       </c>
     </row>
     <row r="103">
@@ -3779,13 +3778,13 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:36.023Z</v>
       </c>
     </row>
     <row r="104">
@@ -3811,13 +3810,13 @@
         <v>PASS</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>1258</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:37.281Z</v>
       </c>
     </row>
     <row r="105">
@@ -3828,7 +3827,7 @@
         <v>Fuzzing with database query snippets (95)</v>
       </c>
       <c r="C105" t="str">
-        <v>sql_fuzz_95_abih@test.com</v>
+        <v>sql_fuzz_95_hc7b@test.com</v>
       </c>
       <c r="D105" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3843,13 +3842,13 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>1325</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:38.606Z</v>
       </c>
     </row>
     <row r="106">
@@ -3875,13 +3874,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:39.524Z</v>
       </c>
     </row>
     <row r="107">
@@ -3907,13 +3906,13 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="I107" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:40.407Z</v>
       </c>
     </row>
     <row r="108">
@@ -3939,13 +3938,13 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:41.343Z</v>
       </c>
     </row>
     <row r="109">
@@ -3971,13 +3970,13 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>1121</v>
       </c>
       <c r="I109" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:42.464Z</v>
       </c>
     </row>
     <row r="110">
@@ -4003,13 +4002,13 @@
         <v>PASS</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:43.312Z</v>
       </c>
     </row>
     <row r="111">
@@ -4020,7 +4019,7 @@
         <v>Fuzzing with database query snippets (101)</v>
       </c>
       <c r="C111" t="str">
-        <v>sql_fuzz_101_4nap@test.com</v>
+        <v>sql_fuzz_101_mxzs@test.com</v>
       </c>
       <c r="D111" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4035,13 +4034,13 @@
         <v>PASS</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:44.506Z</v>
       </c>
     </row>
     <row r="112">
@@ -4067,13 +4066,13 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>1123</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:45.629Z</v>
       </c>
     </row>
     <row r="113">
@@ -4099,13 +4098,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:46.670Z</v>
       </c>
     </row>
     <row r="114">
@@ -4131,13 +4130,13 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:47.636Z</v>
       </c>
     </row>
     <row r="115">
@@ -4163,13 +4162,13 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:48.547Z</v>
       </c>
     </row>
     <row r="116">
@@ -4195,13 +4194,13 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:49.338Z</v>
       </c>
     </row>
     <row r="117">
@@ -4212,7 +4211,7 @@
         <v>Fuzzing with database query snippets (107)</v>
       </c>
       <c r="C117" t="str">
-        <v>sql_fuzz_107_fzjw@test.com</v>
+        <v>sql_fuzz_107_k9s9@test.com</v>
       </c>
       <c r="D117" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4227,13 +4226,13 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:50.237Z</v>
       </c>
     </row>
     <row r="118">
@@ -4259,13 +4258,13 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:51.053Z</v>
       </c>
     </row>
     <row r="119">
@@ -4291,13 +4290,13 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:51.863Z</v>
       </c>
     </row>
     <row r="120">
@@ -4323,13 +4322,13 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:52.559Z</v>
       </c>
     </row>
     <row r="121">
@@ -4355,13 +4354,13 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:53.451Z</v>
       </c>
     </row>
     <row r="122">
@@ -4387,13 +4386,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="I122" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:54.009Z</v>
       </c>
     </row>
     <row r="123">
@@ -4404,7 +4403,7 @@
         <v>Fuzzing with database query snippets (113)</v>
       </c>
       <c r="C123" t="str">
-        <v>sql_fuzz_113_9jcp@test.com</v>
+        <v>sql_fuzz_113_2uxz@test.com</v>
       </c>
       <c r="D123" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4419,13 +4418,13 @@
         <v>PASS</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="I123" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:54.847Z</v>
       </c>
     </row>
     <row r="124">
@@ -4451,13 +4450,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="I124" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:55.617Z</v>
       </c>
     </row>
     <row r="125">
@@ -4483,13 +4482,13 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:56.585Z</v>
       </c>
     </row>
     <row r="126">
@@ -4515,13 +4514,13 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:57.317Z</v>
       </c>
     </row>
     <row r="127">
@@ -4547,13 +4546,13 @@
         <v>PASS</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="I127" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:57.965Z</v>
       </c>
     </row>
     <row r="128">
@@ -4579,13 +4578,13 @@
         <v>PASS</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:58.518Z</v>
       </c>
     </row>
     <row r="129">
@@ -4596,7 +4595,7 @@
         <v>Fuzzing with database query snippets (119)</v>
       </c>
       <c r="C129" t="str">
-        <v>sql_fuzz_119_3ij4@test.com</v>
+        <v>sql_fuzz_119_za9t@test.com</v>
       </c>
       <c r="D129" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4611,13 +4610,13 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="I129" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:59.152Z</v>
       </c>
     </row>
     <row r="130">
@@ -4643,13 +4642,13 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="I130" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:45:59.742Z</v>
       </c>
     </row>
     <row r="131">
@@ -4675,13 +4674,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:00.532Z</v>
       </c>
     </row>
     <row r="132">
@@ -4707,13 +4706,13 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="I132" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:01.272Z</v>
       </c>
     </row>
     <row r="133">
@@ -4739,13 +4738,13 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="I133" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:02.099Z</v>
       </c>
     </row>
     <row r="134">
@@ -4771,13 +4770,13 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="I134" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:02.685Z</v>
       </c>
     </row>
     <row r="135">
@@ -4788,7 +4787,7 @@
         <v>Fuzzing with database query snippets (125)</v>
       </c>
       <c r="C135" t="str">
-        <v>sql_fuzz_125_pf1r@test.com</v>
+        <v>sql_fuzz_125_7xvo@test.com</v>
       </c>
       <c r="D135" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4803,13 +4802,13 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="I135" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:03.381Z</v>
       </c>
     </row>
     <row r="136">
@@ -4835,13 +4834,13 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="I136" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:04.167Z</v>
       </c>
     </row>
     <row r="137">
@@ -4867,13 +4866,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:04.917Z</v>
       </c>
     </row>
     <row r="138">
@@ -4899,13 +4898,13 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:05.408Z</v>
       </c>
     </row>
     <row r="139">
@@ -4931,13 +4930,13 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>878</v>
       </c>
       <c r="I139" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:06.286Z</v>
       </c>
     </row>
     <row r="140">
@@ -4963,13 +4962,13 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="I140" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:06.838Z</v>
       </c>
     </row>
     <row r="141">
@@ -4980,7 +4979,7 @@
         <v>Fuzzing with database query snippets (131)</v>
       </c>
       <c r="C141" t="str">
-        <v>sql_fuzz_131_zhqd@test.com</v>
+        <v>sql_fuzz_131_6w1f@test.com</v>
       </c>
       <c r="D141" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4995,13 +4994,13 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:07.772Z</v>
       </c>
     </row>
     <row r="142">
@@ -5027,13 +5026,13 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>832</v>
       </c>
       <c r="I142" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:08.605Z</v>
       </c>
     </row>
     <row r="143">
@@ -5059,13 +5058,13 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="I143" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:09.173Z</v>
       </c>
     </row>
     <row r="144">
@@ -5091,13 +5090,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:10.120Z</v>
       </c>
     </row>
     <row r="145">
@@ -5123,13 +5122,13 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="I145" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:10.779Z</v>
       </c>
     </row>
     <row r="146">
@@ -5155,13 +5154,13 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="I146" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:11.298Z</v>
       </c>
     </row>
     <row r="147">
@@ -5172,7 +5171,7 @@
         <v>Fuzzing with database query snippets (137)</v>
       </c>
       <c r="C147" t="str">
-        <v>sql_fuzz_137_vv5t@test.com</v>
+        <v>sql_fuzz_137_zbwe@test.com</v>
       </c>
       <c r="D147" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5187,13 +5186,13 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I147" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:11.948Z</v>
       </c>
     </row>
     <row r="148">
@@ -5219,13 +5218,13 @@
         <v>PASS</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:12.803Z</v>
       </c>
     </row>
     <row r="149">
@@ -5251,13 +5250,13 @@
         <v>PASS</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="I149" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:13.519Z</v>
       </c>
     </row>
     <row r="150">
@@ -5283,13 +5282,13 @@
         <v>PASS</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="I150" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:14.059Z</v>
       </c>
     </row>
     <row r="151">
@@ -5315,13 +5314,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>878</v>
       </c>
       <c r="I151" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:14.937Z</v>
       </c>
     </row>
     <row r="152">
@@ -5347,13 +5346,13 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>868</v>
       </c>
       <c r="I152" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:15.805Z</v>
       </c>
     </row>
     <row r="153">
@@ -5364,7 +5363,7 @@
         <v>Fuzzing with database query snippets (143)</v>
       </c>
       <c r="C153" t="str">
-        <v>sql_fuzz_143_rwrk@test.com</v>
+        <v>sql_fuzz_143_hdst@test.com</v>
       </c>
       <c r="D153" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5379,13 +5378,13 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="I153" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:16.516Z</v>
       </c>
     </row>
     <row r="154">
@@ -5411,13 +5410,13 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="I154" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:17.295Z</v>
       </c>
     </row>
     <row r="155">
@@ -5443,13 +5442,13 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="I155" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:18.035Z</v>
       </c>
     </row>
     <row r="156">
@@ -5475,13 +5474,13 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:18.538Z</v>
       </c>
     </row>
     <row r="157">
@@ -5507,13 +5506,13 @@
         <v>PASS</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="I157" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:19.448Z</v>
       </c>
     </row>
     <row r="158">
@@ -5539,13 +5538,13 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="I158" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:20.235Z</v>
       </c>
     </row>
     <row r="159">
@@ -5556,7 +5555,7 @@
         <v>Fuzzing with database query snippets (149)</v>
       </c>
       <c r="C159" t="str">
-        <v>sql_fuzz_149_zhba@test.com</v>
+        <v>sql_fuzz_149_kbpk@test.com</v>
       </c>
       <c r="D159" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5571,13 +5570,13 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="I159" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:21.166Z</v>
       </c>
     </row>
     <row r="160">
@@ -5603,13 +5602,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I160" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:21.866Z</v>
       </c>
     </row>
     <row r="161">
@@ -5635,13 +5634,13 @@
         <v>PASS</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="I161" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:22.644Z</v>
       </c>
     </row>
     <row r="162">
@@ -5667,13 +5666,13 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="I162" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:23.151Z</v>
       </c>
     </row>
     <row r="163">
@@ -5699,13 +5698,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="I163" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:23.750Z</v>
       </c>
     </row>
     <row r="164">
@@ -5731,13 +5730,13 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>869</v>
       </c>
       <c r="I164" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:24.619Z</v>
       </c>
     </row>
     <row r="165">
@@ -5748,7 +5747,7 @@
         <v>Fuzzing with database query snippets (155)</v>
       </c>
       <c r="C165" t="str">
-        <v>sql_fuzz_155_pqsg@test.com</v>
+        <v>sql_fuzz_155_qrv4@test.com</v>
       </c>
       <c r="D165" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5763,13 +5762,13 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="I165" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:25.502Z</v>
       </c>
     </row>
     <row r="166">
@@ -5795,13 +5794,13 @@
         <v>PASS</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="I166" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:26.331Z</v>
       </c>
     </row>
     <row r="167">
@@ -5827,13 +5826,13 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:27.154Z</v>
       </c>
     </row>
     <row r="168">
@@ -5859,13 +5858,13 @@
         <v>PASS</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="I168" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:27.821Z</v>
       </c>
     </row>
     <row r="169">
@@ -5891,13 +5890,13 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="I169" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:28.502Z</v>
       </c>
     </row>
     <row r="170">
@@ -5923,13 +5922,13 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="I170" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:29.082Z</v>
       </c>
     </row>
     <row r="171">
@@ -5940,7 +5939,7 @@
         <v>Fuzzing with database query snippets (161)</v>
       </c>
       <c r="C171" t="str">
-        <v>sql_fuzz_161_u98w@test.com</v>
+        <v>sql_fuzz_161_grfr@test.com</v>
       </c>
       <c r="D171" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5955,13 +5954,13 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="I171" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:29.966Z</v>
       </c>
     </row>
     <row r="172">
@@ -5987,13 +5986,13 @@
         <v>PASS</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="I172" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:30.764Z</v>
       </c>
     </row>
     <row r="173">
@@ -6019,13 +6018,13 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="I173" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:31.546Z</v>
       </c>
     </row>
     <row r="174">
@@ -6051,13 +6050,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="I174" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:32.518Z</v>
       </c>
     </row>
     <row r="175">
@@ -6083,13 +6082,13 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="I175" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:33.603Z</v>
       </c>
     </row>
     <row r="176">
@@ -6115,13 +6114,13 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="I176" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:34.434Z</v>
       </c>
     </row>
     <row r="177">
@@ -6132,7 +6131,7 @@
         <v>Fuzzing with database query snippets (167)</v>
       </c>
       <c r="C177" t="str">
-        <v>sql_fuzz_167_3uv9@test.com</v>
+        <v>sql_fuzz_167_qb3e@test.com</v>
       </c>
       <c r="D177" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6147,13 +6146,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="I177" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:35.335Z</v>
       </c>
     </row>
     <row r="178">
@@ -6179,13 +6178,13 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="I178" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:36.317Z</v>
       </c>
     </row>
     <row r="179">
@@ -6211,13 +6210,13 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="I179" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:37.300Z</v>
       </c>
     </row>
     <row r="180">
@@ -6243,13 +6242,13 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="I180" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:38.262Z</v>
       </c>
     </row>
     <row r="181">
@@ -6275,13 +6274,13 @@
         <v>PASS</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I181" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:39.150Z</v>
       </c>
     </row>
     <row r="182">
@@ -6307,13 +6306,13 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="I182" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:39.965Z</v>
       </c>
     </row>
     <row r="183">
@@ -6324,7 +6323,7 @@
         <v>Fuzzing with database query snippets (173)</v>
       </c>
       <c r="C183" t="str">
-        <v>sql_fuzz_173_ernu@test.com</v>
+        <v>sql_fuzz_173_041q@test.com</v>
       </c>
       <c r="D183" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6339,13 +6338,13 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="I183" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:41.003Z</v>
       </c>
     </row>
     <row r="184">
@@ -6371,13 +6370,13 @@
         <v>PASS</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="I184" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:41.956Z</v>
       </c>
     </row>
     <row r="185">
@@ -6403,13 +6402,13 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="I185" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:42.870Z</v>
       </c>
     </row>
     <row r="186">
@@ -6435,13 +6434,13 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="I186" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:43.797Z</v>
       </c>
     </row>
     <row r="187">
@@ -6467,13 +6466,13 @@
         <v>PASS</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>1139</v>
       </c>
       <c r="I187" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:44.936Z</v>
       </c>
     </row>
     <row r="188">
@@ -6499,13 +6498,13 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="I188" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:45.896Z</v>
       </c>
     </row>
     <row r="189">
@@ -6516,7 +6515,7 @@
         <v>Fuzzing with database query snippets (179)</v>
       </c>
       <c r="C189" t="str">
-        <v>sql_fuzz_179_zo4e@test.com</v>
+        <v>sql_fuzz_179_epw0@test.com</v>
       </c>
       <c r="D189" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6531,13 +6530,13 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="I189" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:46.760Z</v>
       </c>
     </row>
     <row r="190">
@@ -6563,13 +6562,13 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="I190" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:47.445Z</v>
       </c>
     </row>
     <row r="191">
@@ -6595,13 +6594,13 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="I191" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:48.094Z</v>
       </c>
     </row>
     <row r="192">
@@ -6627,13 +6626,13 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="I192" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:48.787Z</v>
       </c>
     </row>
     <row r="193">
@@ -6659,13 +6658,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="I193" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:49.663Z</v>
       </c>
     </row>
     <row r="194">
@@ -6691,13 +6690,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="I194" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:50.371Z</v>
       </c>
     </row>
     <row r="195">
@@ -6708,7 +6707,7 @@
         <v>Fuzzing with database query snippets (185)</v>
       </c>
       <c r="C195" t="str">
-        <v>sql_fuzz_185_uipk@test.com</v>
+        <v>sql_fuzz_185_p8kg@test.com</v>
       </c>
       <c r="D195" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6723,13 +6722,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="I195" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:51.351Z</v>
       </c>
     </row>
     <row r="196">
@@ -6755,13 +6754,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="I196" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:52.313Z</v>
       </c>
     </row>
     <row r="197">
@@ -6787,13 +6786,13 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="I197" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:53.326Z</v>
       </c>
     </row>
     <row r="198">
@@ -6819,13 +6818,13 @@
         <v>PASS</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="I198" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:54.511Z</v>
       </c>
     </row>
     <row r="199">
@@ -6851,13 +6850,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>1479</v>
       </c>
       <c r="I199" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:55.990Z</v>
       </c>
     </row>
     <row r="200">
@@ -6883,13 +6882,13 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="I200" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:56.927Z</v>
       </c>
     </row>
     <row r="201">
@@ -6900,7 +6899,7 @@
         <v>Fuzzing with database query snippets (191)</v>
       </c>
       <c r="C201" t="str">
-        <v>sql_fuzz_191_ptwd@test.com</v>
+        <v>sql_fuzz_191_hlgk@test.com</v>
       </c>
       <c r="D201" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6915,13 +6914,13 @@
         <v>PASS</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="I201" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:58.081Z</v>
       </c>
     </row>
     <row r="202">
@@ -6947,13 +6946,13 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="I202" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:59.089Z</v>
       </c>
     </row>
     <row r="203">
@@ -6979,13 +6978,13 @@
         <v>PASS</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>873</v>
       </c>
       <c r="I203" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:46:59.962Z</v>
       </c>
     </row>
     <row r="204">
@@ -7011,13 +7010,13 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>1081</v>
       </c>
       <c r="I204" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:01.043Z</v>
       </c>
     </row>
     <row r="205">
@@ -7043,13 +7042,13 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="I205" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:02.017Z</v>
       </c>
     </row>
     <row r="206">
@@ -7075,13 +7074,13 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="I206" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:02.964Z</v>
       </c>
     </row>
     <row r="207">
@@ -7092,7 +7091,7 @@
         <v>Fuzzing with database query snippets (197)</v>
       </c>
       <c r="C207" t="str">
-        <v>sql_fuzz_197_3ky6@test.com</v>
+        <v>sql_fuzz_197_ixa1@test.com</v>
       </c>
       <c r="D207" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7107,13 +7106,13 @@
         <v>PASS</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="I207" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:04.127Z</v>
       </c>
     </row>
     <row r="208">
@@ -7139,13 +7138,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="I208" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:05.127Z</v>
       </c>
     </row>
     <row r="209">
@@ -7171,13 +7170,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="I209" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:06.032Z</v>
       </c>
     </row>
     <row r="210">
@@ -7203,13 +7202,13 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="I210" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:06.656Z</v>
       </c>
     </row>
     <row r="211">
@@ -7235,13 +7234,13 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="I211" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:07.520Z</v>
       </c>
     </row>
     <row r="212">
@@ -7267,13 +7266,13 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="I212" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:08.302Z</v>
       </c>
     </row>
     <row r="213">
@@ -7284,7 +7283,7 @@
         <v>Fuzzing with database query snippets (203)</v>
       </c>
       <c r="C213" t="str">
-        <v>sql_fuzz_203_spw6@test.com</v>
+        <v>sql_fuzz_203_xe1x@test.com</v>
       </c>
       <c r="D213" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7299,13 +7298,13 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="I213" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:09.110Z</v>
       </c>
     </row>
     <row r="214">
@@ -7331,13 +7330,13 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="I214" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:10.036Z</v>
       </c>
     </row>
     <row r="215">
@@ -7363,13 +7362,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="I215" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:10.847Z</v>
       </c>
     </row>
     <row r="216">
@@ -7395,13 +7394,13 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="I216" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:11.655Z</v>
       </c>
     </row>
     <row r="217">
@@ -7427,13 +7426,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="I217" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:12.329Z</v>
       </c>
     </row>
     <row r="218">
@@ -7459,13 +7458,13 @@
         <v>PASS</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="I218" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:12.899Z</v>
       </c>
     </row>
     <row r="219">
@@ -7476,7 +7475,7 @@
         <v>Fuzzing with database query snippets (209)</v>
       </c>
       <c r="C219" t="str">
-        <v>sql_fuzz_209_z0mx@test.com</v>
+        <v>sql_fuzz_209_nv4m@test.com</v>
       </c>
       <c r="D219" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7491,13 +7490,13 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="I219" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:13.806Z</v>
       </c>
     </row>
     <row r="220">
@@ -7523,13 +7522,13 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="I220" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:14.591Z</v>
       </c>
     </row>
     <row r="221">
@@ -7555,13 +7554,13 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="I221" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:15.401Z</v>
       </c>
     </row>
     <row r="222">
@@ -7587,13 +7586,13 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="I222" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:16.145Z</v>
       </c>
     </row>
     <row r="223">
@@ -7619,13 +7618,13 @@
         <v>PASS</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I223" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:17.033Z</v>
       </c>
     </row>
     <row r="224">
@@ -7651,13 +7650,13 @@
         <v>PASS</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="I224" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:17.848Z</v>
       </c>
     </row>
     <row r="225">
@@ -7668,7 +7667,7 @@
         <v>Fuzzing with database query snippets (215)</v>
       </c>
       <c r="C225" t="str">
-        <v>sql_fuzz_215_gq7f@test.com</v>
+        <v>sql_fuzz_215_6ktq@test.com</v>
       </c>
       <c r="D225" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7683,13 +7682,13 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>919</v>
       </c>
       <c r="I225" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:18.767Z</v>
       </c>
     </row>
     <row r="226">
@@ -7715,13 +7714,13 @@
         <v>PASS</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>869</v>
       </c>
       <c r="I226" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:19.636Z</v>
       </c>
     </row>
     <row r="227">
@@ -7747,13 +7746,13 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="I227" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:20.393Z</v>
       </c>
     </row>
     <row r="228">
@@ -7779,13 +7778,13 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="I228" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:20.927Z</v>
       </c>
     </row>
     <row r="229">
@@ -7811,13 +7810,13 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="I229" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:21.525Z</v>
       </c>
     </row>
     <row r="230">
@@ -7843,13 +7842,13 @@
         <v>PASS</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="I230" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:22.099Z</v>
       </c>
     </row>
     <row r="231">
@@ -7860,7 +7859,7 @@
         <v>Fuzzing with database query snippets (221)</v>
       </c>
       <c r="C231" t="str">
-        <v>sql_fuzz_221_vo2z@test.com</v>
+        <v>sql_fuzz_221_49lo@test.com</v>
       </c>
       <c r="D231" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7875,13 +7874,13 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I231" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:23.020Z</v>
       </c>
     </row>
     <row r="232">
@@ -7907,13 +7906,13 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="I232" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:23.813Z</v>
       </c>
     </row>
     <row r="233">
@@ -7939,13 +7938,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="I233" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:24.381Z</v>
       </c>
     </row>
     <row r="234">
@@ -7971,13 +7970,13 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="I234" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:24.928Z</v>
       </c>
     </row>
     <row r="235">
@@ -8003,13 +8002,13 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="I235" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:25.864Z</v>
       </c>
     </row>
     <row r="236">
@@ -8035,13 +8034,13 @@
         <v>PASS</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="I236" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:26.411Z</v>
       </c>
     </row>
     <row r="237">
@@ -8052,7 +8051,7 @@
         <v>Fuzzing with database query snippets (227)</v>
       </c>
       <c r="C237" t="str">
-        <v>sql_fuzz_227_zh3n@test.com</v>
+        <v>sql_fuzz_227_wla1@test.com</v>
       </c>
       <c r="D237" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8067,13 +8066,13 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I237" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:27.332Z</v>
       </c>
     </row>
     <row r="238">
@@ -8099,13 +8098,13 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="I238" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:27.950Z</v>
       </c>
     </row>
     <row r="239">
@@ -8131,13 +8130,13 @@
         <v>PASS</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="I239" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:28.717Z</v>
       </c>
     </row>
     <row r="240">
@@ -8163,13 +8162,13 @@
         <v>PASS</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="I240" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:29.489Z</v>
       </c>
     </row>
     <row r="241">
@@ -8195,13 +8194,13 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="I241" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-03T18:47:30.332Z</v>
       </c>
     </row>
     <row r="242">
@@ -8227,13 +8226,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="I242" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:31.181Z</v>
       </c>
     </row>
     <row r="243">
@@ -8244,7 +8243,7 @@
         <v>Fuzzing with database query snippets (233)</v>
       </c>
       <c r="C243" t="str">
-        <v>sql_fuzz_233_gh1d@test.com</v>
+        <v>sql_fuzz_233_eqjg@test.com</v>
       </c>
       <c r="D243" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8259,13 +8258,13 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="I243" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:31.872Z</v>
       </c>
     </row>
     <row r="244">
@@ -8291,13 +8290,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="I244" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:32.645Z</v>
       </c>
     </row>
     <row r="245">
@@ -8323,13 +8322,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="I245" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:33.362Z</v>
       </c>
     </row>
     <row r="246">
@@ -8355,13 +8354,13 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="I246" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:34.083Z</v>
       </c>
     </row>
     <row r="247">
@@ -8387,13 +8386,13 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>662</v>
       </c>
       <c r="I247" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:34.745Z</v>
       </c>
     </row>
     <row r="248">
@@ -8419,13 +8418,13 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I248" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:35.634Z</v>
       </c>
     </row>
     <row r="249">
@@ -8436,7 +8435,7 @@
         <v>Fuzzing with database query snippets (239)</v>
       </c>
       <c r="C249" t="str">
-        <v>sql_fuzz_239_r2ed@test.com</v>
+        <v>sql_fuzz_239_428a@test.com</v>
       </c>
       <c r="D249" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8451,13 +8450,13 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="I249" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:36.672Z</v>
       </c>
     </row>
     <row r="250">
@@ -8483,13 +8482,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>919</v>
       </c>
       <c r="I250" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:37.591Z</v>
       </c>
     </row>
     <row r="251">
@@ -8515,13 +8514,13 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="I251" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:38.432Z</v>
       </c>
     </row>
     <row r="252">
@@ -8547,13 +8546,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="I252" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:39.263Z</v>
       </c>
     </row>
     <row r="253">
@@ -8579,13 +8578,13 @@
         <v>PASS</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="I253" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:39.914Z</v>
       </c>
     </row>
     <row r="254">
@@ -8611,13 +8610,13 @@
         <v>PASS</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="I254" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:40.485Z</v>
       </c>
     </row>
     <row r="255">
@@ -8628,7 +8627,7 @@
         <v>Fuzzing with database query snippets (245)</v>
       </c>
       <c r="C255" t="str">
-        <v>sql_fuzz_245_ujfu@test.com</v>
+        <v>sql_fuzz_245_tdne@test.com</v>
       </c>
       <c r="D255" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8643,13 +8642,13 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="I255" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:41.343Z</v>
       </c>
     </row>
     <row r="256">
@@ -8675,13 +8674,13 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="I256" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:42.361Z</v>
       </c>
     </row>
     <row r="257">
@@ -8707,13 +8706,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="I257" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:42.882Z</v>
       </c>
     </row>
     <row r="258">
@@ -8739,13 +8738,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="I258" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:43.888Z</v>
       </c>
     </row>
     <row r="259">
@@ -8771,13 +8770,13 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="I259" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:44.536Z</v>
       </c>
     </row>
     <row r="260">
@@ -8803,13 +8802,13 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="I260" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:45.066Z</v>
       </c>
     </row>
     <row r="261">
@@ -8820,7 +8819,7 @@
         <v>Fuzzing with database query snippets (251)</v>
       </c>
       <c r="C261" t="str">
-        <v>sql_fuzz_251_mkiw@test.com</v>
+        <v>sql_fuzz_251_8qub@test.com</v>
       </c>
       <c r="D261" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8835,13 +8834,13 @@
         <v>PASS</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I261" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:45.966Z</v>
       </c>
     </row>
     <row r="262">
@@ -8867,13 +8866,13 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="I262" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:46.767Z</v>
       </c>
     </row>
     <row r="263">
@@ -8899,13 +8898,13 @@
         <v>PASS</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="I263" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:47.478Z</v>
       </c>
     </row>
     <row r="264">
@@ -8931,13 +8930,13 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="I264" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:47.964Z</v>
       </c>
     </row>
     <row r="265">
@@ -8963,13 +8962,13 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="I265" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:48.804Z</v>
       </c>
     </row>
     <row r="266">
@@ -8995,13 +8994,13 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="I266" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:49.416Z</v>
       </c>
     </row>
     <row r="267">
@@ -9012,7 +9011,7 @@
         <v>Fuzzing with database query snippets (257)</v>
       </c>
       <c r="C267" t="str">
-        <v>sql_fuzz_257_l2oz@test.com</v>
+        <v>sql_fuzz_257_x7yk@test.com</v>
       </c>
       <c r="D267" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9027,13 +9026,13 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="I267" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:50.292Z</v>
       </c>
     </row>
     <row r="268">
@@ -9059,13 +9058,13 @@
         <v>PASS</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="I268" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:51.080Z</v>
       </c>
     </row>
     <row r="269">
@@ -9091,13 +9090,13 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="I269" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:52.038Z</v>
       </c>
     </row>
     <row r="270">
@@ -9123,13 +9122,13 @@
         <v>PASS</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="I270" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:52.579Z</v>
       </c>
     </row>
     <row r="271">
@@ -9155,13 +9154,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="I271" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:53.480Z</v>
       </c>
     </row>
     <row r="272">
@@ -9187,13 +9186,13 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="I272" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:54.014Z</v>
       </c>
     </row>
     <row r="273">
@@ -9204,7 +9203,7 @@
         <v>Fuzzing with database query snippets (263)</v>
       </c>
       <c r="C273" t="str">
-        <v>sql_fuzz_263_gum0@test.com</v>
+        <v>sql_fuzz_263_6s6p@test.com</v>
       </c>
       <c r="D273" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9219,13 +9218,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>886</v>
       </c>
       <c r="I273" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:54.900Z</v>
       </c>
     </row>
     <row r="274">
@@ -9251,13 +9250,13 @@
         <v>PASS</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="I274" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:55.696Z</v>
       </c>
     </row>
     <row r="275">
@@ -9283,13 +9282,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="I275" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:56.626Z</v>
       </c>
     </row>
     <row r="276">
@@ -9315,13 +9314,13 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="I276" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:57.374Z</v>
       </c>
     </row>
     <row r="277">
@@ -9347,13 +9346,13 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="I277" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:58.217Z</v>
       </c>
     </row>
     <row r="278">
@@ -9379,13 +9378,13 @@
         <v>PASS</v>
       </c>
       <c r="H278">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="I278" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:58.781Z</v>
       </c>
     </row>
     <row r="279">
@@ -9396,7 +9395,7 @@
         <v>Fuzzing with database query snippets (269)</v>
       </c>
       <c r="C279" t="str">
-        <v>sql_fuzz_269_vtu9@test.com</v>
+        <v>sql_fuzz_269_jyek@test.com</v>
       </c>
       <c r="D279" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9411,13 +9410,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="I279" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:47:59.488Z</v>
       </c>
     </row>
     <row r="280">
@@ -9443,13 +9442,13 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="I280" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:00.294Z</v>
       </c>
     </row>
     <row r="281">
@@ -9475,13 +9474,13 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="I281" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:01.317Z</v>
       </c>
     </row>
     <row r="282">
@@ -9507,13 +9506,13 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I282" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:02.238Z</v>
       </c>
     </row>
     <row r="283">
@@ -9539,13 +9538,13 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="I283" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:03.267Z</v>
       </c>
     </row>
     <row r="284">
@@ -9571,13 +9570,13 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I284" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J284" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:04.167Z</v>
       </c>
     </row>
     <row r="285">
@@ -9588,7 +9587,7 @@
         <v>Fuzzing with database query snippets (275)</v>
       </c>
       <c r="C285" t="str">
-        <v>sql_fuzz_275_tx2k@test.com</v>
+        <v>sql_fuzz_275_gwos@test.com</v>
       </c>
       <c r="D285" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9603,13 +9602,13 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="I285" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J285" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:05.249Z</v>
       </c>
     </row>
     <row r="286">
@@ -9635,13 +9634,13 @@
         <v>PASS</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="I286" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J286" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:05.961Z</v>
       </c>
     </row>
     <row r="287">
@@ -9667,13 +9666,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="I287" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J287" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:06.909Z</v>
       </c>
     </row>
     <row r="288">
@@ -9699,13 +9698,13 @@
         <v>PASS</v>
       </c>
       <c r="H288">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="I288" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J288" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:07.552Z</v>
       </c>
     </row>
     <row r="289">
@@ -9731,13 +9730,13 @@
         <v>PASS</v>
       </c>
       <c r="H289">
-        <v>0</v>
+        <v>1074</v>
       </c>
       <c r="I289" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J289" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:08.626Z</v>
       </c>
     </row>
     <row r="290">
@@ -9763,13 +9762,13 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>1066</v>
       </c>
       <c r="I290" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J290" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:09.692Z</v>
       </c>
     </row>
     <row r="291">
@@ -9780,7 +9779,7 @@
         <v>Fuzzing with database query snippets (281)</v>
       </c>
       <c r="C291" t="str">
-        <v>sql_fuzz_281_5ddt@test.com</v>
+        <v>sql_fuzz_281_4oz1@test.com</v>
       </c>
       <c r="D291" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9795,13 +9794,13 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>1089</v>
       </c>
       <c r="I291" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J291" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:10.781Z</v>
       </c>
     </row>
     <row r="292">
@@ -9827,13 +9826,13 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="I292" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J292" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:11.784Z</v>
       </c>
     </row>
     <row r="293">
@@ -9859,13 +9858,13 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="I293" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J293" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:12.515Z</v>
       </c>
     </row>
     <row r="294">
@@ -9891,13 +9890,13 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="I294" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J294" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:13.651Z</v>
       </c>
     </row>
     <row r="295">
@@ -9923,13 +9922,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="I295" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J295" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:15.045Z</v>
       </c>
     </row>
     <row r="296">
@@ -9955,13 +9954,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="I296" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J296" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:16.075Z</v>
       </c>
     </row>
     <row r="297">
@@ -9972,7 +9971,7 @@
         <v>Fuzzing with database query snippets (287)</v>
       </c>
       <c r="C297" t="str">
-        <v>sql_fuzz_287_88l3@test.com</v>
+        <v>sql_fuzz_287_4cko@test.com</v>
       </c>
       <c r="D297" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9987,13 +9986,13 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="I297" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J297" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:17.305Z</v>
       </c>
     </row>
     <row r="298">
@@ -10019,13 +10018,13 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="I298" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J298" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:18.248Z</v>
       </c>
     </row>
     <row r="299">
@@ -10051,13 +10050,13 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I299" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J299" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:19.137Z</v>
       </c>
     </row>
     <row r="300">
@@ -10083,13 +10082,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="I300" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J300" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:20.134Z</v>
       </c>
     </row>
     <row r="301">
@@ -10115,13 +10114,13 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="I301" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J301" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:21.484Z</v>
       </c>
     </row>
     <row r="302">
@@ -10147,13 +10146,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="I302" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J302" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:22.459Z</v>
       </c>
     </row>
     <row r="303">
@@ -10164,7 +10163,7 @@
         <v>Fuzzing with database query snippets (293)</v>
       </c>
       <c r="C303" t="str">
-        <v>sql_fuzz_293_3g0j@test.com</v>
+        <v>sql_fuzz_293_77ge@test.com</v>
       </c>
       <c r="D303" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10179,13 +10178,13 @@
         <v>PASS</v>
       </c>
       <c r="H303">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I303" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J303" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:23.380Z</v>
       </c>
     </row>
     <row r="304">
@@ -10211,13 +10210,13 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="I304" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J304" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:24.179Z</v>
       </c>
     </row>
     <row r="305">
@@ -10243,13 +10242,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I305" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J305" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:24.879Z</v>
       </c>
     </row>
     <row r="306">
@@ -10275,13 +10274,13 @@
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="I306" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J306" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:25.684Z</v>
       </c>
     </row>
     <row r="307">
@@ -10307,13 +10306,13 @@
         <v>PASS</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="I307" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J307" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:26.606Z</v>
       </c>
     </row>
     <row r="308">
@@ -10339,13 +10338,13 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="I308" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J308" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:27.196Z</v>
       </c>
     </row>
     <row r="309">
@@ -10356,7 +10355,7 @@
         <v>Fuzzing with database query snippets (299)</v>
       </c>
       <c r="C309" t="str">
-        <v>sql_fuzz_299_bg15@test.com</v>
+        <v>sql_fuzz_299_2s4r@test.com</v>
       </c>
       <c r="D309" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10371,13 +10370,13 @@
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="I309" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J309" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:27.941Z</v>
       </c>
     </row>
     <row r="310">
@@ -10403,13 +10402,13 @@
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="I310" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J310" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:28.973Z</v>
       </c>
     </row>
     <row r="311">
@@ -10435,13 +10434,13 @@
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="I311" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J311" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:29.512Z</v>
       </c>
     </row>
     <row r="312">
@@ -10467,13 +10466,13 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="I312" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J312" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:30.000Z</v>
       </c>
     </row>
     <row r="313">
@@ -10499,13 +10498,13 @@
         <v>PASS</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="I313" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J313" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:30.883Z</v>
       </c>
     </row>
     <row r="314">
@@ -10531,13 +10530,13 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="I314" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J314" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:31.457Z</v>
       </c>
     </row>
     <row r="315">
@@ -10548,7 +10547,7 @@
         <v>Fuzzing with database query snippets (305)</v>
       </c>
       <c r="C315" t="str">
-        <v>sql_fuzz_305_cib2@test.com</v>
+        <v>sql_fuzz_305_447c@test.com</v>
       </c>
       <c r="D315" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10563,13 +10562,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="I315" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J315" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:32.425Z</v>
       </c>
     </row>
     <row r="316">
@@ -10595,13 +10594,13 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="I316" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J316" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:33.241Z</v>
       </c>
     </row>
     <row r="317">
@@ -10627,13 +10626,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="I317" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J317" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:33.989Z</v>
       </c>
     </row>
     <row r="318">
@@ -10659,13 +10658,13 @@
         <v>PASS</v>
       </c>
       <c r="H318">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="I318" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J318" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:34.769Z</v>
       </c>
     </row>
     <row r="319">
@@ -10691,13 +10690,13 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>1098</v>
       </c>
       <c r="I319" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J319" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:35.867Z</v>
       </c>
     </row>
     <row r="320">
@@ -10723,13 +10722,13 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="I320" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J320" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:36.872Z</v>
       </c>
     </row>
     <row r="321">
@@ -10740,7 +10739,7 @@
         <v>Fuzzing with database query snippets (311)</v>
       </c>
       <c r="C321" t="str">
-        <v>sql_fuzz_311_zr8p@test.com</v>
+        <v>sql_fuzz_311_74sg@test.com</v>
       </c>
       <c r="D321" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10755,13 +10754,13 @@
         <v>PASS</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="I321" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J321" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:37.700Z</v>
       </c>
     </row>
     <row r="322">
@@ -10787,13 +10786,13 @@
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="I322" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J322" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:38.529Z</v>
       </c>
     </row>
     <row r="323">
@@ -10819,13 +10818,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="I323" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J323" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:39.281Z</v>
       </c>
     </row>
     <row r="324">
@@ -10851,13 +10850,13 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="I324" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J324" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:40.065Z</v>
       </c>
     </row>
     <row r="325">
@@ -10883,13 +10882,13 @@
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>1513</v>
       </c>
       <c r="I325" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J325" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:41.578Z</v>
       </c>
     </row>
     <row r="326">
@@ -10915,13 +10914,13 @@
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I326" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J326" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:42.411Z</v>
       </c>
     </row>
     <row r="327">
@@ -10932,7 +10931,7 @@
         <v>Fuzzing with database query snippets (317)</v>
       </c>
       <c r="C327" t="str">
-        <v>sql_fuzz_317_c7dg@test.com</v>
+        <v>sql_fuzz_317_l62x@test.com</v>
       </c>
       <c r="D327" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10947,13 +10946,13 @@
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="I327" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J327" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:43.318Z</v>
       </c>
     </row>
     <row r="328">
@@ -10979,13 +10978,13 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="I328" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J328" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:43.954Z</v>
       </c>
     </row>
     <row r="329">
@@ -11011,13 +11010,13 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="I329" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J329" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:44.741Z</v>
       </c>
     </row>
     <row r="330">
@@ -11043,13 +11042,13 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="I330" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J330" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:45.600Z</v>
       </c>
     </row>
     <row r="331">
@@ -11075,13 +11074,13 @@
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="I331" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J331" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:46.335Z</v>
       </c>
     </row>
     <row r="332">
@@ -11107,13 +11106,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="I332" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J332" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:47.068Z</v>
       </c>
     </row>
     <row r="333">
@@ -11124,7 +11123,7 @@
         <v>Fuzzing with database query snippets (323)</v>
       </c>
       <c r="C333" t="str">
-        <v>sql_fuzz_323_n37r@test.com</v>
+        <v>sql_fuzz_323_y0lm@test.com</v>
       </c>
       <c r="D333" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11139,13 +11138,13 @@
         <v>PASS</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="I333" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J333" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:48.046Z</v>
       </c>
     </row>
     <row r="334">
@@ -11171,13 +11170,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="I334" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J334" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:48.741Z</v>
       </c>
     </row>
     <row r="335">
@@ -11203,13 +11202,13 @@
         <v>PASS</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="I335" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J335" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:49.413Z</v>
       </c>
     </row>
     <row r="336">
@@ -11235,13 +11234,13 @@
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="I336" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J336" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:50.182Z</v>
       </c>
     </row>
     <row r="337">
@@ -11267,13 +11266,13 @@
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="I337" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J337" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:51.065Z</v>
       </c>
     </row>
     <row r="338">
@@ -11299,13 +11298,13 @@
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="I338" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J338" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:52.113Z</v>
       </c>
     </row>
     <row r="339">
@@ -11316,7 +11315,7 @@
         <v>Fuzzing with database query snippets (329)</v>
       </c>
       <c r="C339" t="str">
-        <v>sql_fuzz_329_mtv6@test.com</v>
+        <v>sql_fuzz_329_tmer@test.com</v>
       </c>
       <c r="D339" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11331,13 +11330,13 @@
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="I339" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J339" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:53.264Z</v>
       </c>
     </row>
     <row r="340">
@@ -11363,13 +11362,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="I340" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J340" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:54.270Z</v>
       </c>
     </row>
     <row r="341">
@@ -11395,13 +11394,13 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="I341" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J341" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:55.191Z</v>
       </c>
     </row>
     <row r="342">
@@ -11427,13 +11426,13 @@
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="I342" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J342" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:56.213Z</v>
       </c>
     </row>
     <row r="343">
@@ -11459,13 +11458,13 @@
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="I343" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J343" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:57.278Z</v>
       </c>
     </row>
     <row r="344">
@@ -11491,13 +11490,13 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>0</v>
+        <v>988</v>
       </c>
       <c r="I344" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J344" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:58.266Z</v>
       </c>
     </row>
     <row r="345">
@@ -11508,7 +11507,7 @@
         <v>Fuzzing with database query snippets (335)</v>
       </c>
       <c r="C345" t="str">
-        <v>sql_fuzz_335_mm1g@test.com</v>
+        <v>sql_fuzz_335_b9r1@test.com</v>
       </c>
       <c r="D345" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11523,13 +11522,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="I345" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J345" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:48:59.318Z</v>
       </c>
     </row>
     <row r="346">
@@ -11555,13 +11554,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="I346" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J346" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:00.248Z</v>
       </c>
     </row>
     <row r="347">
@@ -11587,13 +11586,13 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="I347" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J347" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:01.151Z</v>
       </c>
     </row>
     <row r="348">
@@ -11619,13 +11618,13 @@
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="I348" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J348" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:01.882Z</v>
       </c>
     </row>
     <row r="349">
@@ -11651,13 +11650,13 @@
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>0</v>
+        <v>1123</v>
       </c>
       <c r="I349" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J349" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:03.005Z</v>
       </c>
     </row>
     <row r="350">
@@ -11683,13 +11682,13 @@
         <v>PASS</v>
       </c>
       <c r="H350">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I350" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J350" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:03.921Z</v>
       </c>
     </row>
     <row r="351">
@@ -11700,7 +11699,7 @@
         <v>Fuzzing with database query snippets (341)</v>
       </c>
       <c r="C351" t="str">
-        <v>sql_fuzz_341_a9fg@test.com</v>
+        <v>sql_fuzz_341_mkx5@test.com</v>
       </c>
       <c r="D351" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11715,13 +11714,13 @@
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="I351" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J351" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:04.911Z</v>
       </c>
     </row>
     <row r="352">
@@ -11747,13 +11746,13 @@
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="I352" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J352" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:05.806Z</v>
       </c>
     </row>
     <row r="353">
@@ -11779,13 +11778,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="I353" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J353" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:06.424Z</v>
       </c>
     </row>
     <row r="354">
@@ -11811,13 +11810,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>0</v>
+        <v>817</v>
       </c>
       <c r="I354" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J354" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:07.241Z</v>
       </c>
     </row>
     <row r="355">
@@ -11843,13 +11842,13 @@
         <v>PASS</v>
       </c>
       <c r="H355">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="I355" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J355" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:08.276Z</v>
       </c>
     </row>
     <row r="356">
@@ -11875,13 +11874,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>913</v>
       </c>
       <c r="I356" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J356" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:09.189Z</v>
       </c>
     </row>
     <row r="357">
@@ -11892,7 +11891,7 @@
         <v>Fuzzing with database query snippets (347)</v>
       </c>
       <c r="C357" t="str">
-        <v>sql_fuzz_347_wqgc@test.com</v>
+        <v>sql_fuzz_347_odx2@test.com</v>
       </c>
       <c r="D357" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11907,13 +11906,13 @@
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="I357" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J357" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:10.241Z</v>
       </c>
     </row>
     <row r="358">
@@ -11939,13 +11938,13 @@
         <v>PASS</v>
       </c>
       <c r="H358">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="I358" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J358" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:11.239Z</v>
       </c>
     </row>
     <row r="359">
@@ -11971,13 +11970,13 @@
         <v>PASS</v>
       </c>
       <c r="H359">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="I359" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J359" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:12.159Z</v>
       </c>
     </row>
     <row r="360">
@@ -12003,13 +12002,13 @@
         <v>PASS</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="I360" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J360" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:12.789Z</v>
       </c>
     </row>
     <row r="361">
@@ -12035,13 +12034,13 @@
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="I361" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J361" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:13.813Z</v>
       </c>
     </row>
     <row r="362">
@@ -12067,13 +12066,13 @@
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="I362" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J362" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:14.768Z</v>
       </c>
     </row>
     <row r="363">
@@ -12084,7 +12083,7 @@
         <v>Fuzzing with database query snippets (353)</v>
       </c>
       <c r="C363" t="str">
-        <v>sql_fuzz_353_3wgm@test.com</v>
+        <v>sql_fuzz_353_1yta@test.com</v>
       </c>
       <c r="D363" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12099,13 +12098,13 @@
         <v>PASS</v>
       </c>
       <c r="H363">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="I363" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J363" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:15.881Z</v>
       </c>
     </row>
     <row r="364">
@@ -12131,13 +12130,13 @@
         <v>PASS</v>
       </c>
       <c r="H364">
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="I364" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J364" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:16.898Z</v>
       </c>
     </row>
     <row r="365">
@@ -12163,13 +12162,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="I365" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J365" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:17.661Z</v>
       </c>
     </row>
     <row r="366">
@@ -12195,13 +12194,13 @@
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I366" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J366" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:18.550Z</v>
       </c>
     </row>
     <row r="367">
@@ -12227,13 +12226,13 @@
         <v>PASS</v>
       </c>
       <c r="H367">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="I367" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J367" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:19.632Z</v>
       </c>
     </row>
     <row r="368">
@@ -12259,13 +12258,13 @@
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I368" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J368" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:20.532Z</v>
       </c>
     </row>
     <row r="369">
@@ -12276,7 +12275,7 @@
         <v>Fuzzing with database query snippets (359)</v>
       </c>
       <c r="C369" t="str">
-        <v>sql_fuzz_359_q1sz@test.com</v>
+        <v>sql_fuzz_359_y9uz@test.com</v>
       </c>
       <c r="D369" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12291,13 +12290,13 @@
         <v>PASS</v>
       </c>
       <c r="H369">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="I369" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J369" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:21.543Z</v>
       </c>
     </row>
     <row r="370">
@@ -12323,13 +12322,13 @@
         <v>PASS</v>
       </c>
       <c r="H370">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="I370" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J370" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:22.254Z</v>
       </c>
     </row>
     <row r="371">
@@ -12355,13 +12354,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="I371" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J371" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:22.873Z</v>
       </c>
     </row>
     <row r="372">
@@ -12387,13 +12386,13 @@
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="I372" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J372" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:23.774Z</v>
       </c>
     </row>
     <row r="373">
@@ -12419,13 +12418,13 @@
         <v>PASS</v>
       </c>
       <c r="H373">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="I373" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J373" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:24.504Z</v>
       </c>
     </row>
     <row r="374">
@@ -12451,13 +12450,13 @@
         <v>PASS</v>
       </c>
       <c r="H374">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="I374" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J374" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:25.310Z</v>
       </c>
     </row>
     <row r="375">
@@ -12468,7 +12467,7 @@
         <v>Fuzzing with database query snippets (365)</v>
       </c>
       <c r="C375" t="str">
-        <v>sql_fuzz_365_ygrf@test.com</v>
+        <v>sql_fuzz_365_6cgt@test.com</v>
       </c>
       <c r="D375" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12483,13 +12482,13 @@
         <v>PASS</v>
       </c>
       <c r="H375">
-        <v>0</v>
+        <v>1044</v>
       </c>
       <c r="I375" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J375" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:26.354Z</v>
       </c>
     </row>
     <row r="376">
@@ -12515,13 +12514,13 @@
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="I376" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J376" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:27.031Z</v>
       </c>
     </row>
     <row r="377">
@@ -12547,13 +12546,13 @@
         <v>PASS</v>
       </c>
       <c r="H377">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="I377" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J377" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:27.712Z</v>
       </c>
     </row>
     <row r="378">
@@ -12579,13 +12578,13 @@
         <v>PASS</v>
       </c>
       <c r="H378">
-        <v>0</v>
+        <v>713</v>
       </c>
       <c r="I378" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J378" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:28.425Z</v>
       </c>
     </row>
     <row r="379">
@@ -12611,13 +12610,13 @@
         <v>PASS</v>
       </c>
       <c r="H379">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="I379" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J379" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:29.408Z</v>
       </c>
     </row>
     <row r="380">
@@ -12643,13 +12642,13 @@
         <v>PASS</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="I380" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J380" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:30.093Z</v>
       </c>
     </row>
     <row r="381">
@@ -12660,7 +12659,7 @@
         <v>Fuzzing with database query snippets (371)</v>
       </c>
       <c r="C381" t="str">
-        <v>sql_fuzz_371_isq4@test.com</v>
+        <v>sql_fuzz_371_p37l@test.com</v>
       </c>
       <c r="D381" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12675,13 +12674,13 @@
         <v>PASS</v>
       </c>
       <c r="H381">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="I381" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J381" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:31.005Z</v>
       </c>
     </row>
     <row r="382">
@@ -12707,13 +12706,13 @@
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="I382" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J382" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:32.073Z</v>
       </c>
     </row>
     <row r="383">
@@ -12739,13 +12738,13 @@
         <v>PASS</v>
       </c>
       <c r="H383">
-        <v>0</v>
+        <v>1076</v>
       </c>
       <c r="I383" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J383" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:33.149Z</v>
       </c>
     </row>
     <row r="384">
@@ -12771,13 +12770,13 @@
         <v>PASS</v>
       </c>
       <c r="H384">
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="I384" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J384" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:34.091Z</v>
       </c>
     </row>
     <row r="385">
@@ -12803,13 +12802,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>0</v>
+        <v>1226</v>
       </c>
       <c r="I385" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J385" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:35.317Z</v>
       </c>
     </row>
     <row r="386">
@@ -12835,13 +12834,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="I386" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J386" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:36.332Z</v>
       </c>
     </row>
     <row r="387">
@@ -12852,7 +12851,7 @@
         <v>Fuzzing with database query snippets (377)</v>
       </c>
       <c r="C387" t="str">
-        <v>sql_fuzz_377_zd6s@test.com</v>
+        <v>sql_fuzz_377_d635@test.com</v>
       </c>
       <c r="D387" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12867,13 +12866,13 @@
         <v>PASS</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>1058</v>
       </c>
       <c r="I387" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J387" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:37.390Z</v>
       </c>
     </row>
     <row r="388">
@@ -12899,13 +12898,13 @@
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="I388" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J388" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:38.343Z</v>
       </c>
     </row>
     <row r="389">
@@ -12931,13 +12930,13 @@
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I389" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J389" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:38.983Z</v>
       </c>
     </row>
     <row r="390">
@@ -12963,13 +12962,13 @@
         <v>PASS</v>
       </c>
       <c r="H390">
-        <v>0</v>
+        <v>1097</v>
       </c>
       <c r="I390" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J390" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:40.080Z</v>
       </c>
     </row>
     <row r="391">
@@ -12995,13 +12994,13 @@
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="I391" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J391" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:41.144Z</v>
       </c>
     </row>
     <row r="392">
@@ -13027,13 +13026,13 @@
         <v>PASS</v>
       </c>
       <c r="H392">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I392" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J392" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:41.794Z</v>
       </c>
     </row>
     <row r="393">
@@ -13044,7 +13043,7 @@
         <v>Fuzzing with database query snippets (383)</v>
       </c>
       <c r="C393" t="str">
-        <v>sql_fuzz_383_ubkb@test.com</v>
+        <v>sql_fuzz_383_wu78@test.com</v>
       </c>
       <c r="D393" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13059,13 +13058,13 @@
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>0</v>
+        <v>807</v>
       </c>
       <c r="I393" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J393" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:42.601Z</v>
       </c>
     </row>
     <row r="394">
@@ -13091,13 +13090,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="I394" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J394" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:43.279Z</v>
       </c>
     </row>
     <row r="395">
@@ -13123,13 +13122,13 @@
         <v>PASS</v>
       </c>
       <c r="H395">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="I395" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J395" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:44.127Z</v>
       </c>
     </row>
     <row r="396">
@@ -13155,13 +13154,13 @@
         <v>PASS</v>
       </c>
       <c r="H396">
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="I396" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J396" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:44.724Z</v>
       </c>
     </row>
     <row r="397">
@@ -13187,13 +13186,13 @@
         <v>PASS</v>
       </c>
       <c r="H397">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="I397" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J397" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:45.727Z</v>
       </c>
     </row>
     <row r="398">
@@ -13219,13 +13218,13 @@
         <v>PASS</v>
       </c>
       <c r="H398">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I398" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J398" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:46.827Z</v>
       </c>
     </row>
     <row r="399">
@@ -13236,7 +13235,7 @@
         <v>Fuzzing with database query snippets (389)</v>
       </c>
       <c r="C399" t="str">
-        <v>sql_fuzz_389_zh3c@test.com</v>
+        <v>sql_fuzz_389_2a0b@test.com</v>
       </c>
       <c r="D399" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13251,13 +13250,13 @@
         <v>PASS</v>
       </c>
       <c r="H399">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="I399" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J399" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:47.860Z</v>
       </c>
     </row>
     <row r="400">
@@ -13283,13 +13282,13 @@
         <v>PASS</v>
       </c>
       <c r="H400">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="I400" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J400" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:48.537Z</v>
       </c>
     </row>
     <row r="401">
@@ -13315,13 +13314,13 @@
         <v>PASS</v>
       </c>
       <c r="H401">
-        <v>0</v>
+        <v>887</v>
       </c>
       <c r="I401" t="str">
-        <v/>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J401" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-03T18:49:49.424Z</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/reports/selenium-test-report-400.xlsx
+++ b/selenium-tests/reports/selenium-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Total Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>359.95</v>
+        <v>456.35</v>
       </c>
     </row>
     <row r="7">
@@ -465,7 +465,7 @@
         <v>Executed At</v>
       </c>
       <c r="B8" t="str">
-        <v>4/8/2026, 12:19:49 am</v>
+        <v>8/8/2026, 1:07:30 pm</v>
       </c>
     </row>
   </sheetData>
@@ -546,13 +546,13 @@
         <v>FAIL</v>
       </c>
       <c r="H2">
-        <v>1507</v>
+        <v>4790</v>
       </c>
       <c r="I2" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-03T18:43:51.179Z</v>
+        <v>2026-08-08T07:29:59.278Z</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>FAIL</v>
       </c>
       <c r="H3">
-        <v>833</v>
+        <v>5113</v>
       </c>
       <c r="I3" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-03T18:43:52.012Z</v>
+        <v>2026-08-08T07:30:04.391Z</v>
       </c>
     </row>
     <row r="4">
@@ -610,13 +610,13 @@
         <v>FAIL</v>
       </c>
       <c r="H4">
-        <v>815</v>
+        <v>5131</v>
       </c>
       <c r="I4" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-03T18:43:52.827Z</v>
+        <v>2026-08-08T07:30:09.522Z</v>
       </c>
     </row>
     <row r="5">
@@ -642,13 +642,13 @@
         <v>PASS</v>
       </c>
       <c r="H5">
-        <v>3753</v>
+        <v>4558</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-03T18:43:56.580Z</v>
+        <v>2026-08-08T07:30:14.080Z</v>
       </c>
     </row>
     <row r="6">
@@ -674,13 +674,13 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>3594</v>
+        <v>4893</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-03T18:44:00.175Z</v>
+        <v>2026-08-08T07:30:18.974Z</v>
       </c>
     </row>
     <row r="7">
@@ -706,13 +706,13 @@
         <v>PASS</v>
       </c>
       <c r="H7">
-        <v>3553</v>
+        <v>4885</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-03T18:44:03.728Z</v>
+        <v>2026-08-08T07:30:23.859Z</v>
       </c>
     </row>
     <row r="8">
@@ -738,13 +738,13 @@
         <v>PASS</v>
       </c>
       <c r="H8">
-        <v>1210</v>
+        <v>4964</v>
       </c>
       <c r="I8" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-03T18:44:04.938Z</v>
+        <v>2026-08-08T07:30:28.823Z</v>
       </c>
     </row>
     <row r="9">
@@ -770,13 +770,13 @@
         <v>PASS</v>
       </c>
       <c r="H9">
-        <v>3704</v>
+        <v>4362</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-03T18:44:08.642Z</v>
+        <v>2026-08-08T07:30:33.185Z</v>
       </c>
     </row>
     <row r="10">
@@ -802,13 +802,13 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>3727</v>
+        <v>3860</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-03T18:44:12.369Z</v>
+        <v>2026-08-08T07:30:37.045Z</v>
       </c>
     </row>
     <row r="11">
@@ -834,13 +834,13 @@
         <v>PASS</v>
       </c>
       <c r="H11">
-        <v>1308</v>
+        <v>3847</v>
       </c>
       <c r="I11" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-03T18:44:13.678Z</v>
+        <v>2026-08-08T07:30:40.892Z</v>
       </c>
     </row>
     <row r="12">
@@ -866,13 +866,13 @@
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>1137</v>
+        <v>3757</v>
       </c>
       <c r="I12" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-03T18:44:14.815Z</v>
+        <v>2026-08-08T07:30:44.649Z</v>
       </c>
     </row>
     <row r="13">
@@ -898,13 +898,13 @@
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>1607</v>
+        <v>3723</v>
       </c>
       <c r="I13" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-03T18:44:16.422Z</v>
+        <v>2026-08-08T07:30:48.372Z</v>
       </c>
     </row>
     <row r="14">
@@ -930,13 +930,13 @@
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>987</v>
+        <v>3817</v>
       </c>
       <c r="I14" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-03T18:44:17.409Z</v>
+        <v>2026-08-08T07:30:52.189Z</v>
       </c>
     </row>
     <row r="15">
@@ -947,7 +947,7 @@
         <v>Fuzzing with database query snippets (5)</v>
       </c>
       <c r="C15" t="str">
-        <v>sql_fuzz_5_b60v@test.com</v>
+        <v>sql_fuzz_5_c022@test.com</v>
       </c>
       <c r="D15" t="str">
         <v>'; DROP TABLE u...</v>
@@ -962,13 +962,13 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>1074</v>
+        <v>3931</v>
       </c>
       <c r="I15" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-03T18:44:18.483Z</v>
+        <v>2026-08-08T07:30:56.120Z</v>
       </c>
     </row>
     <row r="16">
@@ -994,13 +994,13 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>995</v>
+        <v>3825</v>
       </c>
       <c r="I16" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-03T18:44:19.478Z</v>
+        <v>2026-08-08T07:30:59.945Z</v>
       </c>
     </row>
     <row r="17">
@@ -1026,13 +1026,13 @@
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>811</v>
+        <v>3880</v>
       </c>
       <c r="I17" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-03T18:44:20.289Z</v>
+        <v>2026-08-08T07:31:03.825Z</v>
       </c>
     </row>
     <row r="18">
@@ -1058,13 +1058,13 @@
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>874</v>
+        <v>4691</v>
       </c>
       <c r="I18" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-03T18:44:21.163Z</v>
+        <v>2026-08-08T07:31:08.516Z</v>
       </c>
     </row>
     <row r="19">
@@ -1090,13 +1090,13 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>950</v>
+        <v>5368</v>
       </c>
       <c r="I19" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-03T18:44:22.113Z</v>
+        <v>2026-08-08T07:31:13.884Z</v>
       </c>
     </row>
     <row r="20">
@@ -1122,13 +1122,13 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>722</v>
+        <v>5172</v>
       </c>
       <c r="I20" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-03T18:44:22.835Z</v>
+        <v>2026-08-08T07:31:19.056Z</v>
       </c>
     </row>
     <row r="21">
@@ -1139,7 +1139,7 @@
         <v>Fuzzing with database query snippets (11)</v>
       </c>
       <c r="C21" t="str">
-        <v>sql_fuzz_11_3ne4@test.com</v>
+        <v>sql_fuzz_11_1yrl@test.com</v>
       </c>
       <c r="D21" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1154,13 +1154,13 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>1025</v>
+        <v>5711</v>
       </c>
       <c r="I21" t="str">
-        <v>Email address does not exist.</v>
+        <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-03T18:44:23.860Z</v>
+        <v>2026-08-08T07:31:24.767Z</v>
       </c>
     </row>
     <row r="22">
@@ -1186,13 +1186,13 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>930</v>
+        <v>2263</v>
       </c>
       <c r="I22" t="str">
-        <v>Email address does not exist.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-03T18:44:24.790Z</v>
+        <v>2026-08-08T07:31:27.031Z</v>
       </c>
     </row>
     <row r="23">
@@ -1218,13 +1218,13 @@
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>665</v>
+        <v>2201</v>
       </c>
       <c r="I23" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-03T18:44:25.455Z</v>
+        <v>2026-08-08T07:31:29.232Z</v>
       </c>
     </row>
     <row r="24">
@@ -1250,13 +1250,13 @@
         <v>PASS</v>
       </c>
       <c r="H24">
-        <v>716</v>
+        <v>1932</v>
       </c>
       <c r="I24" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-03T18:44:26.171Z</v>
+        <v>2026-08-08T07:31:31.164Z</v>
       </c>
     </row>
     <row r="25">
@@ -1282,13 +1282,13 @@
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>982</v>
+        <v>2791</v>
       </c>
       <c r="I25" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-03T18:44:27.153Z</v>
+        <v>2026-08-08T07:31:33.955Z</v>
       </c>
     </row>
     <row r="26">
@@ -1314,13 +1314,13 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>775</v>
+        <v>2250</v>
       </c>
       <c r="I26" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-03T18:44:27.928Z</v>
+        <v>2026-08-08T07:31:36.206Z</v>
       </c>
     </row>
     <row r="27">
@@ -1331,7 +1331,7 @@
         <v>Fuzzing with database query snippets (17)</v>
       </c>
       <c r="C27" t="str">
-        <v>sql_fuzz_17_inl7@test.com</v>
+        <v>sql_fuzz_17_jyky@test.com</v>
       </c>
       <c r="D27" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1346,13 +1346,13 @@
         <v>PASS</v>
       </c>
       <c r="H27">
-        <v>1086</v>
+        <v>2617</v>
       </c>
       <c r="I27" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-03T18:44:29.014Z</v>
+        <v>2026-08-08T07:31:38.823Z</v>
       </c>
     </row>
     <row r="28">
@@ -1378,13 +1378,13 @@
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>847</v>
+        <v>2155</v>
       </c>
       <c r="I28" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-03T18:44:29.861Z</v>
+        <v>2026-08-08T07:31:40.978Z</v>
       </c>
     </row>
     <row r="29">
@@ -1410,13 +1410,13 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>660</v>
+        <v>2006</v>
       </c>
       <c r="I29" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-03T18:44:30.521Z</v>
+        <v>2026-08-08T07:31:42.984Z</v>
       </c>
     </row>
     <row r="30">
@@ -1442,13 +1442,13 @@
         <v>PASS</v>
       </c>
       <c r="H30">
-        <v>959</v>
+        <v>2079</v>
       </c>
       <c r="I30" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-03T18:44:31.480Z</v>
+        <v>2026-08-08T07:31:45.063Z</v>
       </c>
     </row>
     <row r="31">
@@ -1474,13 +1474,13 @@
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>960</v>
+        <v>2908</v>
       </c>
       <c r="I31" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-03T18:44:32.440Z</v>
+        <v>2026-08-08T07:31:47.971Z</v>
       </c>
     </row>
     <row r="32">
@@ -1506,13 +1506,13 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>877</v>
+        <v>2265</v>
       </c>
       <c r="I32" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-03T18:44:33.317Z</v>
+        <v>2026-08-08T07:31:50.237Z</v>
       </c>
     </row>
     <row r="33">
@@ -1523,7 +1523,7 @@
         <v>Fuzzing with database query snippets (23)</v>
       </c>
       <c r="C33" t="str">
-        <v>sql_fuzz_23_1ggr@test.com</v>
+        <v>sql_fuzz_23_nema@test.com</v>
       </c>
       <c r="D33" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1538,13 +1538,13 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>789</v>
+        <v>2843</v>
       </c>
       <c r="I33" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-03T18:44:34.106Z</v>
+        <v>2026-08-08T07:31:53.080Z</v>
       </c>
     </row>
     <row r="34">
@@ -1570,13 +1570,13 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>889</v>
+        <v>2253</v>
       </c>
       <c r="I34" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-03T18:44:34.995Z</v>
+        <v>2026-08-08T07:31:55.333Z</v>
       </c>
     </row>
     <row r="35">
@@ -1602,13 +1602,13 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>589</v>
+        <v>2132</v>
       </c>
       <c r="I35" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-03T18:44:35.584Z</v>
+        <v>2026-08-08T07:31:57.465Z</v>
       </c>
     </row>
     <row r="36">
@@ -1634,13 +1634,13 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>698</v>
+        <v>2056</v>
       </c>
       <c r="I36" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-03T18:44:36.282Z</v>
+        <v>2026-08-08T07:31:59.521Z</v>
       </c>
     </row>
     <row r="37">
@@ -1666,13 +1666,13 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>787</v>
+        <v>2833</v>
       </c>
       <c r="I37" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-03T18:44:37.069Z</v>
+        <v>2026-08-08T07:32:02.354Z</v>
       </c>
     </row>
     <row r="38">
@@ -1698,13 +1698,13 @@
         <v>PASS</v>
       </c>
       <c r="H38">
-        <v>662</v>
+        <v>1880</v>
       </c>
       <c r="I38" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-03T18:44:37.731Z</v>
+        <v>2026-08-08T07:32:04.234Z</v>
       </c>
     </row>
     <row r="39">
@@ -1715,7 +1715,7 @@
         <v>Fuzzing with database query snippets (29)</v>
       </c>
       <c r="C39" t="str">
-        <v>sql_fuzz_29_ci2k@test.com</v>
+        <v>sql_fuzz_29_v8ka@test.com</v>
       </c>
       <c r="D39" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1730,13 +1730,13 @@
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>975</v>
+        <v>2462</v>
       </c>
       <c r="I39" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-03T18:44:38.706Z</v>
+        <v>2026-08-08T07:32:06.696Z</v>
       </c>
     </row>
     <row r="40">
@@ -1762,13 +1762,13 @@
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>917</v>
+        <v>2033</v>
       </c>
       <c r="I40" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-03T18:44:39.623Z</v>
+        <v>2026-08-08T07:32:08.729Z</v>
       </c>
     </row>
     <row r="41">
@@ -1794,13 +1794,13 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>854</v>
+        <v>1999</v>
       </c>
       <c r="I41" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-03T18:44:40.477Z</v>
+        <v>2026-08-08T07:32:10.728Z</v>
       </c>
     </row>
     <row r="42">
@@ -1826,13 +1826,13 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>928</v>
+        <v>2068</v>
       </c>
       <c r="I42" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-03T18:44:41.405Z</v>
+        <v>2026-08-08T07:32:12.797Z</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>982</v>
+        <v>2843</v>
       </c>
       <c r="I43" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-03T18:44:42.387Z</v>
+        <v>2026-08-08T07:32:15.640Z</v>
       </c>
     </row>
     <row r="44">
@@ -1890,13 +1890,13 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>900</v>
+        <v>2130</v>
       </c>
       <c r="I44" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-03T18:44:43.288Z</v>
+        <v>2026-08-08T07:32:17.770Z</v>
       </c>
     </row>
     <row r="45">
@@ -1907,7 +1907,7 @@
         <v>Fuzzing with database query snippets (35)</v>
       </c>
       <c r="C45" t="str">
-        <v>sql_fuzz_35_u65j@test.com</v>
+        <v>sql_fuzz_35_zqx1@test.com</v>
       </c>
       <c r="D45" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1922,13 +1922,13 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>968</v>
+        <v>2904</v>
       </c>
       <c r="I45" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-03T18:44:44.256Z</v>
+        <v>2026-08-08T07:32:20.674Z</v>
       </c>
     </row>
     <row r="46">
@@ -1954,13 +1954,13 @@
         <v>PASS</v>
       </c>
       <c r="H46">
-        <v>659</v>
+        <v>2112</v>
       </c>
       <c r="I46" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-03T18:44:44.915Z</v>
+        <v>2026-08-08T07:32:22.786Z</v>
       </c>
     </row>
     <row r="47">
@@ -1986,13 +1986,13 @@
         <v>PASS</v>
       </c>
       <c r="H47">
-        <v>853</v>
+        <v>2143</v>
       </c>
       <c r="I47" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-03T18:44:45.768Z</v>
+        <v>2026-08-08T07:32:24.929Z</v>
       </c>
     </row>
     <row r="48">
@@ -2018,13 +2018,13 @@
         <v>PASS</v>
       </c>
       <c r="H48">
-        <v>922</v>
+        <v>1799</v>
       </c>
       <c r="I48" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-03T18:44:46.691Z</v>
+        <v>2026-08-08T07:32:26.728Z</v>
       </c>
     </row>
     <row r="49">
@@ -2050,13 +2050,13 @@
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>1031</v>
+        <v>2937</v>
       </c>
       <c r="I49" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-03T18:44:47.722Z</v>
+        <v>2026-08-08T07:32:29.665Z</v>
       </c>
     </row>
     <row r="50">
@@ -2082,13 +2082,13 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>623</v>
+        <v>2136</v>
       </c>
       <c r="I50" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-03T18:44:48.345Z</v>
+        <v>2026-08-08T07:32:31.801Z</v>
       </c>
     </row>
     <row r="51">
@@ -2099,7 +2099,7 @@
         <v>Fuzzing with database query snippets (41)</v>
       </c>
       <c r="C51" t="str">
-        <v>sql_fuzz_41_j6zl@test.com</v>
+        <v>sql_fuzz_41_kte5@test.com</v>
       </c>
       <c r="D51" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2114,13 +2114,13 @@
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>759</v>
+        <v>2960</v>
       </c>
       <c r="I51" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-03T18:44:49.104Z</v>
+        <v>2026-08-08T07:32:34.761Z</v>
       </c>
     </row>
     <row r="52">
@@ -2146,13 +2146,13 @@
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>882</v>
+        <v>2207</v>
       </c>
       <c r="I52" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-03T18:44:49.986Z</v>
+        <v>2026-08-08T07:32:36.968Z</v>
       </c>
     </row>
     <row r="53">
@@ -2178,13 +2178,13 @@
         <v>PASS</v>
       </c>
       <c r="H53">
-        <v>838</v>
+        <v>2094</v>
       </c>
       <c r="I53" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-03T18:44:50.824Z</v>
+        <v>2026-08-08T07:32:39.062Z</v>
       </c>
     </row>
     <row r="54">
@@ -2210,13 +2210,13 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>911</v>
+        <v>1971</v>
       </c>
       <c r="I54" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-03T18:44:51.735Z</v>
+        <v>2026-08-08T07:32:41.033Z</v>
       </c>
     </row>
     <row r="55">
@@ -2242,13 +2242,13 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>1065</v>
+        <v>2896</v>
       </c>
       <c r="I55" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-03T18:44:52.800Z</v>
+        <v>2026-08-08T07:32:43.929Z</v>
       </c>
     </row>
     <row r="56">
@@ -2274,13 +2274,13 @@
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>950</v>
+        <v>2167</v>
       </c>
       <c r="I56" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-03T18:44:53.750Z</v>
+        <v>2026-08-08T07:32:46.096Z</v>
       </c>
     </row>
     <row r="57">
@@ -2291,7 +2291,7 @@
         <v>Fuzzing with database query snippets (47)</v>
       </c>
       <c r="C57" t="str">
-        <v>sql_fuzz_47_th2t@test.com</v>
+        <v>sql_fuzz_47_t8m5@test.com</v>
       </c>
       <c r="D57" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2306,13 +2306,13 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>805</v>
+        <v>2596</v>
       </c>
       <c r="I57" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-03T18:44:54.555Z</v>
+        <v>2026-08-08T07:32:48.692Z</v>
       </c>
     </row>
     <row r="58">
@@ -2338,13 +2338,13 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>728</v>
+        <v>2282</v>
       </c>
       <c r="I58" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-03T18:44:55.283Z</v>
+        <v>2026-08-08T07:32:50.974Z</v>
       </c>
     </row>
     <row r="59">
@@ -2370,13 +2370,13 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>744</v>
+        <v>1966</v>
       </c>
       <c r="I59" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-03T18:44:56.027Z</v>
+        <v>2026-08-08T07:32:52.940Z</v>
       </c>
     </row>
     <row r="60">
@@ -2402,13 +2402,13 @@
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>681</v>
+        <v>950</v>
       </c>
       <c r="I60" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-03T18:44:56.708Z</v>
+        <v>2026-08-08T07:32:53.890Z</v>
       </c>
     </row>
     <row r="61">
@@ -2434,13 +2434,13 @@
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>774</v>
+        <v>1177</v>
       </c>
       <c r="I61" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-03T18:44:57.482Z</v>
+        <v>2026-08-08T07:32:55.067Z</v>
       </c>
     </row>
     <row r="62">
@@ -2466,13 +2466,13 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>656</v>
+        <v>997</v>
       </c>
       <c r="I62" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-03T18:44:58.138Z</v>
+        <v>2026-08-08T07:32:56.064Z</v>
       </c>
     </row>
     <row r="63">
@@ -2483,7 +2483,7 @@
         <v>Fuzzing with database query snippets (53)</v>
       </c>
       <c r="C63" t="str">
-        <v>sql_fuzz_53_efas@test.com</v>
+        <v>sql_fuzz_53_acxy@test.com</v>
       </c>
       <c r="D63" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2498,13 +2498,13 @@
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>1253</v>
+        <v>2503</v>
       </c>
       <c r="I63" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-03T18:44:59.391Z</v>
+        <v>2026-08-08T07:32:58.567Z</v>
       </c>
     </row>
     <row r="64">
@@ -2530,13 +2530,13 @@
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>926</v>
+        <v>1886</v>
       </c>
       <c r="I64" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-03T18:45:00.317Z</v>
+        <v>2026-08-08T07:33:00.453Z</v>
       </c>
     </row>
     <row r="65">
@@ -2562,13 +2562,13 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>923</v>
+        <v>807</v>
       </c>
       <c r="I65" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-03T18:45:01.240Z</v>
+        <v>2026-08-08T07:33:01.260Z</v>
       </c>
     </row>
     <row r="66">
@@ -2594,13 +2594,13 @@
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>610</v>
+        <v>732</v>
       </c>
       <c r="I66" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-03T18:45:01.850Z</v>
+        <v>2026-08-08T07:33:01.993Z</v>
       </c>
     </row>
     <row r="67">
@@ -2626,13 +2626,13 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>1085</v>
+        <v>885</v>
       </c>
       <c r="I67" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-03T18:45:02.935Z</v>
+        <v>2026-08-08T07:33:02.878Z</v>
       </c>
     </row>
     <row r="68">
@@ -2658,13 +2658,13 @@
         <v>PASS</v>
       </c>
       <c r="H68">
-        <v>630</v>
+        <v>768</v>
       </c>
       <c r="I68" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-03T18:45:03.565Z</v>
+        <v>2026-08-08T07:33:03.646Z</v>
       </c>
     </row>
     <row r="69">
@@ -2675,7 +2675,7 @@
         <v>Fuzzing with database query snippets (59)</v>
       </c>
       <c r="C69" t="str">
-        <v>sql_fuzz_59_bmy5@test.com</v>
+        <v>sql_fuzz_59_rh3h@test.com</v>
       </c>
       <c r="D69" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2690,13 +2690,13 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>986</v>
+        <v>885</v>
       </c>
       <c r="I69" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-03T18:45:04.551Z</v>
+        <v>2026-08-08T07:33:04.531Z</v>
       </c>
     </row>
     <row r="70">
@@ -2722,13 +2722,13 @@
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>656</v>
+        <v>860</v>
       </c>
       <c r="I70" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-03T18:45:05.207Z</v>
+        <v>2026-08-08T07:33:05.391Z</v>
       </c>
     </row>
     <row r="71">
@@ -2754,13 +2754,13 @@
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>882</v>
+        <v>921</v>
       </c>
       <c r="I71" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-03T18:45:06.089Z</v>
+        <v>2026-08-08T07:33:06.312Z</v>
       </c>
     </row>
     <row r="72">
@@ -2786,13 +2786,13 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>904</v>
+        <v>727</v>
       </c>
       <c r="I72" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-03T18:45:06.993Z</v>
+        <v>2026-08-08T07:33:07.039Z</v>
       </c>
     </row>
     <row r="73">
@@ -2818,13 +2818,13 @@
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>911</v>
+        <v>617</v>
       </c>
       <c r="I73" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-03T18:45:07.904Z</v>
+        <v>2026-08-08T07:33:07.656Z</v>
       </c>
     </row>
     <row r="74">
@@ -2850,13 +2850,13 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>1056</v>
+        <v>789</v>
       </c>
       <c r="I74" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-03T18:45:08.960Z</v>
+        <v>2026-08-08T07:33:08.445Z</v>
       </c>
     </row>
     <row r="75">
@@ -2867,7 +2867,7 @@
         <v>Fuzzing with database query snippets (65)</v>
       </c>
       <c r="C75" t="str">
-        <v>sql_fuzz_65_bk5m@test.com</v>
+        <v>sql_fuzz_65_owpa@test.com</v>
       </c>
       <c r="D75" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2882,13 +2882,13 @@
         <v>PASS</v>
       </c>
       <c r="H75">
-        <v>921</v>
+        <v>895</v>
       </c>
       <c r="I75" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-03T18:45:09.881Z</v>
+        <v>2026-08-08T07:33:09.340Z</v>
       </c>
     </row>
     <row r="76">
@@ -2914,13 +2914,13 @@
         <v>PASS</v>
       </c>
       <c r="H76">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="I76" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-03T18:45:10.891Z</v>
+        <v>2026-08-08T07:33:10.311Z</v>
       </c>
     </row>
     <row r="77">
@@ -2946,13 +2946,13 @@
         <v>PASS</v>
       </c>
       <c r="H77">
-        <v>613</v>
+        <v>784</v>
       </c>
       <c r="I77" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-03T18:45:11.504Z</v>
+        <v>2026-08-08T07:33:11.095Z</v>
       </c>
     </row>
     <row r="78">
@@ -2978,13 +2978,13 @@
         <v>PASS</v>
       </c>
       <c r="H78">
-        <v>666</v>
+        <v>942</v>
       </c>
       <c r="I78" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-03T18:45:12.170Z</v>
+        <v>2026-08-08T07:33:12.037Z</v>
       </c>
     </row>
     <row r="79">
@@ -3010,13 +3010,13 @@
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>1053</v>
+        <v>871</v>
       </c>
       <c r="I79" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-03T18:45:13.223Z</v>
+        <v>2026-08-08T07:33:12.908Z</v>
       </c>
     </row>
     <row r="80">
@@ -3042,13 +3042,13 @@
         <v>PASS</v>
       </c>
       <c r="H80">
-        <v>918</v>
+        <v>764</v>
       </c>
       <c r="I80" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-03T18:45:14.141Z</v>
+        <v>2026-08-08T07:33:13.672Z</v>
       </c>
     </row>
     <row r="81">
@@ -3059,7 +3059,7 @@
         <v>Fuzzing with database query snippets (71)</v>
       </c>
       <c r="C81" t="str">
-        <v>sql_fuzz_71_ostr@test.com</v>
+        <v>sql_fuzz_71_xx0s@test.com</v>
       </c>
       <c r="D81" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3074,13 +3074,13 @@
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>1115</v>
+        <v>617</v>
       </c>
       <c r="I81" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-03T18:45:15.256Z</v>
+        <v>2026-08-08T07:33:14.289Z</v>
       </c>
     </row>
     <row r="82">
@@ -3106,13 +3106,13 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>1116</v>
+        <v>770</v>
       </c>
       <c r="I82" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-03T18:45:16.372Z</v>
+        <v>2026-08-08T07:33:15.059Z</v>
       </c>
     </row>
     <row r="83">
@@ -3138,13 +3138,13 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>916</v>
+        <v>758</v>
       </c>
       <c r="I83" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-03T18:45:17.288Z</v>
+        <v>2026-08-08T07:33:15.817Z</v>
       </c>
     </row>
     <row r="84">
@@ -3170,13 +3170,13 @@
         <v>PASS</v>
       </c>
       <c r="H84">
-        <v>830</v>
+        <v>541</v>
       </c>
       <c r="I84" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-03T18:45:18.118Z</v>
+        <v>2026-08-08T07:33:16.358Z</v>
       </c>
     </row>
     <row r="85">
@@ -3202,13 +3202,13 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>1138</v>
+        <v>864</v>
       </c>
       <c r="I85" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-03T18:45:19.256Z</v>
+        <v>2026-08-08T07:33:17.222Z</v>
       </c>
     </row>
     <row r="86">
@@ -3234,13 +3234,13 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>923</v>
+        <v>803</v>
       </c>
       <c r="I86" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-03T18:45:20.179Z</v>
+        <v>2026-08-08T07:33:18.025Z</v>
       </c>
     </row>
     <row r="87">
@@ -3251,7 +3251,7 @@
         <v>Fuzzing with database query snippets (77)</v>
       </c>
       <c r="C87" t="str">
-        <v>sql_fuzz_77_zxfx@test.com</v>
+        <v>sql_fuzz_77_64eq@test.com</v>
       </c>
       <c r="D87" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3266,13 +3266,13 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I87" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-03T18:45:21.068Z</v>
+        <v>2026-08-08T07:33:18.911Z</v>
       </c>
     </row>
     <row r="88">
@@ -3298,13 +3298,13 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>951</v>
+        <v>783</v>
       </c>
       <c r="I88" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-03T18:45:22.019Z</v>
+        <v>2026-08-08T07:33:19.694Z</v>
       </c>
     </row>
     <row r="89">
@@ -3330,13 +3330,13 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>892</v>
+        <v>760</v>
       </c>
       <c r="I89" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-03T18:45:22.911Z</v>
+        <v>2026-08-08T07:33:20.454Z</v>
       </c>
     </row>
     <row r="90">
@@ -3362,13 +3362,13 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>851</v>
+        <v>952</v>
       </c>
       <c r="I90" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-03T18:45:23.762Z</v>
+        <v>2026-08-08T07:33:21.406Z</v>
       </c>
     </row>
     <row r="91">
@@ -3394,13 +3394,13 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>1063</v>
+        <v>798</v>
       </c>
       <c r="I91" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-03T18:45:24.825Z</v>
+        <v>2026-08-08T07:33:22.204Z</v>
       </c>
     </row>
     <row r="92">
@@ -3426,13 +3426,13 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>658</v>
+        <v>984</v>
       </c>
       <c r="I92" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-03T18:45:25.483Z</v>
+        <v>2026-08-08T07:33:23.188Z</v>
       </c>
     </row>
     <row r="93">
@@ -3443,7 +3443,7 @@
         <v>Fuzzing with database query snippets (83)</v>
       </c>
       <c r="C93" t="str">
-        <v>sql_fuzz_83_p7oy@test.com</v>
+        <v>sql_fuzz_83_bofn@test.com</v>
       </c>
       <c r="D93" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3458,13 +3458,13 @@
         <v>PASS</v>
       </c>
       <c r="H93">
-        <v>1095</v>
+        <v>841</v>
       </c>
       <c r="I93" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-03T18:45:26.578Z</v>
+        <v>2026-08-08T07:33:24.029Z</v>
       </c>
     </row>
     <row r="94">
@@ -3490,13 +3490,13 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>656</v>
+        <v>782</v>
       </c>
       <c r="I94" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-03T18:45:27.234Z</v>
+        <v>2026-08-08T07:33:24.811Z</v>
       </c>
     </row>
     <row r="95">
@@ -3522,13 +3522,13 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>858</v>
+        <v>781</v>
       </c>
       <c r="I95" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-03T18:45:28.092Z</v>
+        <v>2026-08-08T07:33:25.592Z</v>
       </c>
     </row>
     <row r="96">
@@ -3554,13 +3554,13 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>633</v>
+        <v>684</v>
       </c>
       <c r="I96" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-03T18:45:28.725Z</v>
+        <v>2026-08-08T07:33:26.276Z</v>
       </c>
     </row>
     <row r="97">
@@ -3586,13 +3586,13 @@
         <v>PASS</v>
       </c>
       <c r="H97">
-        <v>1154</v>
+        <v>588</v>
       </c>
       <c r="I97" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-03T18:45:29.879Z</v>
+        <v>2026-08-08T07:33:26.864Z</v>
       </c>
     </row>
     <row r="98">
@@ -3618,13 +3618,13 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>938</v>
+        <v>757</v>
       </c>
       <c r="I98" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-03T18:45:30.817Z</v>
+        <v>2026-08-08T07:33:27.621Z</v>
       </c>
     </row>
     <row r="99">
@@ -3635,7 +3635,7 @@
         <v>Fuzzing with database query snippets (89)</v>
       </c>
       <c r="C99" t="str">
-        <v>sql_fuzz_89_6iv0@test.com</v>
+        <v>sql_fuzz_89_4wm2@test.com</v>
       </c>
       <c r="D99" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3650,13 +3650,13 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>1101</v>
+        <v>864</v>
       </c>
       <c r="I99" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-03T18:45:31.918Z</v>
+        <v>2026-08-08T07:33:28.485Z</v>
       </c>
     </row>
     <row r="100">
@@ -3682,13 +3682,13 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>1018</v>
+        <v>751</v>
       </c>
       <c r="I100" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-03T18:45:32.936Z</v>
+        <v>2026-08-08T07:33:29.236Z</v>
       </c>
     </row>
     <row r="101">
@@ -3720,7 +3720,7 @@
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-03T18:45:33.889Z</v>
+        <v>2026-08-08T07:33:30.189Z</v>
       </c>
     </row>
     <row r="102">
@@ -3746,13 +3746,13 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>1033</v>
+        <v>788</v>
       </c>
       <c r="I102" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-03T18:45:34.923Z</v>
+        <v>2026-08-08T07:33:30.977Z</v>
       </c>
     </row>
     <row r="103">
@@ -3778,13 +3778,13 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>1100</v>
+        <v>851</v>
       </c>
       <c r="I103" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-03T18:45:36.023Z</v>
+        <v>2026-08-08T07:33:31.828Z</v>
       </c>
     </row>
     <row r="104">
@@ -3810,13 +3810,13 @@
         <v>PASS</v>
       </c>
       <c r="H104">
-        <v>1258</v>
+        <v>982</v>
       </c>
       <c r="I104" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-03T18:45:37.281Z</v>
+        <v>2026-08-08T07:33:32.810Z</v>
       </c>
     </row>
     <row r="105">
@@ -3827,7 +3827,7 @@
         <v>Fuzzing with database query snippets (95)</v>
       </c>
       <c r="C105" t="str">
-        <v>sql_fuzz_95_hc7b@test.com</v>
+        <v>sql_fuzz_95_t5n8@test.com</v>
       </c>
       <c r="D105" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3842,13 +3842,13 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>1325</v>
+        <v>826</v>
       </c>
       <c r="I105" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-03T18:45:38.606Z</v>
+        <v>2026-08-08T07:33:33.636Z</v>
       </c>
     </row>
     <row r="106">
@@ -3874,13 +3874,13 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>918</v>
+        <v>839</v>
       </c>
       <c r="I106" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-03T18:45:39.524Z</v>
+        <v>2026-08-08T07:33:34.475Z</v>
       </c>
     </row>
     <row r="107">
@@ -3906,13 +3906,13 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>883</v>
+        <v>736</v>
       </c>
       <c r="I107" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-03T18:45:40.407Z</v>
+        <v>2026-08-08T07:33:35.211Z</v>
       </c>
     </row>
     <row r="108">
@@ -3938,13 +3938,13 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>936</v>
+        <v>723</v>
       </c>
       <c r="I108" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-03T18:45:41.343Z</v>
+        <v>2026-08-08T07:33:35.934Z</v>
       </c>
     </row>
     <row r="109">
@@ -3970,13 +3970,13 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>1121</v>
+        <v>893</v>
       </c>
       <c r="I109" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-03T18:45:42.464Z</v>
+        <v>2026-08-08T07:33:36.827Z</v>
       </c>
     </row>
     <row r="110">
@@ -4002,13 +4002,13 @@
         <v>PASS</v>
       </c>
       <c r="H110">
-        <v>848</v>
+        <v>783</v>
       </c>
       <c r="I110" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-03T18:45:43.312Z</v>
+        <v>2026-08-08T07:33:37.610Z</v>
       </c>
     </row>
     <row r="111">
@@ -4019,7 +4019,7 @@
         <v>Fuzzing with database query snippets (101)</v>
       </c>
       <c r="C111" t="str">
-        <v>sql_fuzz_101_mxzs@test.com</v>
+        <v>sql_fuzz_101_0taj@test.com</v>
       </c>
       <c r="D111" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4034,13 +4034,13 @@
         <v>PASS</v>
       </c>
       <c r="H111">
-        <v>1194</v>
+        <v>872</v>
       </c>
       <c r="I111" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-03T18:45:44.506Z</v>
+        <v>2026-08-08T07:33:38.482Z</v>
       </c>
     </row>
     <row r="112">
@@ -4066,13 +4066,13 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>1123</v>
+        <v>804</v>
       </c>
       <c r="I112" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-03T18:45:45.629Z</v>
+        <v>2026-08-08T07:33:39.286Z</v>
       </c>
     </row>
     <row r="113">
@@ -4098,13 +4098,13 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>1041</v>
+        <v>760</v>
       </c>
       <c r="I113" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-03T18:45:46.670Z</v>
+        <v>2026-08-08T07:33:40.046Z</v>
       </c>
     </row>
     <row r="114">
@@ -4130,13 +4130,13 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>966</v>
+        <v>715</v>
       </c>
       <c r="I114" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-03T18:45:47.636Z</v>
+        <v>2026-08-08T07:33:40.761Z</v>
       </c>
     </row>
     <row r="115">
@@ -4162,13 +4162,13 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>911</v>
+        <v>950</v>
       </c>
       <c r="I115" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-03T18:45:48.547Z</v>
+        <v>2026-08-08T07:33:41.711Z</v>
       </c>
     </row>
     <row r="116">
@@ -4194,13 +4194,13 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>791</v>
+        <v>862</v>
       </c>
       <c r="I116" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-03T18:45:49.338Z</v>
+        <v>2026-08-08T07:33:42.573Z</v>
       </c>
     </row>
     <row r="117">
@@ -4211,7 +4211,7 @@
         <v>Fuzzing with database query snippets (107)</v>
       </c>
       <c r="C117" t="str">
-        <v>sql_fuzz_107_k9s9@test.com</v>
+        <v>sql_fuzz_107_ctfz@test.com</v>
       </c>
       <c r="D117" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4226,13 +4226,13 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="I117" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-03T18:45:50.237Z</v>
+        <v>2026-08-08T07:33:43.421Z</v>
       </c>
     </row>
     <row r="118">
@@ -4258,13 +4258,13 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>816</v>
+        <v>772</v>
       </c>
       <c r="I118" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-03T18:45:51.053Z</v>
+        <v>2026-08-08T07:33:44.193Z</v>
       </c>
     </row>
     <row r="119">
@@ -4290,13 +4290,13 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="I119" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-03T18:45:51.863Z</v>
+        <v>2026-08-08T07:33:45.013Z</v>
       </c>
     </row>
     <row r="120">
@@ -4322,13 +4322,13 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>696</v>
+        <v>811</v>
       </c>
       <c r="I120" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-03T18:45:52.559Z</v>
+        <v>2026-08-08T07:33:45.824Z</v>
       </c>
     </row>
     <row r="121">
@@ -4354,13 +4354,13 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>892</v>
+        <v>1103</v>
       </c>
       <c r="I121" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-03T18:45:53.451Z</v>
+        <v>2026-08-08T07:33:46.927Z</v>
       </c>
     </row>
     <row r="122">
@@ -4386,13 +4386,13 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>558</v>
+        <v>854</v>
       </c>
       <c r="I122" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-03T18:45:54.009Z</v>
+        <v>2026-08-08T07:33:47.781Z</v>
       </c>
     </row>
     <row r="123">
@@ -4403,7 +4403,7 @@
         <v>Fuzzing with database query snippets (113)</v>
       </c>
       <c r="C123" t="str">
-        <v>sql_fuzz_113_2uxz@test.com</v>
+        <v>sql_fuzz_113_cfts@test.com</v>
       </c>
       <c r="D123" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4418,13 +4418,13 @@
         <v>PASS</v>
       </c>
       <c r="H123">
-        <v>838</v>
+        <v>907</v>
       </c>
       <c r="I123" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-03T18:45:54.847Z</v>
+        <v>2026-08-08T07:33:48.688Z</v>
       </c>
     </row>
     <row r="124">
@@ -4450,13 +4450,13 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="I124" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-03T18:45:55.617Z</v>
+        <v>2026-08-08T07:33:49.460Z</v>
       </c>
     </row>
     <row r="125">
@@ -4482,13 +4482,13 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>968</v>
+        <v>804</v>
       </c>
       <c r="I125" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-03T18:45:56.585Z</v>
+        <v>2026-08-08T07:33:50.264Z</v>
       </c>
     </row>
     <row r="126">
@@ -4514,13 +4514,13 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="I126" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-03T18:45:57.317Z</v>
+        <v>2026-08-08T07:33:50.978Z</v>
       </c>
     </row>
     <row r="127">
@@ -4546,13 +4546,13 @@
         <v>PASS</v>
       </c>
       <c r="H127">
-        <v>648</v>
+        <v>927</v>
       </c>
       <c r="I127" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-03T18:45:57.965Z</v>
+        <v>2026-08-08T07:33:51.905Z</v>
       </c>
     </row>
     <row r="128">
@@ -4578,13 +4578,13 @@
         <v>PASS</v>
       </c>
       <c r="H128">
-        <v>553</v>
+        <v>730</v>
       </c>
       <c r="I128" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-03T18:45:58.518Z</v>
+        <v>2026-08-08T07:33:52.635Z</v>
       </c>
     </row>
     <row r="129">
@@ -4595,7 +4595,7 @@
         <v>Fuzzing with database query snippets (119)</v>
       </c>
       <c r="C129" t="str">
-        <v>sql_fuzz_119_za9t@test.com</v>
+        <v>sql_fuzz_119_to4y@test.com</v>
       </c>
       <c r="D129" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4610,13 +4610,13 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>634</v>
+        <v>965</v>
       </c>
       <c r="I129" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-03T18:45:59.152Z</v>
+        <v>2026-08-08T07:33:53.600Z</v>
       </c>
     </row>
     <row r="130">
@@ -4642,13 +4642,13 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>590</v>
+        <v>838</v>
       </c>
       <c r="I130" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-03T18:45:59.742Z</v>
+        <v>2026-08-08T07:33:54.438Z</v>
       </c>
     </row>
     <row r="131">
@@ -4674,13 +4674,13 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="I131" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-03T18:46:00.532Z</v>
+        <v>2026-08-08T07:33:55.202Z</v>
       </c>
     </row>
     <row r="132">
@@ -4706,13 +4706,13 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>740</v>
+        <v>810</v>
       </c>
       <c r="I132" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-03T18:46:01.272Z</v>
+        <v>2026-08-08T07:33:56.013Z</v>
       </c>
     </row>
     <row r="133">
@@ -4744,7 +4744,7 @@
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-03T18:46:02.099Z</v>
+        <v>2026-08-08T07:33:56.839Z</v>
       </c>
     </row>
     <row r="134">
@@ -4770,13 +4770,13 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>586</v>
+        <v>797</v>
       </c>
       <c r="I134" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-03T18:46:02.685Z</v>
+        <v>2026-08-08T07:33:57.636Z</v>
       </c>
     </row>
     <row r="135">
@@ -4787,7 +4787,7 @@
         <v>Fuzzing with database query snippets (125)</v>
       </c>
       <c r="C135" t="str">
-        <v>sql_fuzz_125_7xvo@test.com</v>
+        <v>sql_fuzz_125_7dng@test.com</v>
       </c>
       <c r="D135" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4802,13 +4802,13 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>695</v>
+        <v>964</v>
       </c>
       <c r="I135" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-03T18:46:03.381Z</v>
+        <v>2026-08-08T07:33:58.600Z</v>
       </c>
     </row>
     <row r="136">
@@ -4834,13 +4834,13 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>786</v>
+        <v>853</v>
       </c>
       <c r="I136" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-03T18:46:04.167Z</v>
+        <v>2026-08-08T07:33:59.453Z</v>
       </c>
     </row>
     <row r="137">
@@ -4866,13 +4866,13 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>750</v>
+        <v>1475</v>
       </c>
       <c r="I137" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-03T18:46:04.917Z</v>
+        <v>2026-08-08T07:34:00.928Z</v>
       </c>
     </row>
     <row r="138">
@@ -4898,13 +4898,13 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>491</v>
+        <v>1744</v>
       </c>
       <c r="I138" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-03T18:46:05.408Z</v>
+        <v>2026-08-08T07:34:02.672Z</v>
       </c>
     </row>
     <row r="139">
@@ -4930,13 +4930,13 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>878</v>
+        <v>2005</v>
       </c>
       <c r="I139" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-03T18:46:06.286Z</v>
+        <v>2026-08-08T07:34:04.677Z</v>
       </c>
     </row>
     <row r="140">
@@ -4962,13 +4962,13 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>552</v>
+        <v>1987</v>
       </c>
       <c r="I140" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-03T18:46:06.838Z</v>
+        <v>2026-08-08T07:34:06.664Z</v>
       </c>
     </row>
     <row r="141">
@@ -4979,7 +4979,7 @@
         <v>Fuzzing with database query snippets (131)</v>
       </c>
       <c r="C141" t="str">
-        <v>sql_fuzz_131_6w1f@test.com</v>
+        <v>sql_fuzz_131_r4b1@test.com</v>
       </c>
       <c r="D141" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4994,13 +4994,13 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>934</v>
+        <v>3034</v>
       </c>
       <c r="I141" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-03T18:46:07.772Z</v>
+        <v>2026-08-08T07:34:09.698Z</v>
       </c>
     </row>
     <row r="142">
@@ -5026,13 +5026,13 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>832</v>
+        <v>1934</v>
       </c>
       <c r="I142" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-03T18:46:08.605Z</v>
+        <v>2026-08-08T07:34:11.632Z</v>
       </c>
     </row>
     <row r="143">
@@ -5058,13 +5058,13 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>568</v>
+        <v>2101</v>
       </c>
       <c r="I143" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-03T18:46:09.173Z</v>
+        <v>2026-08-08T07:34:13.733Z</v>
       </c>
     </row>
     <row r="144">
@@ -5090,13 +5090,13 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>947</v>
+        <v>1795</v>
       </c>
       <c r="I144" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-03T18:46:10.120Z</v>
+        <v>2026-08-08T07:34:15.528Z</v>
       </c>
     </row>
     <row r="145">
@@ -5122,13 +5122,13 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>659</v>
+        <v>2755</v>
       </c>
       <c r="I145" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-03T18:46:10.779Z</v>
+        <v>2026-08-08T07:34:18.283Z</v>
       </c>
     </row>
     <row r="146">
@@ -5154,13 +5154,13 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>519</v>
+        <v>2253</v>
       </c>
       <c r="I146" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-03T18:46:11.298Z</v>
+        <v>2026-08-08T07:34:20.536Z</v>
       </c>
     </row>
     <row r="147">
@@ -5171,7 +5171,7 @@
         <v>Fuzzing with database query snippets (137)</v>
       </c>
       <c r="C147" t="str">
-        <v>sql_fuzz_137_zbwe@test.com</v>
+        <v>sql_fuzz_137_z22q@test.com</v>
       </c>
       <c r="D147" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5186,13 +5186,13 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>650</v>
+        <v>2889</v>
       </c>
       <c r="I147" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-03T18:46:11.948Z</v>
+        <v>2026-08-08T07:34:23.425Z</v>
       </c>
     </row>
     <row r="148">
@@ -5218,13 +5218,13 @@
         <v>PASS</v>
       </c>
       <c r="H148">
-        <v>855</v>
+        <v>2091</v>
       </c>
       <c r="I148" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-03T18:46:12.803Z</v>
+        <v>2026-08-08T07:34:25.516Z</v>
       </c>
     </row>
     <row r="149">
@@ -5250,13 +5250,13 @@
         <v>PASS</v>
       </c>
       <c r="H149">
-        <v>716</v>
+        <v>2182</v>
       </c>
       <c r="I149" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-03T18:46:13.519Z</v>
+        <v>2026-08-08T07:34:27.698Z</v>
       </c>
     </row>
     <row r="150">
@@ -5282,13 +5282,13 @@
         <v>PASS</v>
       </c>
       <c r="H150">
-        <v>540</v>
+        <v>1931</v>
       </c>
       <c r="I150" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-03T18:46:14.059Z</v>
+        <v>2026-08-08T07:34:29.629Z</v>
       </c>
     </row>
     <row r="151">
@@ -5314,13 +5314,13 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>878</v>
+        <v>2796</v>
       </c>
       <c r="I151" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-03T18:46:14.937Z</v>
+        <v>2026-08-08T07:34:32.425Z</v>
       </c>
     </row>
     <row r="152">
@@ -5346,13 +5346,13 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>868</v>
+        <v>2387</v>
       </c>
       <c r="I152" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-03T18:46:15.805Z</v>
+        <v>2026-08-08T07:34:34.812Z</v>
       </c>
     </row>
     <row r="153">
@@ -5363,7 +5363,7 @@
         <v>Fuzzing with database query snippets (143)</v>
       </c>
       <c r="C153" t="str">
-        <v>sql_fuzz_143_hdst@test.com</v>
+        <v>sql_fuzz_143_f84o@test.com</v>
       </c>
       <c r="D153" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5378,13 +5378,13 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>711</v>
+        <v>3000</v>
       </c>
       <c r="I153" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-03T18:46:16.516Z</v>
+        <v>2026-08-08T07:34:37.812Z</v>
       </c>
     </row>
     <row r="154">
@@ -5410,13 +5410,13 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>779</v>
+        <v>2282</v>
       </c>
       <c r="I154" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-03T18:46:17.295Z</v>
+        <v>2026-08-08T07:34:40.094Z</v>
       </c>
     </row>
     <row r="155">
@@ -5442,13 +5442,13 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>740</v>
+        <v>2003</v>
       </c>
       <c r="I155" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-03T18:46:18.035Z</v>
+        <v>2026-08-08T07:34:42.097Z</v>
       </c>
     </row>
     <row r="156">
@@ -5474,13 +5474,13 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>503</v>
+        <v>2111</v>
       </c>
       <c r="I156" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-03T18:46:18.538Z</v>
+        <v>2026-08-08T07:34:44.208Z</v>
       </c>
     </row>
     <row r="157">
@@ -5506,13 +5506,13 @@
         <v>PASS</v>
       </c>
       <c r="H157">
-        <v>910</v>
+        <v>2789</v>
       </c>
       <c r="I157" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-03T18:46:19.448Z</v>
+        <v>2026-08-08T07:34:46.997Z</v>
       </c>
     </row>
     <row r="158">
@@ -5538,13 +5538,13 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>787</v>
+        <v>2367</v>
       </c>
       <c r="I158" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-03T18:46:20.235Z</v>
+        <v>2026-08-08T07:34:49.364Z</v>
       </c>
     </row>
     <row r="159">
@@ -5555,7 +5555,7 @@
         <v>Fuzzing with database query snippets (149)</v>
       </c>
       <c r="C159" t="str">
-        <v>sql_fuzz_149_kbpk@test.com</v>
+        <v>sql_fuzz_149_x7x1@test.com</v>
       </c>
       <c r="D159" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5570,13 +5570,13 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>931</v>
+        <v>3032</v>
       </c>
       <c r="I159" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-03T18:46:21.166Z</v>
+        <v>2026-08-08T07:34:52.396Z</v>
       </c>
     </row>
     <row r="160">
@@ -5602,13 +5602,13 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>700</v>
+        <v>2514</v>
       </c>
       <c r="I160" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-03T18:46:21.866Z</v>
+        <v>2026-08-08T07:34:54.910Z</v>
       </c>
     </row>
     <row r="161">
@@ -5634,13 +5634,13 @@
         <v>PASS</v>
       </c>
       <c r="H161">
-        <v>778</v>
+        <v>2009</v>
       </c>
       <c r="I161" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-03T18:46:22.644Z</v>
+        <v>2026-08-08T07:34:56.919Z</v>
       </c>
     </row>
     <row r="162">
@@ -5666,13 +5666,13 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>507</v>
+        <v>2281</v>
       </c>
       <c r="I162" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-03T18:46:23.151Z</v>
+        <v>2026-08-08T07:34:59.200Z</v>
       </c>
     </row>
     <row r="163">
@@ -5698,13 +5698,13 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>599</v>
+        <v>2736</v>
       </c>
       <c r="I163" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-03T18:46:23.750Z</v>
+        <v>2026-08-08T07:35:01.936Z</v>
       </c>
     </row>
     <row r="164">
@@ -5730,13 +5730,13 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>869</v>
+        <v>2257</v>
       </c>
       <c r="I164" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-03T18:46:24.619Z</v>
+        <v>2026-08-08T07:35:04.193Z</v>
       </c>
     </row>
     <row r="165">
@@ -5747,7 +5747,7 @@
         <v>Fuzzing with database query snippets (155)</v>
       </c>
       <c r="C165" t="str">
-        <v>sql_fuzz_155_qrv4@test.com</v>
+        <v>sql_fuzz_155_2rvz@test.com</v>
       </c>
       <c r="D165" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5762,13 +5762,13 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>883</v>
+        <v>3143</v>
       </c>
       <c r="I165" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-03T18:46:25.502Z</v>
+        <v>2026-08-08T07:35:07.336Z</v>
       </c>
     </row>
     <row r="166">
@@ -5794,13 +5794,13 @@
         <v>PASS</v>
       </c>
       <c r="H166">
-        <v>829</v>
+        <v>2363</v>
       </c>
       <c r="I166" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-03T18:46:26.331Z</v>
+        <v>2026-08-08T07:35:09.699Z</v>
       </c>
     </row>
     <row r="167">
@@ -5826,13 +5826,13 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>823</v>
+        <v>2130</v>
       </c>
       <c r="I167" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-03T18:46:27.154Z</v>
+        <v>2026-08-08T07:35:11.829Z</v>
       </c>
     </row>
     <row r="168">
@@ -5858,13 +5858,13 @@
         <v>PASS</v>
       </c>
       <c r="H168">
-        <v>667</v>
+        <v>2252</v>
       </c>
       <c r="I168" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-03T18:46:27.821Z</v>
+        <v>2026-08-08T07:35:14.081Z</v>
       </c>
     </row>
     <row r="169">
@@ -5890,13 +5890,13 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>681</v>
+        <v>3065</v>
       </c>
       <c r="I169" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-03T18:46:28.502Z</v>
+        <v>2026-08-08T07:35:17.146Z</v>
       </c>
     </row>
     <row r="170">
@@ -5922,13 +5922,13 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>580</v>
+        <v>2344</v>
       </c>
       <c r="I170" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-03T18:46:29.082Z</v>
+        <v>2026-08-08T07:35:19.490Z</v>
       </c>
     </row>
     <row r="171">
@@ -5939,7 +5939,7 @@
         <v>Fuzzing with database query snippets (161)</v>
       </c>
       <c r="C171" t="str">
-        <v>sql_fuzz_161_grfr@test.com</v>
+        <v>sql_fuzz_161_u6an@test.com</v>
       </c>
       <c r="D171" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5954,13 +5954,13 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>884</v>
+        <v>3110</v>
       </c>
       <c r="I171" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-03T18:46:29.966Z</v>
+        <v>2026-08-08T07:35:22.601Z</v>
       </c>
     </row>
     <row r="172">
@@ -5986,13 +5986,13 @@
         <v>PASS</v>
       </c>
       <c r="H172">
-        <v>798</v>
+        <v>2438</v>
       </c>
       <c r="I172" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-03T18:46:30.764Z</v>
+        <v>2026-08-08T07:35:25.039Z</v>
       </c>
     </row>
     <row r="173">
@@ -6018,13 +6018,13 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>782</v>
+        <v>2132</v>
       </c>
       <c r="I173" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-03T18:46:31.546Z</v>
+        <v>2026-08-08T07:35:27.171Z</v>
       </c>
     </row>
     <row r="174">
@@ -6050,13 +6050,13 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>972</v>
+        <v>2218</v>
       </c>
       <c r="I174" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-03T18:46:32.518Z</v>
+        <v>2026-08-08T07:35:29.389Z</v>
       </c>
     </row>
     <row r="175">
@@ -6082,13 +6082,13 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>1085</v>
+        <v>2871</v>
       </c>
       <c r="I175" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-03T18:46:33.603Z</v>
+        <v>2026-08-08T07:35:32.260Z</v>
       </c>
     </row>
     <row r="176">
@@ -6114,13 +6114,13 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>831</v>
+        <v>2346</v>
       </c>
       <c r="I176" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-03T18:46:34.434Z</v>
+        <v>2026-08-08T07:35:34.606Z</v>
       </c>
     </row>
     <row r="177">
@@ -6131,7 +6131,7 @@
         <v>Fuzzing with database query snippets (167)</v>
       </c>
       <c r="C177" t="str">
-        <v>sql_fuzz_167_qb3e@test.com</v>
+        <v>sql_fuzz_167_jtm3@test.com</v>
       </c>
       <c r="D177" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6146,13 +6146,13 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>901</v>
+        <v>3080</v>
       </c>
       <c r="I177" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-03T18:46:35.335Z</v>
+        <v>2026-08-08T07:35:37.686Z</v>
       </c>
     </row>
     <row r="178">
@@ -6178,13 +6178,13 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>982</v>
+        <v>2374</v>
       </c>
       <c r="I178" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-03T18:46:36.317Z</v>
+        <v>2026-08-08T07:35:40.061Z</v>
       </c>
     </row>
     <row r="179">
@@ -6210,13 +6210,13 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>983</v>
+        <v>2169</v>
       </c>
       <c r="I179" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-03T18:46:37.300Z</v>
+        <v>2026-08-08T07:35:42.230Z</v>
       </c>
     </row>
     <row r="180">
@@ -6242,13 +6242,13 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>962</v>
+        <v>2224</v>
       </c>
       <c r="I180" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-03T18:46:38.262Z</v>
+        <v>2026-08-08T07:35:44.454Z</v>
       </c>
     </row>
     <row r="181">
@@ -6274,13 +6274,13 @@
         <v>PASS</v>
       </c>
       <c r="H181">
-        <v>888</v>
+        <v>3184</v>
       </c>
       <c r="I181" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-03T18:46:39.150Z</v>
+        <v>2026-08-08T07:35:47.638Z</v>
       </c>
     </row>
     <row r="182">
@@ -6306,13 +6306,13 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>815</v>
+        <v>2287</v>
       </c>
       <c r="I182" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-03T18:46:39.965Z</v>
+        <v>2026-08-08T07:35:49.928Z</v>
       </c>
     </row>
     <row r="183">
@@ -6323,7 +6323,7 @@
         <v>Fuzzing with database query snippets (173)</v>
       </c>
       <c r="C183" t="str">
-        <v>sql_fuzz_173_041q@test.com</v>
+        <v>sql_fuzz_173_mxam@test.com</v>
       </c>
       <c r="D183" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6338,13 +6338,13 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>1038</v>
+        <v>3016</v>
       </c>
       <c r="I183" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-03T18:46:41.003Z</v>
+        <v>2026-08-08T07:35:52.944Z</v>
       </c>
     </row>
     <row r="184">
@@ -6370,13 +6370,13 @@
         <v>PASS</v>
       </c>
       <c r="H184">
-        <v>953</v>
+        <v>2269</v>
       </c>
       <c r="I184" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-03T18:46:41.956Z</v>
+        <v>2026-08-08T07:35:55.213Z</v>
       </c>
     </row>
     <row r="185">
@@ -6402,13 +6402,13 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>914</v>
+        <v>2175</v>
       </c>
       <c r="I185" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-03T18:46:42.870Z</v>
+        <v>2026-08-08T07:35:57.388Z</v>
       </c>
     </row>
     <row r="186">
@@ -6434,13 +6434,13 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>927</v>
+        <v>2089</v>
       </c>
       <c r="I186" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-03T18:46:43.797Z</v>
+        <v>2026-08-08T07:35:59.477Z</v>
       </c>
     </row>
     <row r="187">
@@ -6466,13 +6466,13 @@
         <v>PASS</v>
       </c>
       <c r="H187">
-        <v>1139</v>
+        <v>3336</v>
       </c>
       <c r="I187" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-03T18:46:44.936Z</v>
+        <v>2026-08-08T07:36:02.813Z</v>
       </c>
     </row>
     <row r="188">
@@ -6498,13 +6498,13 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>960</v>
+        <v>2366</v>
       </c>
       <c r="I188" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-03T18:46:45.896Z</v>
+        <v>2026-08-08T07:36:05.179Z</v>
       </c>
     </row>
     <row r="189">
@@ -6515,7 +6515,7 @@
         <v>Fuzzing with database query snippets (179)</v>
       </c>
       <c r="C189" t="str">
-        <v>sql_fuzz_179_epw0@test.com</v>
+        <v>sql_fuzz_179_hjz1@test.com</v>
       </c>
       <c r="D189" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6530,13 +6530,13 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>864</v>
+        <v>2980</v>
       </c>
       <c r="I189" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-03T18:46:46.760Z</v>
+        <v>2026-08-08T07:36:08.159Z</v>
       </c>
     </row>
     <row r="190">
@@ -6562,13 +6562,13 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>685</v>
+        <v>2359</v>
       </c>
       <c r="I190" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-03T18:46:47.445Z</v>
+        <v>2026-08-08T07:36:10.518Z</v>
       </c>
     </row>
     <row r="191">
@@ -6594,13 +6594,13 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>649</v>
+        <v>2201</v>
       </c>
       <c r="I191" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-03T18:46:48.094Z</v>
+        <v>2026-08-08T07:36:12.719Z</v>
       </c>
     </row>
     <row r="192">
@@ -6626,13 +6626,13 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>693</v>
+        <v>2239</v>
       </c>
       <c r="I192" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-03T18:46:48.787Z</v>
+        <v>2026-08-08T07:36:14.959Z</v>
       </c>
     </row>
     <row r="193">
@@ -6658,13 +6658,13 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>876</v>
+        <v>2470</v>
       </c>
       <c r="I193" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-03T18:46:49.663Z</v>
+        <v>2026-08-08T07:36:17.429Z</v>
       </c>
     </row>
     <row r="194">
@@ -6690,13 +6690,13 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>708</v>
+        <v>2305</v>
       </c>
       <c r="I194" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-03T18:46:50.371Z</v>
+        <v>2026-08-08T07:36:19.734Z</v>
       </c>
     </row>
     <row r="195">
@@ -6707,7 +6707,7 @@
         <v>Fuzzing with database query snippets (185)</v>
       </c>
       <c r="C195" t="str">
-        <v>sql_fuzz_185_p8kg@test.com</v>
+        <v>sql_fuzz_185_2l8v@test.com</v>
       </c>
       <c r="D195" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6722,13 +6722,13 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>980</v>
+        <v>3083</v>
       </c>
       <c r="I195" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-03T18:46:51.351Z</v>
+        <v>2026-08-08T07:36:22.817Z</v>
       </c>
     </row>
     <row r="196">
@@ -6754,13 +6754,13 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>962</v>
+        <v>2286</v>
       </c>
       <c r="I196" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-03T18:46:52.313Z</v>
+        <v>2026-08-08T07:36:25.104Z</v>
       </c>
     </row>
     <row r="197">
@@ -6786,13 +6786,13 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>1013</v>
+        <v>2072</v>
       </c>
       <c r="I197" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-03T18:46:53.326Z</v>
+        <v>2026-08-08T07:36:27.176Z</v>
       </c>
     </row>
     <row r="198">
@@ -6818,13 +6818,13 @@
         <v>PASS</v>
       </c>
       <c r="H198">
-        <v>1185</v>
+        <v>2015</v>
       </c>
       <c r="I198" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-03T18:46:54.511Z</v>
+        <v>2026-08-08T07:36:29.191Z</v>
       </c>
     </row>
     <row r="199">
@@ -6850,13 +6850,13 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>1479</v>
+        <v>2256</v>
       </c>
       <c r="I199" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-03T18:46:55.990Z</v>
+        <v>2026-08-08T07:36:31.447Z</v>
       </c>
     </row>
     <row r="200">
@@ -6882,13 +6882,13 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>937</v>
+        <v>790</v>
       </c>
       <c r="I200" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-03T18:46:56.927Z</v>
+        <v>2026-08-08T07:36:32.237Z</v>
       </c>
     </row>
     <row r="201">
@@ -6899,7 +6899,7 @@
         <v>Fuzzing with database query snippets (191)</v>
       </c>
       <c r="C201" t="str">
-        <v>sql_fuzz_191_hlgk@test.com</v>
+        <v>sql_fuzz_191_6f30@test.com</v>
       </c>
       <c r="D201" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6914,13 +6914,13 @@
         <v>PASS</v>
       </c>
       <c r="H201">
-        <v>1154</v>
+        <v>898</v>
       </c>
       <c r="I201" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-03T18:46:58.081Z</v>
+        <v>2026-08-08T07:36:33.135Z</v>
       </c>
     </row>
     <row r="202">
@@ -6946,13 +6946,13 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>1008</v>
+        <v>802</v>
       </c>
       <c r="I202" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-03T18:46:59.089Z</v>
+        <v>2026-08-08T07:36:33.938Z</v>
       </c>
     </row>
     <row r="203">
@@ -6978,13 +6978,13 @@
         <v>PASS</v>
       </c>
       <c r="H203">
-        <v>873</v>
+        <v>929</v>
       </c>
       <c r="I203" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-03T18:46:59.962Z</v>
+        <v>2026-08-08T07:36:34.867Z</v>
       </c>
     </row>
     <row r="204">
@@ -7010,13 +7010,13 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>1081</v>
+        <v>423</v>
       </c>
       <c r="I204" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-03T18:47:01.043Z</v>
+        <v>2026-08-08T07:36:35.290Z</v>
       </c>
     </row>
     <row r="205">
@@ -7042,13 +7042,13 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>974</v>
+        <v>850</v>
       </c>
       <c r="I205" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-03T18:47:02.017Z</v>
+        <v>2026-08-08T07:36:36.140Z</v>
       </c>
     </row>
     <row r="206">
@@ -7074,13 +7074,13 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>947</v>
+        <v>743</v>
       </c>
       <c r="I206" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-03T18:47:02.964Z</v>
+        <v>2026-08-08T07:36:36.883Z</v>
       </c>
     </row>
     <row r="207">
@@ -7091,7 +7091,7 @@
         <v>Fuzzing with database query snippets (197)</v>
       </c>
       <c r="C207" t="str">
-        <v>sql_fuzz_197_ixa1@test.com</v>
+        <v>sql_fuzz_197_zj3z@test.com</v>
       </c>
       <c r="D207" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7106,13 +7106,13 @@
         <v>PASS</v>
       </c>
       <c r="H207">
-        <v>1163</v>
+        <v>822</v>
       </c>
       <c r="I207" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-03T18:47:04.127Z</v>
+        <v>2026-08-08T07:36:37.705Z</v>
       </c>
     </row>
     <row r="208">
@@ -7138,13 +7138,13 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>999</v>
+        <v>852</v>
       </c>
       <c r="I208" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-03T18:47:05.127Z</v>
+        <v>2026-08-08T07:36:38.557Z</v>
       </c>
     </row>
     <row r="209">
@@ -7170,13 +7170,13 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>905</v>
+        <v>788</v>
       </c>
       <c r="I209" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-03T18:47:06.032Z</v>
+        <v>2026-08-08T07:36:39.345Z</v>
       </c>
     </row>
     <row r="210">
@@ -7202,13 +7202,13 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>624</v>
+        <v>698</v>
       </c>
       <c r="I210" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-03T18:47:06.656Z</v>
+        <v>2026-08-08T07:36:40.043Z</v>
       </c>
     </row>
     <row r="211">
@@ -7234,13 +7234,13 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>864</v>
+        <v>806</v>
       </c>
       <c r="I211" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-03T18:47:07.520Z</v>
+        <v>2026-08-08T07:36:40.849Z</v>
       </c>
     </row>
     <row r="212">
@@ -7266,13 +7266,13 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>782</v>
+        <v>753</v>
       </c>
       <c r="I212" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-03T18:47:08.302Z</v>
+        <v>2026-08-08T07:36:41.602Z</v>
       </c>
     </row>
     <row r="213">
@@ -7283,7 +7283,7 @@
         <v>Fuzzing with database query snippets (203)</v>
       </c>
       <c r="C213" t="str">
-        <v>sql_fuzz_203_xe1x@test.com</v>
+        <v>sql_fuzz_203_v9as@test.com</v>
       </c>
       <c r="D213" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7298,13 +7298,13 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>808</v>
+        <v>854</v>
       </c>
       <c r="I213" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-03T18:47:09.110Z</v>
+        <v>2026-08-08T07:36:42.456Z</v>
       </c>
     </row>
     <row r="214">
@@ -7330,13 +7330,13 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>926</v>
+        <v>730</v>
       </c>
       <c r="I214" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-03T18:47:10.036Z</v>
+        <v>2026-08-08T07:36:43.186Z</v>
       </c>
     </row>
     <row r="215">
@@ -7362,13 +7362,13 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>811</v>
+        <v>984</v>
       </c>
       <c r="I215" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-03T18:47:10.847Z</v>
+        <v>2026-08-08T07:36:44.170Z</v>
       </c>
     </row>
     <row r="216">
@@ -7394,13 +7394,13 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>808</v>
+        <v>715</v>
       </c>
       <c r="I216" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-03T18:47:11.655Z</v>
+        <v>2026-08-08T07:36:44.885Z</v>
       </c>
     </row>
     <row r="217">
@@ -7426,13 +7426,13 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>674</v>
+        <v>800</v>
       </c>
       <c r="I217" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-03T18:47:12.329Z</v>
+        <v>2026-08-08T07:36:45.685Z</v>
       </c>
     </row>
     <row r="218">
@@ -7458,13 +7458,13 @@
         <v>PASS</v>
       </c>
       <c r="H218">
-        <v>570</v>
+        <v>816</v>
       </c>
       <c r="I218" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-03T18:47:12.899Z</v>
+        <v>2026-08-08T07:36:46.501Z</v>
       </c>
     </row>
     <row r="219">
@@ -7475,7 +7475,7 @@
         <v>Fuzzing with database query snippets (209)</v>
       </c>
       <c r="C219" t="str">
-        <v>sql_fuzz_209_nv4m@test.com</v>
+        <v>sql_fuzz_209_ocyt@test.com</v>
       </c>
       <c r="D219" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7490,13 +7490,13 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>907</v>
+        <v>811</v>
       </c>
       <c r="I219" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-03T18:47:13.806Z</v>
+        <v>2026-08-08T07:36:47.312Z</v>
       </c>
     </row>
     <row r="220">
@@ -7522,13 +7522,13 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="I220" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-03T18:47:14.591Z</v>
+        <v>2026-08-08T07:36:48.069Z</v>
       </c>
     </row>
     <row r="221">
@@ -7554,13 +7554,13 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>809</v>
+        <v>731</v>
       </c>
       <c r="I221" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-03T18:47:15.401Z</v>
+        <v>2026-08-08T07:36:48.800Z</v>
       </c>
     </row>
     <row r="222">
@@ -7586,13 +7586,13 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>744</v>
+        <v>900</v>
       </c>
       <c r="I222" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-03T18:47:16.145Z</v>
+        <v>2026-08-08T07:36:49.700Z</v>
       </c>
     </row>
     <row r="223">
@@ -7618,13 +7618,13 @@
         <v>PASS</v>
       </c>
       <c r="H223">
-        <v>888</v>
+        <v>834</v>
       </c>
       <c r="I223" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-03T18:47:17.033Z</v>
+        <v>2026-08-08T07:36:50.534Z</v>
       </c>
     </row>
     <row r="224">
@@ -7650,13 +7650,13 @@
         <v>PASS</v>
       </c>
       <c r="H224">
-        <v>815</v>
+        <v>769</v>
       </c>
       <c r="I224" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-03T18:47:17.848Z</v>
+        <v>2026-08-08T07:36:51.303Z</v>
       </c>
     </row>
     <row r="225">
@@ -7667,7 +7667,7 @@
         <v>Fuzzing with database query snippets (215)</v>
       </c>
       <c r="C225" t="str">
-        <v>sql_fuzz_215_6ktq@test.com</v>
+        <v>sql_fuzz_215_0wec@test.com</v>
       </c>
       <c r="D225" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7682,13 +7682,13 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>919</v>
+        <v>887</v>
       </c>
       <c r="I225" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-03T18:47:18.767Z</v>
+        <v>2026-08-08T07:36:52.190Z</v>
       </c>
     </row>
     <row r="226">
@@ -7714,13 +7714,13 @@
         <v>PASS</v>
       </c>
       <c r="H226">
-        <v>869</v>
+        <v>760</v>
       </c>
       <c r="I226" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-03T18:47:19.636Z</v>
+        <v>2026-08-08T07:36:52.950Z</v>
       </c>
     </row>
     <row r="227">
@@ -7746,13 +7746,13 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>757</v>
+        <v>715</v>
       </c>
       <c r="I227" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-03T18:47:20.393Z</v>
+        <v>2026-08-08T07:36:53.665Z</v>
       </c>
     </row>
     <row r="228">
@@ -7778,13 +7778,13 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>534</v>
+        <v>740</v>
       </c>
       <c r="I228" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-03T18:47:20.927Z</v>
+        <v>2026-08-08T07:36:54.405Z</v>
       </c>
     </row>
     <row r="229">
@@ -7810,13 +7810,13 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>598</v>
+        <v>1060</v>
       </c>
       <c r="I229" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-03T18:47:21.525Z</v>
+        <v>2026-08-08T07:36:55.465Z</v>
       </c>
     </row>
     <row r="230">
@@ -7842,13 +7842,13 @@
         <v>PASS</v>
       </c>
       <c r="H230">
-        <v>574</v>
+        <v>763</v>
       </c>
       <c r="I230" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-03T18:47:22.099Z</v>
+        <v>2026-08-08T07:36:56.228Z</v>
       </c>
     </row>
     <row r="231">
@@ -7859,7 +7859,7 @@
         <v>Fuzzing with database query snippets (221)</v>
       </c>
       <c r="C231" t="str">
-        <v>sql_fuzz_221_49lo@test.com</v>
+        <v>sql_fuzz_221_ugcu@test.com</v>
       </c>
       <c r="D231" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7874,13 +7874,13 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>921</v>
+        <v>769</v>
       </c>
       <c r="I231" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-03T18:47:23.020Z</v>
+        <v>2026-08-08T07:36:56.997Z</v>
       </c>
     </row>
     <row r="232">
@@ -7906,13 +7906,13 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>793</v>
+        <v>750</v>
       </c>
       <c r="I232" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-03T18:47:23.813Z</v>
+        <v>2026-08-08T07:36:57.747Z</v>
       </c>
     </row>
     <row r="233">
@@ -7938,13 +7938,13 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>568</v>
+        <v>705</v>
       </c>
       <c r="I233" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-03T18:47:24.381Z</v>
+        <v>2026-08-08T07:36:58.452Z</v>
       </c>
     </row>
     <row r="234">
@@ -7970,13 +7970,13 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>547</v>
+        <v>692</v>
       </c>
       <c r="I234" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-03T18:47:24.928Z</v>
+        <v>2026-08-08T07:36:59.144Z</v>
       </c>
     </row>
     <row r="235">
@@ -8002,13 +8002,13 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>936</v>
+        <v>910</v>
       </c>
       <c r="I235" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-03T18:47:25.864Z</v>
+        <v>2026-08-08T07:37:00.054Z</v>
       </c>
     </row>
     <row r="236">
@@ -8034,13 +8034,13 @@
         <v>PASS</v>
       </c>
       <c r="H236">
-        <v>547</v>
+        <v>812</v>
       </c>
       <c r="I236" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-03T18:47:26.411Z</v>
+        <v>2026-08-08T07:37:00.866Z</v>
       </c>
     </row>
     <row r="237">
@@ -8051,7 +8051,7 @@
         <v>Fuzzing with database query snippets (227)</v>
       </c>
       <c r="C237" t="str">
-        <v>sql_fuzz_227_wla1@test.com</v>
+        <v>sql_fuzz_227_4ej7@test.com</v>
       </c>
       <c r="D237" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8066,13 +8066,13 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>921</v>
+        <v>882</v>
       </c>
       <c r="I237" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-03T18:47:27.332Z</v>
+        <v>2026-08-08T07:37:01.748Z</v>
       </c>
     </row>
     <row r="238">
@@ -8098,13 +8098,13 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>618</v>
+        <v>592</v>
       </c>
       <c r="I238" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-03T18:47:27.950Z</v>
+        <v>2026-08-08T07:37:02.340Z</v>
       </c>
     </row>
     <row r="239">
@@ -8130,13 +8130,13 @@
         <v>PASS</v>
       </c>
       <c r="H239">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="I239" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-03T18:47:28.717Z</v>
+        <v>2026-08-08T07:37:03.088Z</v>
       </c>
     </row>
     <row r="240">
@@ -8162,13 +8162,13 @@
         <v>PASS</v>
       </c>
       <c r="H240">
-        <v>772</v>
+        <v>688</v>
       </c>
       <c r="I240" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-03T18:47:29.489Z</v>
+        <v>2026-08-08T07:37:03.776Z</v>
       </c>
     </row>
     <row r="241">
@@ -8194,13 +8194,13 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="I241" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-03T18:47:30.332Z</v>
+        <v>2026-08-08T07:37:04.578Z</v>
       </c>
     </row>
     <row r="242">
@@ -8226,13 +8226,13 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>849</v>
+        <v>772</v>
       </c>
       <c r="I242" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-03T18:47:31.181Z</v>
+        <v>2026-08-08T07:37:05.350Z</v>
       </c>
     </row>
     <row r="243">
@@ -8243,7 +8243,7 @@
         <v>Fuzzing with database query snippets (233)</v>
       </c>
       <c r="C243" t="str">
-        <v>sql_fuzz_233_eqjg@test.com</v>
+        <v>sql_fuzz_233_i8c4@test.com</v>
       </c>
       <c r="D243" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8258,13 +8258,13 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>691</v>
+        <v>820</v>
       </c>
       <c r="I243" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-03T18:47:31.872Z</v>
+        <v>2026-08-08T07:37:06.170Z</v>
       </c>
     </row>
     <row r="244">
@@ -8290,13 +8290,13 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>773</v>
+        <v>839</v>
       </c>
       <c r="I244" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-03T18:47:32.645Z</v>
+        <v>2026-08-08T07:37:07.009Z</v>
       </c>
     </row>
     <row r="245">
@@ -8322,13 +8322,13 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>717</v>
+        <v>826</v>
       </c>
       <c r="I245" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-03T18:47:33.362Z</v>
+        <v>2026-08-08T07:37:07.835Z</v>
       </c>
     </row>
     <row r="246">
@@ -8354,13 +8354,13 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>721</v>
+        <v>912</v>
       </c>
       <c r="I246" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-03T18:47:34.083Z</v>
+        <v>2026-08-08T07:37:08.747Z</v>
       </c>
     </row>
     <row r="247">
@@ -8386,13 +8386,13 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>662</v>
+        <v>864</v>
       </c>
       <c r="I247" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-03T18:47:34.745Z</v>
+        <v>2026-08-08T07:37:09.611Z</v>
       </c>
     </row>
     <row r="248">
@@ -8418,13 +8418,13 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>889</v>
+        <v>742</v>
       </c>
       <c r="I248" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-03T18:47:35.634Z</v>
+        <v>2026-08-08T07:37:10.353Z</v>
       </c>
     </row>
     <row r="249">
@@ -8435,7 +8435,7 @@
         <v>Fuzzing with database query snippets (239)</v>
       </c>
       <c r="C249" t="str">
-        <v>sql_fuzz_239_428a@test.com</v>
+        <v>sql_fuzz_239_f2ca@test.com</v>
       </c>
       <c r="D249" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8450,13 +8450,13 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>1038</v>
+        <v>911</v>
       </c>
       <c r="I249" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-03T18:47:36.672Z</v>
+        <v>2026-08-08T07:37:11.264Z</v>
       </c>
     </row>
     <row r="250">
@@ -8482,13 +8482,13 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>919</v>
+        <v>804</v>
       </c>
       <c r="I250" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-03T18:47:37.591Z</v>
+        <v>2026-08-08T07:37:12.068Z</v>
       </c>
     </row>
     <row r="251">
@@ -8514,13 +8514,13 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>841</v>
+        <v>767</v>
       </c>
       <c r="I251" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-03T18:47:38.432Z</v>
+        <v>2026-08-08T07:37:12.835Z</v>
       </c>
     </row>
     <row r="252">
@@ -8546,13 +8546,13 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>831</v>
+        <v>734</v>
       </c>
       <c r="I252" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-03T18:47:39.263Z</v>
+        <v>2026-08-08T07:37:13.569Z</v>
       </c>
     </row>
     <row r="253">
@@ -8578,13 +8578,13 @@
         <v>PASS</v>
       </c>
       <c r="H253">
-        <v>651</v>
+        <v>932</v>
       </c>
       <c r="I253" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-03T18:47:39.914Z</v>
+        <v>2026-08-08T07:37:14.501Z</v>
       </c>
     </row>
     <row r="254">
@@ -8610,13 +8610,13 @@
         <v>PASS</v>
       </c>
       <c r="H254">
-        <v>571</v>
+        <v>849</v>
       </c>
       <c r="I254" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-03T18:47:40.485Z</v>
+        <v>2026-08-08T07:37:15.350Z</v>
       </c>
     </row>
     <row r="255">
@@ -8627,7 +8627,7 @@
         <v>Fuzzing with database query snippets (245)</v>
       </c>
       <c r="C255" t="str">
-        <v>sql_fuzz_245_tdne@test.com</v>
+        <v>sql_fuzz_245_0cix@test.com</v>
       </c>
       <c r="D255" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8642,13 +8642,13 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="I255" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-03T18:47:41.343Z</v>
+        <v>2026-08-08T07:37:16.222Z</v>
       </c>
     </row>
     <row r="256">
@@ -8674,13 +8674,13 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>1018</v>
+        <v>822</v>
       </c>
       <c r="I256" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-03T18:47:42.361Z</v>
+        <v>2026-08-08T07:37:17.044Z</v>
       </c>
     </row>
     <row r="257">
@@ -8706,13 +8706,13 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>521</v>
+        <v>755</v>
       </c>
       <c r="I257" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-03T18:47:42.882Z</v>
+        <v>2026-08-08T07:37:17.799Z</v>
       </c>
     </row>
     <row r="258">
@@ -8738,13 +8738,13 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>1006</v>
+        <v>769</v>
       </c>
       <c r="I258" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-03T18:47:43.888Z</v>
+        <v>2026-08-08T07:37:18.568Z</v>
       </c>
     </row>
     <row r="259">
@@ -8770,13 +8770,13 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>648</v>
+        <v>915</v>
       </c>
       <c r="I259" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-03T18:47:44.536Z</v>
+        <v>2026-08-08T07:37:19.483Z</v>
       </c>
     </row>
     <row r="260">
@@ -8802,13 +8802,13 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>530</v>
+        <v>768</v>
       </c>
       <c r="I260" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-03T18:47:45.066Z</v>
+        <v>2026-08-08T07:37:20.251Z</v>
       </c>
     </row>
     <row r="261">
@@ -8819,7 +8819,7 @@
         <v>Fuzzing with database query snippets (251)</v>
       </c>
       <c r="C261" t="str">
-        <v>sql_fuzz_251_8qub@test.com</v>
+        <v>sql_fuzz_251_xqim@test.com</v>
       </c>
       <c r="D261" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8834,13 +8834,13 @@
         <v>PASS</v>
       </c>
       <c r="H261">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="I261" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-03T18:47:45.966Z</v>
+        <v>2026-08-08T07:37:21.166Z</v>
       </c>
     </row>
     <row r="262">
@@ -8866,13 +8866,13 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>801</v>
+        <v>819</v>
       </c>
       <c r="I262" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-03T18:47:46.767Z</v>
+        <v>2026-08-08T07:37:21.985Z</v>
       </c>
     </row>
     <row r="263">
@@ -8898,13 +8898,13 @@
         <v>PASS</v>
       </c>
       <c r="H263">
-        <v>711</v>
+        <v>766</v>
       </c>
       <c r="I263" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-03T18:47:47.478Z</v>
+        <v>2026-08-08T07:37:22.751Z</v>
       </c>
     </row>
     <row r="264">
@@ -8930,13 +8930,13 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>486</v>
+        <v>762</v>
       </c>
       <c r="I264" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-03T18:47:47.964Z</v>
+        <v>2026-08-08T07:37:23.513Z</v>
       </c>
     </row>
     <row r="265">
@@ -8962,13 +8962,13 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>840</v>
+        <v>959</v>
       </c>
       <c r="I265" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-03T18:47:48.804Z</v>
+        <v>2026-08-08T07:37:24.472Z</v>
       </c>
     </row>
     <row r="266">
@@ -8994,13 +8994,13 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>612</v>
+        <v>798</v>
       </c>
       <c r="I266" t="str">
         <v>Too many requests from this IP, please try again later.</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-03T18:47:49.416Z</v>
+        <v>2026-08-08T07:37:25.270Z</v>
       </c>
     </row>
     <row r="267">
@@ -9011,7 +9011,7 @@
         <v>Fuzzing with database query snippets (257)</v>
       </c>
       <c r="C267" t="str">
-        <v>sql_fuzz_257_x7yk@test.com</v>
+        <v>sql_fuzz_257_9k0b@test.com</v>
       </c>
       <c r="D267" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9026,16 +9026,16 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>876</v>
+        <v>3245</v>
       </c>
       <c r="I267" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Failed to fetch</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-03T18:47:50.292Z</v>
-      </c>
-    </row>
-    <row r="268">
+        <v>2026-08-08T07:37:28.515Z</v>
+      </c>
+    </row>
+    <row r="268" xml:space="preserve">
       <c r="A268" t="str">
         <v>TC-GEN-1258</v>
       </c>
@@ -9058,13 +9058,14 @@
         <v>PASS</v>
       </c>
       <c r="H268">
-        <v>788</v>
-      </c>
-      <c r="I268" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>2318</v>
+      </c>
+      <c r="I268" t="str" xml:space="preserve">
+        <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
+  (Session info: chrome=151.0.7922.77)</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-03T18:47:51.080Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="269">
@@ -9090,13 +9091,13 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-03T18:47:52.038Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="270">
@@ -9122,13 +9123,13 @@
         <v>PASS</v>
       </c>
       <c r="H270">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="I270" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-03T18:47:52.579Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="271">
@@ -9154,13 +9155,13 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="I271" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-03T18:47:53.480Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="272">
@@ -9186,13 +9187,13 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-03T18:47:54.014Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="273">
@@ -9203,7 +9204,7 @@
         <v>Fuzzing with database query snippets (263)</v>
       </c>
       <c r="C273" t="str">
-        <v>sql_fuzz_263_6s6p@test.com</v>
+        <v>sql_fuzz_263_gfrj@test.com</v>
       </c>
       <c r="D273" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9218,13 +9219,13 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>886</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-03T18:47:54.900Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="274">
@@ -9250,13 +9251,13 @@
         <v>PASS</v>
       </c>
       <c r="H274">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="I274" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-03T18:47:55.696Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="275">
@@ -9282,13 +9283,13 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-03T18:47:56.626Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="276">
@@ -9314,13 +9315,13 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="I276" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-03T18:47:57.374Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="277">
@@ -9346,13 +9347,13 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-03T18:47:58.217Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="278">
@@ -9378,13 +9379,13 @@
         <v>PASS</v>
       </c>
       <c r="H278">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="I278" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-03T18:47:58.781Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="279">
@@ -9395,7 +9396,7 @@
         <v>Fuzzing with database query snippets (269)</v>
       </c>
       <c r="C279" t="str">
-        <v>sql_fuzz_269_jyek@test.com</v>
+        <v>sql_fuzz_269_tm5e@test.com</v>
       </c>
       <c r="D279" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9410,13 +9411,13 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-03T18:47:59.488Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="280">
@@ -9442,13 +9443,13 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="I280" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-03T18:48:00.294Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="281">
@@ -9474,13 +9475,13 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="I281" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-03T18:48:01.317Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="282">
@@ -9506,13 +9507,13 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="I282" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-03T18:48:02.238Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="283">
@@ -9538,13 +9539,13 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>1029</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-03T18:48:03.267Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="284">
@@ -9570,13 +9571,13 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I284" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-03T18:48:04.167Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="285">
@@ -9587,7 +9588,7 @@
         <v>Fuzzing with database query snippets (275)</v>
       </c>
       <c r="C285" t="str">
-        <v>sql_fuzz_275_gwos@test.com</v>
+        <v>sql_fuzz_275_qvn2@test.com</v>
       </c>
       <c r="D285" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9602,13 +9603,13 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-03T18:48:05.249Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="286">
@@ -9634,13 +9635,13 @@
         <v>PASS</v>
       </c>
       <c r="H286">
-        <v>712</v>
+        <v>0</v>
       </c>
       <c r="I286" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-03T18:48:05.961Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="287">
@@ -9666,13 +9667,13 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-03T18:48:06.909Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="288">
@@ -9698,13 +9699,13 @@
         <v>PASS</v>
       </c>
       <c r="H288">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="I288" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-03T18:48:07.552Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="289">
@@ -9730,13 +9731,13 @@
         <v>PASS</v>
       </c>
       <c r="H289">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="I289" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-03T18:48:08.626Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="290">
@@ -9762,13 +9763,13 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="I290" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-03T18:48:09.692Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="291">
@@ -9779,7 +9780,7 @@
         <v>Fuzzing with database query snippets (281)</v>
       </c>
       <c r="C291" t="str">
-        <v>sql_fuzz_281_4oz1@test.com</v>
+        <v>sql_fuzz_281_l56n@test.com</v>
       </c>
       <c r="D291" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9794,13 +9795,13 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>1089</v>
+        <v>0</v>
       </c>
       <c r="I291" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-03T18:48:10.781Z</v>
+        <v>2026-08-08T07:37:30.833Z</v>
       </c>
     </row>
     <row r="292">
@@ -9826,13 +9827,13 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-03T18:48:11.784Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="293">
@@ -9858,13 +9859,13 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="I293" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-03T18:48:12.515Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="294">
@@ -9890,13 +9891,13 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>1136</v>
+        <v>0</v>
       </c>
       <c r="I294" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-03T18:48:13.651Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="295">
@@ -9922,13 +9923,13 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>1394</v>
+        <v>0</v>
       </c>
       <c r="I295" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-03T18:48:15.045Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="296">
@@ -9954,13 +9955,13 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-03T18:48:16.075Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="297">
@@ -9971,7 +9972,7 @@
         <v>Fuzzing with database query snippets (287)</v>
       </c>
       <c r="C297" t="str">
-        <v>sql_fuzz_287_4cko@test.com</v>
+        <v>sql_fuzz_287_n26b@test.com</v>
       </c>
       <c r="D297" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9986,13 +9987,13 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="I297" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-03T18:48:17.305Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="298">
@@ -10018,13 +10019,13 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-03T18:48:18.248Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="299">
@@ -10050,13 +10051,13 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="I299" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-03T18:48:19.137Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="300">
@@ -10082,13 +10083,13 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>997</v>
+        <v>0</v>
       </c>
       <c r="I300" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-03T18:48:20.134Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="301">
@@ -10114,13 +10115,13 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="I301" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-03T18:48:21.484Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="302">
@@ -10146,13 +10147,13 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="I302" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-03T18:48:22.459Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="303">
@@ -10163,7 +10164,7 @@
         <v>Fuzzing with database query snippets (293)</v>
       </c>
       <c r="C303" t="str">
-        <v>sql_fuzz_293_77ge@test.com</v>
+        <v>sql_fuzz_293_ib0m@test.com</v>
       </c>
       <c r="D303" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10178,13 +10179,13 @@
         <v>PASS</v>
       </c>
       <c r="H303">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="I303" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-03T18:48:23.380Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="304">
@@ -10210,13 +10211,13 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>799</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-03T18:48:24.179Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="305">
@@ -10242,13 +10243,13 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-03T18:48:24.879Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="306">
@@ -10274,13 +10275,13 @@
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>805</v>
+        <v>0</v>
       </c>
       <c r="I306" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-03T18:48:25.684Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="307">
@@ -10306,13 +10307,13 @@
         <v>PASS</v>
       </c>
       <c r="H307">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="I307" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-03T18:48:26.606Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="308">
@@ -10338,13 +10339,13 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="I308" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-03T18:48:27.196Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="309">
@@ -10355,7 +10356,7 @@
         <v>Fuzzing with database query snippets (299)</v>
       </c>
       <c r="C309" t="str">
-        <v>sql_fuzz_299_2s4r@test.com</v>
+        <v>sql_fuzz_299_u2sk@test.com</v>
       </c>
       <c r="D309" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10370,13 +10371,13 @@
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-03T18:48:27.941Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="310">
@@ -10402,13 +10403,13 @@
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="I310" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-03T18:48:28.973Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="311">
@@ -10434,13 +10435,13 @@
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-03T18:48:29.512Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="312">
@@ -10466,13 +10467,13 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>488</v>
+        <v>0</v>
       </c>
       <c r="I312" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-03T18:48:30.000Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="313">
@@ -10498,13 +10499,13 @@
         <v>PASS</v>
       </c>
       <c r="H313">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-03T18:48:30.883Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="314">
@@ -10530,13 +10531,13 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="I314" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-03T18:48:31.457Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="315">
@@ -10547,7 +10548,7 @@
         <v>Fuzzing with database query snippets (305)</v>
       </c>
       <c r="C315" t="str">
-        <v>sql_fuzz_305_447c@test.com</v>
+        <v>sql_fuzz_305_cqz7@test.com</v>
       </c>
       <c r="D315" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10562,13 +10563,13 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-03T18:48:32.425Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="316">
@@ -10594,13 +10595,13 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="I316" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-03T18:48:33.241Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="317">
@@ -10626,13 +10627,13 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-03T18:48:33.989Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="318">
@@ -10658,13 +10659,13 @@
         <v>PASS</v>
       </c>
       <c r="H318">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I318" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-03T18:48:34.769Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="319">
@@ -10690,13 +10691,13 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>1098</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-03T18:48:35.867Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="320">
@@ -10722,13 +10723,13 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>1005</v>
+        <v>0</v>
       </c>
       <c r="I320" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-03T18:48:36.872Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="321">
@@ -10739,7 +10740,7 @@
         <v>Fuzzing with database query snippets (311)</v>
       </c>
       <c r="C321" t="str">
-        <v>sql_fuzz_311_74sg@test.com</v>
+        <v>sql_fuzz_311_tbfx@test.com</v>
       </c>
       <c r="D321" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10754,13 +10755,13 @@
         <v>PASS</v>
       </c>
       <c r="H321">
-        <v>828</v>
+        <v>0</v>
       </c>
       <c r="I321" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-03T18:48:37.700Z</v>
+        <v>2026-08-08T07:37:30.834Z</v>
       </c>
     </row>
     <row r="322">
@@ -10786,13 +10787,13 @@
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="I322" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-03T18:48:38.529Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="323">
@@ -10818,13 +10819,13 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="I323" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-03T18:48:39.281Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="324">
@@ -10850,13 +10851,13 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>784</v>
+        <v>0</v>
       </c>
       <c r="I324" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-03T18:48:40.065Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="325">
@@ -10882,13 +10883,13 @@
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>1513</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-03T18:48:41.578Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="326">
@@ -10914,13 +10915,13 @@
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="I326" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-03T18:48:42.411Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="327">
@@ -10931,7 +10932,7 @@
         <v>Fuzzing with database query snippets (317)</v>
       </c>
       <c r="C327" t="str">
-        <v>sql_fuzz_317_l62x@test.com</v>
+        <v>sql_fuzz_317_vh8t@test.com</v>
       </c>
       <c r="D327" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10946,13 +10947,13 @@
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-03T18:48:43.318Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="328">
@@ -10978,13 +10979,13 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="I328" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-03T18:48:43.954Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="329">
@@ -11010,13 +11011,13 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="I329" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-03T18:48:44.741Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="330">
@@ -11042,13 +11043,13 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="I330" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-03T18:48:45.600Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="331">
@@ -11074,13 +11075,13 @@
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="I331" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-03T18:48:46.335Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="332">
@@ -11106,13 +11107,13 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="I332" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-03T18:48:47.068Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="333">
@@ -11123,7 +11124,7 @@
         <v>Fuzzing with database query snippets (323)</v>
       </c>
       <c r="C333" t="str">
-        <v>sql_fuzz_323_y0lm@test.com</v>
+        <v>sql_fuzz_323_fi1m@test.com</v>
       </c>
       <c r="D333" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11138,13 +11139,13 @@
         <v>PASS</v>
       </c>
       <c r="H333">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="I333" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-03T18:48:48.046Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="334">
@@ -11170,13 +11171,13 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="I334" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-03T18:48:48.741Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="335">
@@ -11202,13 +11203,13 @@
         <v>PASS</v>
       </c>
       <c r="H335">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="I335" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-03T18:48:49.413Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="336">
@@ -11234,13 +11235,13 @@
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>769</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-03T18:48:50.182Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="337">
@@ -11266,13 +11267,13 @@
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-03T18:48:51.065Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="338">
@@ -11298,13 +11299,13 @@
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>1048</v>
+        <v>0</v>
       </c>
       <c r="I338" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-03T18:48:52.113Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="339">
@@ -11315,7 +11316,7 @@
         <v>Fuzzing with database query snippets (329)</v>
       </c>
       <c r="C339" t="str">
-        <v>sql_fuzz_329_tmer@test.com</v>
+        <v>sql_fuzz_329_1rig@test.com</v>
       </c>
       <c r="D339" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11330,13 +11331,13 @@
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="I339" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-03T18:48:53.264Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="340">
@@ -11362,13 +11363,13 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="I340" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-03T18:48:54.270Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="341">
@@ -11394,13 +11395,13 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="I341" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-03T18:48:55.191Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="342">
@@ -11426,13 +11427,13 @@
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="I342" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-03T18:48:56.213Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="343">
@@ -11458,13 +11459,13 @@
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-03T18:48:57.278Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="344">
@@ -11490,13 +11491,13 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>988</v>
+        <v>0</v>
       </c>
       <c r="I344" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-03T18:48:58.266Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="345">
@@ -11507,7 +11508,7 @@
         <v>Fuzzing with database query snippets (335)</v>
       </c>
       <c r="C345" t="str">
-        <v>sql_fuzz_335_b9r1@test.com</v>
+        <v>sql_fuzz_335_t6rv@test.com</v>
       </c>
       <c r="D345" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11522,13 +11523,13 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>1052</v>
+        <v>0</v>
       </c>
       <c r="I345" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-03T18:48:59.318Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="346">
@@ -11554,13 +11555,13 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="I346" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-03T18:49:00.248Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="347">
@@ -11586,13 +11587,13 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>903</v>
+        <v>0</v>
       </c>
       <c r="I347" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-03T18:49:01.151Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="348">
@@ -11618,13 +11619,13 @@
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="I348" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-03T18:49:01.882Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="349">
@@ -11650,13 +11651,13 @@
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>1123</v>
+        <v>0</v>
       </c>
       <c r="I349" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-03T18:49:03.005Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="350">
@@ -11682,13 +11683,13 @@
         <v>PASS</v>
       </c>
       <c r="H350">
-        <v>916</v>
+        <v>0</v>
       </c>
       <c r="I350" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-03T18:49:03.921Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="351">
@@ -11699,7 +11700,7 @@
         <v>Fuzzing with database query snippets (341)</v>
       </c>
       <c r="C351" t="str">
-        <v>sql_fuzz_341_mkx5@test.com</v>
+        <v>sql_fuzz_341_cw35@test.com</v>
       </c>
       <c r="D351" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11714,13 +11715,13 @@
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="I351" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-03T18:49:04.911Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="352">
@@ -11746,13 +11747,13 @@
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="I352" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-03T18:49:05.806Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="353">
@@ -11778,13 +11779,13 @@
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="I353" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-03T18:49:06.424Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="354">
@@ -11810,13 +11811,13 @@
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="I354" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-03T18:49:07.241Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="355">
@@ -11842,13 +11843,13 @@
         <v>PASS</v>
       </c>
       <c r="H355">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="I355" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-03T18:49:08.276Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="356">
@@ -11874,13 +11875,13 @@
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>913</v>
+        <v>0</v>
       </c>
       <c r="I356" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-03T18:49:09.189Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="357">
@@ -11891,7 +11892,7 @@
         <v>Fuzzing with database query snippets (347)</v>
       </c>
       <c r="C357" t="str">
-        <v>sql_fuzz_347_odx2@test.com</v>
+        <v>sql_fuzz_347_09le@test.com</v>
       </c>
       <c r="D357" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11906,13 +11907,13 @@
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>1052</v>
+        <v>0</v>
       </c>
       <c r="I357" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-03T18:49:10.241Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="358">
@@ -11938,13 +11939,13 @@
         <v>PASS</v>
       </c>
       <c r="H358">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="I358" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-03T18:49:11.239Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="359">
@@ -11970,13 +11971,13 @@
         <v>PASS</v>
       </c>
       <c r="H359">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="I359" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-03T18:49:12.159Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="360">
@@ -12002,13 +12003,13 @@
         <v>PASS</v>
       </c>
       <c r="H360">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="I360" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-03T18:49:12.789Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="361">
@@ -12034,13 +12035,13 @@
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="I361" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-03T18:49:13.813Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="362">
@@ -12066,13 +12067,13 @@
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>955</v>
+        <v>0</v>
       </c>
       <c r="I362" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-03T18:49:14.768Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="363">
@@ -12083,7 +12084,7 @@
         <v>Fuzzing with database query snippets (353)</v>
       </c>
       <c r="C363" t="str">
-        <v>sql_fuzz_353_1yta@test.com</v>
+        <v>sql_fuzz_353_dbqb@test.com</v>
       </c>
       <c r="D363" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12098,13 +12099,13 @@
         <v>PASS</v>
       </c>
       <c r="H363">
-        <v>1113</v>
+        <v>0</v>
       </c>
       <c r="I363" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-03T18:49:15.881Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="364">
@@ -12130,13 +12131,13 @@
         <v>PASS</v>
       </c>
       <c r="H364">
-        <v>1017</v>
+        <v>0</v>
       </c>
       <c r="I364" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-03T18:49:16.898Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="365">
@@ -12162,13 +12163,13 @@
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>763</v>
+        <v>0</v>
       </c>
       <c r="I365" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-03T18:49:17.661Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="366">
@@ -12194,13 +12195,13 @@
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="I366" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-03T18:49:18.550Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="367">
@@ -12226,13 +12227,13 @@
         <v>PASS</v>
       </c>
       <c r="H367">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="I367" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-03T18:49:19.632Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="368">
@@ -12258,13 +12259,13 @@
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I368" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-03T18:49:20.532Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="369">
@@ -12275,7 +12276,7 @@
         <v>Fuzzing with database query snippets (359)</v>
       </c>
       <c r="C369" t="str">
-        <v>sql_fuzz_359_y9uz@test.com</v>
+        <v>sql_fuzz_359_6zl6@test.com</v>
       </c>
       <c r="D369" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12290,13 +12291,13 @@
         <v>PASS</v>
       </c>
       <c r="H369">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="I369" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-03T18:49:21.543Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="370">
@@ -12322,13 +12323,13 @@
         <v>PASS</v>
       </c>
       <c r="H370">
-        <v>711</v>
+        <v>0</v>
       </c>
       <c r="I370" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-03T18:49:22.254Z</v>
+        <v>2026-08-08T07:37:30.835Z</v>
       </c>
     </row>
     <row r="371">
@@ -12354,13 +12355,13 @@
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="I371" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-03T18:49:22.873Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="372">
@@ -12386,13 +12387,13 @@
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="I372" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-03T18:49:23.774Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="373">
@@ -12418,13 +12419,13 @@
         <v>PASS</v>
       </c>
       <c r="H373">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="I373" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-03T18:49:24.504Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="374">
@@ -12450,13 +12451,13 @@
         <v>PASS</v>
       </c>
       <c r="H374">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="I374" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-03T18:49:25.310Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="375">
@@ -12467,7 +12468,7 @@
         <v>Fuzzing with database query snippets (365)</v>
       </c>
       <c r="C375" t="str">
-        <v>sql_fuzz_365_6cgt@test.com</v>
+        <v>sql_fuzz_365_8924@test.com</v>
       </c>
       <c r="D375" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12482,13 +12483,13 @@
         <v>PASS</v>
       </c>
       <c r="H375">
-        <v>1044</v>
+        <v>0</v>
       </c>
       <c r="I375" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-03T18:49:26.354Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="376">
@@ -12514,13 +12515,13 @@
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="I376" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-03T18:49:27.031Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="377">
@@ -12546,13 +12547,13 @@
         <v>PASS</v>
       </c>
       <c r="H377">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="I377" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-03T18:49:27.712Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="378">
@@ -12578,13 +12579,13 @@
         <v>PASS</v>
       </c>
       <c r="H378">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="I378" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-03T18:49:28.425Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="379">
@@ -12610,13 +12611,13 @@
         <v>PASS</v>
       </c>
       <c r="H379">
-        <v>983</v>
+        <v>0</v>
       </c>
       <c r="I379" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-03T18:49:29.408Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="380">
@@ -12642,13 +12643,13 @@
         <v>PASS</v>
       </c>
       <c r="H380">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="I380" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-03T18:49:30.093Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="381">
@@ -12659,7 +12660,7 @@
         <v>Fuzzing with database query snippets (371)</v>
       </c>
       <c r="C381" t="str">
-        <v>sql_fuzz_371_p37l@test.com</v>
+        <v>sql_fuzz_371_h7b1@test.com</v>
       </c>
       <c r="D381" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12674,13 +12675,13 @@
         <v>PASS</v>
       </c>
       <c r="H381">
-        <v>911</v>
+        <v>0</v>
       </c>
       <c r="I381" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-03T18:49:31.005Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="382">
@@ -12706,13 +12707,13 @@
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>1068</v>
+        <v>0</v>
       </c>
       <c r="I382" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-03T18:49:32.073Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="383">
@@ -12738,13 +12739,13 @@
         <v>PASS</v>
       </c>
       <c r="H383">
-        <v>1076</v>
+        <v>0</v>
       </c>
       <c r="I383" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-03T18:49:33.149Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="384">
@@ -12770,13 +12771,13 @@
         <v>PASS</v>
       </c>
       <c r="H384">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="I384" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-03T18:49:34.091Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="385">
@@ -12802,13 +12803,13 @@
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>1226</v>
+        <v>0</v>
       </c>
       <c r="I385" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-03T18:49:35.317Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="386">
@@ -12834,13 +12835,13 @@
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="I386" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-03T18:49:36.332Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="387">
@@ -12851,7 +12852,7 @@
         <v>Fuzzing with database query snippets (377)</v>
       </c>
       <c r="C387" t="str">
-        <v>sql_fuzz_377_d635@test.com</v>
+        <v>sql_fuzz_377_95ab@test.com</v>
       </c>
       <c r="D387" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12866,13 +12867,13 @@
         <v>PASS</v>
       </c>
       <c r="H387">
-        <v>1058</v>
+        <v>0</v>
       </c>
       <c r="I387" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-03T18:49:37.390Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="388">
@@ -12898,13 +12899,13 @@
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="I388" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-03T18:49:38.343Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="389">
@@ -12930,13 +12931,13 @@
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="I389" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-03T18:49:38.983Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="390">
@@ -12962,13 +12963,13 @@
         <v>PASS</v>
       </c>
       <c r="H390">
-        <v>1097</v>
+        <v>0</v>
       </c>
       <c r="I390" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-03T18:49:40.080Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="391">
@@ -12994,13 +12995,13 @@
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="I391" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-03T18:49:41.144Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="392">
@@ -13026,13 +13027,13 @@
         <v>PASS</v>
       </c>
       <c r="H392">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="I392" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-03T18:49:41.794Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="393">
@@ -13043,7 +13044,7 @@
         <v>Fuzzing with database query snippets (383)</v>
       </c>
       <c r="C393" t="str">
-        <v>sql_fuzz_383_wu78@test.com</v>
+        <v>sql_fuzz_383_1hhz@test.com</v>
       </c>
       <c r="D393" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13058,13 +13059,13 @@
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="I393" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-03T18:49:42.601Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="394">
@@ -13090,13 +13091,13 @@
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="I394" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-03T18:49:43.279Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="395">
@@ -13122,13 +13123,13 @@
         <v>PASS</v>
       </c>
       <c r="H395">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="I395" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-03T18:49:44.127Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="396">
@@ -13154,13 +13155,13 @@
         <v>PASS</v>
       </c>
       <c r="H396">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="I396" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-03T18:49:44.724Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="397">
@@ -13186,13 +13187,13 @@
         <v>PASS</v>
       </c>
       <c r="H397">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="I397" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-03T18:49:45.727Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="398">
@@ -13218,13 +13219,13 @@
         <v>PASS</v>
       </c>
       <c r="H398">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="I398" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-03T18:49:46.827Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="399">
@@ -13235,7 +13236,7 @@
         <v>Fuzzing with database query snippets (389)</v>
       </c>
       <c r="C399" t="str">
-        <v>sql_fuzz_389_2a0b@test.com</v>
+        <v>sql_fuzz_389_5ggh@test.com</v>
       </c>
       <c r="D399" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13250,13 +13251,13 @@
         <v>PASS</v>
       </c>
       <c r="H399">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="I399" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-03T18:49:47.860Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="400">
@@ -13282,13 +13283,13 @@
         <v>PASS</v>
       </c>
       <c r="H400">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="I400" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-03T18:49:48.537Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
     <row r="401">
@@ -13314,13 +13315,13 @@
         <v>PASS</v>
       </c>
       <c r="H401">
-        <v>887</v>
+        <v>0</v>
       </c>
       <c r="I401" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-03T18:49:49.424Z</v>
+        <v>2026-08-08T07:37:30.836Z</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/reports/selenium-test-report-400.xlsx
+++ b/selenium-tests/reports/selenium-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Total Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
@@ -465,7 +465,7 @@
         <v>Executed At</v>
       </c>
       <c r="B8" t="str">
-        <v>9/8/2026, 8:25:01 pm</v>
+        <v>9/8/2026, 11:49:32 pm</v>
       </c>
     </row>
   </sheetData>
@@ -546,14 +546,14 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>2444</v>
+        <v>4325</v>
       </c>
       <c r="I2" t="str" xml:space="preserve">
         <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
   (Session info: chrome=151.0.7922.77)</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="6">
@@ -681,7 +681,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="9">
@@ -777,7 +777,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
     </row>
     <row r="10">
@@ -809,7 +809,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="11">
@@ -841,7 +841,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="12">
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="13">
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="14">
@@ -937,7 +937,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="15">
@@ -948,7 +948,7 @@
         <v>Fuzzing with database query snippets (5)</v>
       </c>
       <c r="C15" t="str">
-        <v>sql_fuzz_5_wcbc@test.com</v>
+        <v>sql_fuzz_5_9j5n@test.com</v>
       </c>
       <c r="D15" t="str">
         <v>'; DROP TABLE u...</v>
@@ -969,7 +969,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="16">
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="17">
@@ -1033,7 +1033,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="18">
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="19">
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="20">
@@ -1129,7 +1129,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="21">
@@ -1140,7 +1140,7 @@
         <v>Fuzzing with database query snippets (11)</v>
       </c>
       <c r="C21" t="str">
-        <v>sql_fuzz_11_mpk3@test.com</v>
+        <v>sql_fuzz_11_nvbz@test.com</v>
       </c>
       <c r="D21" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="22">
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="23">
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="25">
@@ -1289,7 +1289,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="26">
@@ -1321,7 +1321,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="27">
@@ -1332,7 +1332,7 @@
         <v>Fuzzing with database query snippets (17)</v>
       </c>
       <c r="C27" t="str">
-        <v>sql_fuzz_17_aq5z@test.com</v>
+        <v>sql_fuzz_17_f89w@test.com</v>
       </c>
       <c r="D27" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1353,7 +1353,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="28">
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="29">
@@ -1417,7 +1417,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="30">
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="31">
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-09T14:55:01.794Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="32">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="33">
@@ -1524,7 +1524,7 @@
         <v>Fuzzing with database query snippets (23)</v>
       </c>
       <c r="C33" t="str">
-        <v>sql_fuzz_23_o1d7@test.com</v>
+        <v>sql_fuzz_23_lejh@test.com</v>
       </c>
       <c r="D33" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="34">
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="35">
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="36">
@@ -1641,7 +1641,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="37">
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="39">
@@ -1716,7 +1716,7 @@
         <v>Fuzzing with database query snippets (29)</v>
       </c>
       <c r="C39" t="str">
-        <v>sql_fuzz_29_cv4k@test.com</v>
+        <v>sql_fuzz_29_9yu7@test.com</v>
       </c>
       <c r="D39" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1737,7 +1737,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="40">
@@ -1769,7 +1769,7 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="41">
@@ -1801,7 +1801,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
     </row>
     <row r="42">
@@ -1833,7 +1833,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="43">
@@ -1865,7 +1865,7 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="44">
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="45">
@@ -1908,7 +1908,7 @@
         <v>Fuzzing with database query snippets (35)</v>
       </c>
       <c r="C45" t="str">
-        <v>sql_fuzz_35_4jgw@test.com</v>
+        <v>sql_fuzz_35_hgyl@test.com</v>
       </c>
       <c r="D45" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1929,7 +1929,7 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="46">
@@ -1961,7 +1961,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="47">
@@ -1993,7 +1993,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="48">
@@ -2025,7 +2025,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="49">
@@ -2057,7 +2057,7 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="50">
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="51">
@@ -2100,7 +2100,7 @@
         <v>Fuzzing with database query snippets (41)</v>
       </c>
       <c r="C51" t="str">
-        <v>sql_fuzz_41_zg11@test.com</v>
+        <v>sql_fuzz_41_d57b@test.com</v>
       </c>
       <c r="D51" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="52">
@@ -2153,7 +2153,7 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="53">
@@ -2185,7 +2185,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="54">
@@ -2217,7 +2217,7 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="55">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="56">
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="57">
@@ -2292,7 +2292,7 @@
         <v>Fuzzing with database query snippets (47)</v>
       </c>
       <c r="C57" t="str">
-        <v>sql_fuzz_47_od71@test.com</v>
+        <v>sql_fuzz_47_pqii@test.com</v>
       </c>
       <c r="D57" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="58">
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="59">
@@ -2377,7 +2377,7 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="60">
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="61">
@@ -2441,7 +2441,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="62">
@@ -2473,7 +2473,7 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="63">
@@ -2484,7 +2484,7 @@
         <v>Fuzzing with database query snippets (53)</v>
       </c>
       <c r="C63" t="str">
-        <v>sql_fuzz_53_61rd@test.com</v>
+        <v>sql_fuzz_53_60jd@test.com</v>
       </c>
       <c r="D63" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2505,7 +2505,7 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="64">
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="65">
@@ -2569,7 +2569,7 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="66">
@@ -2601,7 +2601,7 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="67">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="68">
@@ -2665,7 +2665,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="69">
@@ -2676,7 +2676,7 @@
         <v>Fuzzing with database query snippets (59)</v>
       </c>
       <c r="C69" t="str">
-        <v>sql_fuzz_59_bglc@test.com</v>
+        <v>sql_fuzz_59_2cmq@test.com</v>
       </c>
       <c r="D69" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2697,7 +2697,7 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="70">
@@ -2729,7 +2729,7 @@
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="71">
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="72">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="73">
@@ -2825,7 +2825,7 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="74">
@@ -2857,7 +2857,7 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="75">
@@ -2868,7 +2868,7 @@
         <v>Fuzzing with database query snippets (65)</v>
       </c>
       <c r="C75" t="str">
-        <v>sql_fuzz_65_aknt@test.com</v>
+        <v>sql_fuzz_65_mqrx@test.com</v>
       </c>
       <c r="D75" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="76">
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="77">
@@ -2953,7 +2953,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="78">
@@ -2985,7 +2985,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="79">
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="80">
@@ -3049,7 +3049,7 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="81">
@@ -3060,7 +3060,7 @@
         <v>Fuzzing with database query snippets (71)</v>
       </c>
       <c r="C81" t="str">
-        <v>sql_fuzz_71_3ryn@test.com</v>
+        <v>sql_fuzz_71_84x1@test.com</v>
       </c>
       <c r="D81" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3081,7 +3081,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="82">
@@ -3113,7 +3113,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="83">
@@ -3145,7 +3145,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="84">
@@ -3177,7 +3177,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="85">
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="86">
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="87">
@@ -3252,7 +3252,7 @@
         <v>Fuzzing with database query snippets (77)</v>
       </c>
       <c r="C87" t="str">
-        <v>sql_fuzz_77_2hwm@test.com</v>
+        <v>sql_fuzz_77_mq2u@test.com</v>
       </c>
       <c r="D87" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3273,7 +3273,7 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="88">
@@ -3305,7 +3305,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="89">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="90">
@@ -3369,7 +3369,7 @@
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="91">
@@ -3401,7 +3401,7 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="92">
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="93">
@@ -3444,7 +3444,7 @@
         <v>Fuzzing with database query snippets (83)</v>
       </c>
       <c r="C93" t="str">
-        <v>sql_fuzz_83_we08@test.com</v>
+        <v>sql_fuzz_83_xwm1@test.com</v>
       </c>
       <c r="D93" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="94">
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="95">
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="96">
@@ -3561,7 +3561,7 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="97">
@@ -3593,7 +3593,7 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="98">
@@ -3625,7 +3625,7 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="99">
@@ -3636,7 +3636,7 @@
         <v>Fuzzing with database query snippets (89)</v>
       </c>
       <c r="C99" t="str">
-        <v>sql_fuzz_89_ffwh@test.com</v>
+        <v>sql_fuzz_89_kdfi@test.com</v>
       </c>
       <c r="D99" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3657,7 +3657,7 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="100">
@@ -3689,7 +3689,7 @@
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="101">
@@ -3721,7 +3721,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
     </row>
     <row r="102">
@@ -3753,7 +3753,7 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="103">
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="104">
@@ -3817,7 +3817,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="105">
@@ -3828,7 +3828,7 @@
         <v>Fuzzing with database query snippets (95)</v>
       </c>
       <c r="C105" t="str">
-        <v>sql_fuzz_95_afkq@test.com</v>
+        <v>sql_fuzz_95_shl5@test.com</v>
       </c>
       <c r="D105" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3849,7 +3849,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="106">
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="107">
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="108">
@@ -3945,7 +3945,7 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="109">
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="110">
@@ -4009,7 +4009,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="111">
@@ -4020,7 +4020,7 @@
         <v>Fuzzing with database query snippets (101)</v>
       </c>
       <c r="C111" t="str">
-        <v>sql_fuzz_101_ep26@test.com</v>
+        <v>sql_fuzz_101_vecw@test.com</v>
       </c>
       <c r="D111" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4041,7 +4041,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="112">
@@ -4073,7 +4073,7 @@
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="113">
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="114">
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="115">
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="116">
@@ -4201,7 +4201,7 @@
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="117">
@@ -4212,7 +4212,7 @@
         <v>Fuzzing with database query snippets (107)</v>
       </c>
       <c r="C117" t="str">
-        <v>sql_fuzz_107_iz0r@test.com</v>
+        <v>sql_fuzz_107_zjt7@test.com</v>
       </c>
       <c r="D117" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4233,7 +4233,7 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="118">
@@ -4265,7 +4265,7 @@
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="119">
@@ -4297,7 +4297,7 @@
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="120">
@@ -4329,7 +4329,7 @@
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="121">
@@ -4361,7 +4361,7 @@
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="122">
@@ -4393,7 +4393,7 @@
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="123">
@@ -4404,7 +4404,7 @@
         <v>Fuzzing with database query snippets (113)</v>
       </c>
       <c r="C123" t="str">
-        <v>sql_fuzz_113_faos@test.com</v>
+        <v>sql_fuzz_113_jblu@test.com</v>
       </c>
       <c r="D123" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="124">
@@ -4457,7 +4457,7 @@
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="125">
@@ -4489,7 +4489,7 @@
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="126">
@@ -4521,7 +4521,7 @@
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="127">
@@ -4553,7 +4553,7 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="128">
@@ -4585,7 +4585,7 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="129">
@@ -4596,7 +4596,7 @@
         <v>Fuzzing with database query snippets (119)</v>
       </c>
       <c r="C129" t="str">
-        <v>sql_fuzz_119_y4g6@test.com</v>
+        <v>sql_fuzz_119_hzoq@test.com</v>
       </c>
       <c r="D129" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4617,7 +4617,7 @@
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="130">
@@ -4649,7 +4649,7 @@
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="131">
@@ -4681,7 +4681,7 @@
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="132">
@@ -4713,7 +4713,7 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="133">
@@ -4745,7 +4745,7 @@
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="134">
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="135">
@@ -4788,7 +4788,7 @@
         <v>Fuzzing with database query snippets (125)</v>
       </c>
       <c r="C135" t="str">
-        <v>sql_fuzz_125_irv0@test.com</v>
+        <v>sql_fuzz_125_9cc1@test.com</v>
       </c>
       <c r="D135" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4809,7 +4809,7 @@
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="136">
@@ -4841,7 +4841,7 @@
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="137">
@@ -4873,7 +4873,7 @@
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="138">
@@ -4905,7 +4905,7 @@
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="139">
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="140">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="141">
@@ -4980,7 +4980,7 @@
         <v>Fuzzing with database query snippets (131)</v>
       </c>
       <c r="C141" t="str">
-        <v>sql_fuzz_131_cofx@test.com</v>
+        <v>sql_fuzz_131_u1ct@test.com</v>
       </c>
       <c r="D141" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5001,7 +5001,7 @@
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="142">
@@ -5033,7 +5033,7 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="143">
@@ -5065,7 +5065,7 @@
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="144">
@@ -5097,7 +5097,7 @@
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="145">
@@ -5129,7 +5129,7 @@
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="146">
@@ -5161,7 +5161,7 @@
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="147">
@@ -5172,7 +5172,7 @@
         <v>Fuzzing with database query snippets (137)</v>
       </c>
       <c r="C147" t="str">
-        <v>sql_fuzz_137_ar7o@test.com</v>
+        <v>sql_fuzz_137_ucyq@test.com</v>
       </c>
       <c r="D147" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5193,7 +5193,7 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="148">
@@ -5225,7 +5225,7 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="149">
@@ -5257,7 +5257,7 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="150">
@@ -5289,7 +5289,7 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="151">
@@ -5321,7 +5321,7 @@
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="152">
@@ -5353,7 +5353,7 @@
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="153">
@@ -5364,7 +5364,7 @@
         <v>Fuzzing with database query snippets (143)</v>
       </c>
       <c r="C153" t="str">
-        <v>sql_fuzz_143_ghu4@test.com</v>
+        <v>sql_fuzz_143_uu2t@test.com</v>
       </c>
       <c r="D153" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5385,7 +5385,7 @@
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="154">
@@ -5417,7 +5417,7 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="155">
@@ -5449,7 +5449,7 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="156">
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="157">
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="158">
@@ -5545,7 +5545,7 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="159">
@@ -5556,7 +5556,7 @@
         <v>Fuzzing with database query snippets (149)</v>
       </c>
       <c r="C159" t="str">
-        <v>sql_fuzz_149_oqf9@test.com</v>
+        <v>sql_fuzz_149_th4k@test.com</v>
       </c>
       <c r="D159" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="160">
@@ -5609,7 +5609,7 @@
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="161">
@@ -5641,7 +5641,7 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="162">
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="163">
@@ -5705,7 +5705,7 @@
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="164">
@@ -5737,7 +5737,7 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="165">
@@ -5748,7 +5748,7 @@
         <v>Fuzzing with database query snippets (155)</v>
       </c>
       <c r="C165" t="str">
-        <v>sql_fuzz_155_lqvx@test.com</v>
+        <v>sql_fuzz_155_1era@test.com</v>
       </c>
       <c r="D165" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="166">
@@ -5801,7 +5801,7 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="167">
@@ -5833,7 +5833,7 @@
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="168">
@@ -5865,7 +5865,7 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="169">
@@ -5897,7 +5897,7 @@
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="170">
@@ -5929,7 +5929,7 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="171">
@@ -5940,7 +5940,7 @@
         <v>Fuzzing with database query snippets (161)</v>
       </c>
       <c r="C171" t="str">
-        <v>sql_fuzz_161_eay6@test.com</v>
+        <v>sql_fuzz_161_bvsn@test.com</v>
       </c>
       <c r="D171" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5961,7 +5961,7 @@
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
     </row>
     <row r="172">
@@ -5993,7 +5993,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="173">
@@ -6025,7 +6025,7 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="174">
@@ -6057,7 +6057,7 @@
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="175">
@@ -6089,7 +6089,7 @@
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="176">
@@ -6121,7 +6121,7 @@
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="177">
@@ -6132,7 +6132,7 @@
         <v>Fuzzing with database query snippets (167)</v>
       </c>
       <c r="C177" t="str">
-        <v>sql_fuzz_167_59fq@test.com</v>
+        <v>sql_fuzz_167_xmj1@test.com</v>
       </c>
       <c r="D177" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6153,7 +6153,7 @@
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="178">
@@ -6185,7 +6185,7 @@
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="179">
@@ -6217,7 +6217,7 @@
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="180">
@@ -6249,7 +6249,7 @@
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="181">
@@ -6281,7 +6281,7 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="182">
@@ -6313,7 +6313,7 @@
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="183">
@@ -6324,7 +6324,7 @@
         <v>Fuzzing with database query snippets (173)</v>
       </c>
       <c r="C183" t="str">
-        <v>sql_fuzz_173_b7ky@test.com</v>
+        <v>sql_fuzz_173_w1re@test.com</v>
       </c>
       <c r="D183" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6345,7 +6345,7 @@
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="184">
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="185">
@@ -6409,7 +6409,7 @@
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="186">
@@ -6441,7 +6441,7 @@
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="187">
@@ -6473,7 +6473,7 @@
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="188">
@@ -6505,7 +6505,7 @@
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="189">
@@ -6516,7 +6516,7 @@
         <v>Fuzzing with database query snippets (179)</v>
       </c>
       <c r="C189" t="str">
-        <v>sql_fuzz_179_g4hd@test.com</v>
+        <v>sql_fuzz_179_h79s@test.com</v>
       </c>
       <c r="D189" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6537,7 +6537,7 @@
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="190">
@@ -6569,7 +6569,7 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="191">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="192">
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="193">
@@ -6665,7 +6665,7 @@
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="194">
@@ -6697,7 +6697,7 @@
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="195">
@@ -6708,7 +6708,7 @@
         <v>Fuzzing with database query snippets (185)</v>
       </c>
       <c r="C195" t="str">
-        <v>sql_fuzz_185_k57b@test.com</v>
+        <v>sql_fuzz_185_9wsf@test.com</v>
       </c>
       <c r="D195" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6729,7 +6729,7 @@
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="196">
@@ -6761,7 +6761,7 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="197">
@@ -6793,7 +6793,7 @@
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="198">
@@ -6825,7 +6825,7 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="199">
@@ -6857,7 +6857,7 @@
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="200">
@@ -6889,7 +6889,7 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="201">
@@ -6900,7 +6900,7 @@
         <v>Fuzzing with database query snippets (191)</v>
       </c>
       <c r="C201" t="str">
-        <v>sql_fuzz_191_vqo1@test.com</v>
+        <v>sql_fuzz_191_6ol7@test.com</v>
       </c>
       <c r="D201" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6921,7 +6921,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="202">
@@ -6953,7 +6953,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="203">
@@ -6985,7 +6985,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="204">
@@ -7017,7 +7017,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="205">
@@ -7049,7 +7049,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="206">
@@ -7081,7 +7081,7 @@
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="207">
@@ -7092,7 +7092,7 @@
         <v>Fuzzing with database query snippets (197)</v>
       </c>
       <c r="C207" t="str">
-        <v>sql_fuzz_197_0is5@test.com</v>
+        <v>sql_fuzz_197_8wzy@test.com</v>
       </c>
       <c r="D207" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7113,7 +7113,7 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="208">
@@ -7145,7 +7145,7 @@
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="209">
@@ -7177,7 +7177,7 @@
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="210">
@@ -7209,7 +7209,7 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="211">
@@ -7241,7 +7241,7 @@
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="212">
@@ -7273,7 +7273,7 @@
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="213">
@@ -7284,7 +7284,7 @@
         <v>Fuzzing with database query snippets (203)</v>
       </c>
       <c r="C213" t="str">
-        <v>sql_fuzz_203_qtax@test.com</v>
+        <v>sql_fuzz_203_ozk6@test.com</v>
       </c>
       <c r="D213" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7305,7 +7305,7 @@
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="214">
@@ -7337,7 +7337,7 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="215">
@@ -7369,7 +7369,7 @@
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="216">
@@ -7401,7 +7401,7 @@
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="217">
@@ -7433,7 +7433,7 @@
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="218">
@@ -7465,7 +7465,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="219">
@@ -7476,7 +7476,7 @@
         <v>Fuzzing with database query snippets (209)</v>
       </c>
       <c r="C219" t="str">
-        <v>sql_fuzz_209_rhyt@test.com</v>
+        <v>sql_fuzz_209_fb2x@test.com</v>
       </c>
       <c r="D219" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7497,7 +7497,7 @@
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="220">
@@ -7529,7 +7529,7 @@
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="221">
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="222">
@@ -7593,7 +7593,7 @@
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="223">
@@ -7625,7 +7625,7 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="224">
@@ -7657,7 +7657,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="225">
@@ -7668,7 +7668,7 @@
         <v>Fuzzing with database query snippets (215)</v>
       </c>
       <c r="C225" t="str">
-        <v>sql_fuzz_215_1kwc@test.com</v>
+        <v>sql_fuzz_215_sglk@test.com</v>
       </c>
       <c r="D225" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7689,7 +7689,7 @@
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="226">
@@ -7721,7 +7721,7 @@
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="227">
@@ -7753,7 +7753,7 @@
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="228">
@@ -7785,7 +7785,7 @@
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="229">
@@ -7817,7 +7817,7 @@
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="230">
@@ -7849,7 +7849,7 @@
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="231">
@@ -7860,7 +7860,7 @@
         <v>Fuzzing with database query snippets (221)</v>
       </c>
       <c r="C231" t="str">
-        <v>sql_fuzz_221_tfbf@test.com</v>
+        <v>sql_fuzz_221_a88i@test.com</v>
       </c>
       <c r="D231" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7881,7 +7881,7 @@
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="232">
@@ -7913,7 +7913,7 @@
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="233">
@@ -7945,7 +7945,7 @@
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="234">
@@ -7977,7 +7977,7 @@
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="235">
@@ -8009,7 +8009,7 @@
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="236">
@@ -8041,7 +8041,7 @@
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="237">
@@ -8052,7 +8052,7 @@
         <v>Fuzzing with database query snippets (227)</v>
       </c>
       <c r="C237" t="str">
-        <v>sql_fuzz_227_kafa@test.com</v>
+        <v>sql_fuzz_227_yxe5@test.com</v>
       </c>
       <c r="D237" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8073,7 +8073,7 @@
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="238">
@@ -8105,7 +8105,7 @@
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="239">
@@ -8137,7 +8137,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="240">
@@ -8169,7 +8169,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="241">
@@ -8201,7 +8201,7 @@
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
     </row>
     <row r="242">
@@ -8233,7 +8233,7 @@
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="243">
@@ -8244,7 +8244,7 @@
         <v>Fuzzing with database query snippets (233)</v>
       </c>
       <c r="C243" t="str">
-        <v>sql_fuzz_233_n5q1@test.com</v>
+        <v>sql_fuzz_233_sb07@test.com</v>
       </c>
       <c r="D243" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8265,7 +8265,7 @@
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="244">
@@ -8297,7 +8297,7 @@
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="245">
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="246">
@@ -8361,7 +8361,7 @@
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="247">
@@ -8393,7 +8393,7 @@
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="248">
@@ -8425,7 +8425,7 @@
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="249">
@@ -8436,7 +8436,7 @@
         <v>Fuzzing with database query snippets (239)</v>
       </c>
       <c r="C249" t="str">
-        <v>sql_fuzz_239_83c1@test.com</v>
+        <v>sql_fuzz_239_1yxg@test.com</v>
       </c>
       <c r="D249" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8457,7 +8457,7 @@
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="250">
@@ -8489,7 +8489,7 @@
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="251">
@@ -8521,7 +8521,7 @@
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="252">
@@ -8553,7 +8553,7 @@
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="253">
@@ -8585,7 +8585,7 @@
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="254">
@@ -8617,7 +8617,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="255">
@@ -8628,7 +8628,7 @@
         <v>Fuzzing with database query snippets (245)</v>
       </c>
       <c r="C255" t="str">
-        <v>sql_fuzz_245_4n7y@test.com</v>
+        <v>sql_fuzz_245_58dg@test.com</v>
       </c>
       <c r="D255" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8649,7 +8649,7 @@
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="256">
@@ -8681,7 +8681,7 @@
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="257">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="258">
@@ -8745,7 +8745,7 @@
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="259">
@@ -8777,7 +8777,7 @@
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="260">
@@ -8809,7 +8809,7 @@
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="261">
@@ -8820,7 +8820,7 @@
         <v>Fuzzing with database query snippets (251)</v>
       </c>
       <c r="C261" t="str">
-        <v>sql_fuzz_251_x69i@test.com</v>
+        <v>sql_fuzz_251_7ddy@test.com</v>
       </c>
       <c r="D261" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8841,7 +8841,7 @@
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="262">
@@ -8873,7 +8873,7 @@
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="263">
@@ -8905,7 +8905,7 @@
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="264">
@@ -8937,7 +8937,7 @@
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="265">
@@ -8969,7 +8969,7 @@
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="266">
@@ -9001,7 +9001,7 @@
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="267">
@@ -9012,7 +9012,7 @@
         <v>Fuzzing with database query snippets (257)</v>
       </c>
       <c r="C267" t="str">
-        <v>sql_fuzz_257_fsdd@test.com</v>
+        <v>sql_fuzz_257_6bde@test.com</v>
       </c>
       <c r="D267" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9033,7 +9033,7 @@
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="268">
@@ -9065,7 +9065,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="269">
@@ -9097,7 +9097,7 @@
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="270">
@@ -9129,7 +9129,7 @@
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="271">
@@ -9161,7 +9161,7 @@
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="272">
@@ -9193,7 +9193,7 @@
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="273">
@@ -9204,7 +9204,7 @@
         <v>Fuzzing with database query snippets (263)</v>
       </c>
       <c r="C273" t="str">
-        <v>sql_fuzz_263_ly0x@test.com</v>
+        <v>sql_fuzz_263_w2s0@test.com</v>
       </c>
       <c r="D273" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9225,7 +9225,7 @@
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="274">
@@ -9257,7 +9257,7 @@
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="275">
@@ -9289,7 +9289,7 @@
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="276">
@@ -9321,7 +9321,7 @@
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="277">
@@ -9353,7 +9353,7 @@
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="278">
@@ -9385,7 +9385,7 @@
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="279">
@@ -9396,7 +9396,7 @@
         <v>Fuzzing with database query snippets (269)</v>
       </c>
       <c r="C279" t="str">
-        <v>sql_fuzz_269_6n49@test.com</v>
+        <v>sql_fuzz_269_4wye@test.com</v>
       </c>
       <c r="D279" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9417,7 +9417,7 @@
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="280">
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="281">
@@ -9481,7 +9481,7 @@
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="282">
@@ -9513,7 +9513,7 @@
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="283">
@@ -9545,7 +9545,7 @@
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="284">
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="285">
@@ -9588,7 +9588,7 @@
         <v>Fuzzing with database query snippets (275)</v>
       </c>
       <c r="C285" t="str">
-        <v>sql_fuzz_275_jeho@test.com</v>
+        <v>sql_fuzz_275_k7j0@test.com</v>
       </c>
       <c r="D285" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9609,7 +9609,7 @@
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="286">
@@ -9641,7 +9641,7 @@
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="287">
@@ -9673,7 +9673,7 @@
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="288">
@@ -9705,7 +9705,7 @@
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="289">
@@ -9737,7 +9737,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="290">
@@ -9769,7 +9769,7 @@
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="291">
@@ -9780,7 +9780,7 @@
         <v>Fuzzing with database query snippets (281)</v>
       </c>
       <c r="C291" t="str">
-        <v>sql_fuzz_281_7wr3@test.com</v>
+        <v>sql_fuzz_281_bq3h@test.com</v>
       </c>
       <c r="D291" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9801,7 +9801,7 @@
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="292">
@@ -9833,7 +9833,7 @@
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="293">
@@ -9865,7 +9865,7 @@
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="294">
@@ -9897,7 +9897,7 @@
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="295">
@@ -9929,7 +9929,7 @@
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="296">
@@ -9961,7 +9961,7 @@
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="297">
@@ -9972,7 +9972,7 @@
         <v>Fuzzing with database query snippets (287)</v>
       </c>
       <c r="C297" t="str">
-        <v>sql_fuzz_287_jfqk@test.com</v>
+        <v>sql_fuzz_287_8ip1@test.com</v>
       </c>
       <c r="D297" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9993,7 +9993,7 @@
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="298">
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="299">
@@ -10057,7 +10057,7 @@
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="300">
@@ -10089,7 +10089,7 @@
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="301">
@@ -10121,7 +10121,7 @@
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="302">
@@ -10153,7 +10153,7 @@
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="303">
@@ -10164,7 +10164,7 @@
         <v>Fuzzing with database query snippets (293)</v>
       </c>
       <c r="C303" t="str">
-        <v>sql_fuzz_293_ir3k@test.com</v>
+        <v>sql_fuzz_293_0ynq@test.com</v>
       </c>
       <c r="D303" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10185,7 +10185,7 @@
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="304">
@@ -10217,7 +10217,7 @@
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="305">
@@ -10249,7 +10249,7 @@
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="306">
@@ -10281,7 +10281,7 @@
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="307">
@@ -10313,7 +10313,7 @@
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="308">
@@ -10345,7 +10345,7 @@
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="309">
@@ -10356,7 +10356,7 @@
         <v>Fuzzing with database query snippets (299)</v>
       </c>
       <c r="C309" t="str">
-        <v>sql_fuzz_299_4ywo@test.com</v>
+        <v>sql_fuzz_299_hzd4@test.com</v>
       </c>
       <c r="D309" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10377,7 +10377,7 @@
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="310">
@@ -10409,7 +10409,7 @@
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="311">
@@ -10441,7 +10441,7 @@
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="312">
@@ -10473,7 +10473,7 @@
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="313">
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="314">
@@ -10537,7 +10537,7 @@
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="315">
@@ -10548,7 +10548,7 @@
         <v>Fuzzing with database query snippets (305)</v>
       </c>
       <c r="C315" t="str">
-        <v>sql_fuzz_305_t7na@test.com</v>
+        <v>sql_fuzz_305_gkmq@test.com</v>
       </c>
       <c r="D315" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10569,7 +10569,7 @@
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="316">
@@ -10601,7 +10601,7 @@
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="317">
@@ -10633,7 +10633,7 @@
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="318">
@@ -10665,7 +10665,7 @@
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="319">
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="320">
@@ -10729,7 +10729,7 @@
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="321">
@@ -10740,7 +10740,7 @@
         <v>Fuzzing with database query snippets (311)</v>
       </c>
       <c r="C321" t="str">
-        <v>sql_fuzz_311_zikg@test.com</v>
+        <v>sql_fuzz_311_kz2a@test.com</v>
       </c>
       <c r="D321" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10761,7 +10761,7 @@
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
     </row>
     <row r="322">
@@ -10793,7 +10793,7 @@
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="323">
@@ -10825,7 +10825,7 @@
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="324">
@@ -10857,7 +10857,7 @@
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-09T14:55:01.795Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="325">
@@ -10889,7 +10889,7 @@
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="326">
@@ -10921,7 +10921,7 @@
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="327">
@@ -10932,7 +10932,7 @@
         <v>Fuzzing with database query snippets (317)</v>
       </c>
       <c r="C327" t="str">
-        <v>sql_fuzz_317_7bx6@test.com</v>
+        <v>sql_fuzz_317_2qde@test.com</v>
       </c>
       <c r="D327" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10953,7 +10953,7 @@
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="328">
@@ -10985,7 +10985,7 @@
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="329">
@@ -11017,7 +11017,7 @@
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="330">
@@ -11049,7 +11049,7 @@
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="331">
@@ -11081,7 +11081,7 @@
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="332">
@@ -11113,7 +11113,7 @@
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="333">
@@ -11124,7 +11124,7 @@
         <v>Fuzzing with database query snippets (323)</v>
       </c>
       <c r="C333" t="str">
-        <v>sql_fuzz_323_2kql@test.com</v>
+        <v>sql_fuzz_323_usri@test.com</v>
       </c>
       <c r="D333" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11145,7 +11145,7 @@
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="334">
@@ -11177,7 +11177,7 @@
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="335">
@@ -11209,7 +11209,7 @@
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="336">
@@ -11241,7 +11241,7 @@
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="337">
@@ -11273,7 +11273,7 @@
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="338">
@@ -11305,7 +11305,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="339">
@@ -11316,7 +11316,7 @@
         <v>Fuzzing with database query snippets (329)</v>
       </c>
       <c r="C339" t="str">
-        <v>sql_fuzz_329_caq3@test.com</v>
+        <v>sql_fuzz_329_6vun@test.com</v>
       </c>
       <c r="D339" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11337,7 +11337,7 @@
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="340">
@@ -11369,7 +11369,7 @@
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="341">
@@ -11401,7 +11401,7 @@
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="342">
@@ -11433,7 +11433,7 @@
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="343">
@@ -11465,7 +11465,7 @@
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="344">
@@ -11497,7 +11497,7 @@
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="345">
@@ -11508,7 +11508,7 @@
         <v>Fuzzing with database query snippets (335)</v>
       </c>
       <c r="C345" t="str">
-        <v>sql_fuzz_335_tsjf@test.com</v>
+        <v>sql_fuzz_335_6b1f@test.com</v>
       </c>
       <c r="D345" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11529,7 +11529,7 @@
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="346">
@@ -11561,7 +11561,7 @@
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="347">
@@ -11593,7 +11593,7 @@
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="348">
@@ -11625,7 +11625,7 @@
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="349">
@@ -11657,7 +11657,7 @@
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="350">
@@ -11689,7 +11689,7 @@
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="351">
@@ -11700,7 +11700,7 @@
         <v>Fuzzing with database query snippets (341)</v>
       </c>
       <c r="C351" t="str">
-        <v>sql_fuzz_341_s3gr@test.com</v>
+        <v>sql_fuzz_341_tsqw@test.com</v>
       </c>
       <c r="D351" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="352">
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="353">
@@ -11785,7 +11785,7 @@
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="354">
@@ -11817,7 +11817,7 @@
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="355">
@@ -11849,7 +11849,7 @@
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="356">
@@ -11881,7 +11881,7 @@
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="357">
@@ -11892,7 +11892,7 @@
         <v>Fuzzing with database query snippets (347)</v>
       </c>
       <c r="C357" t="str">
-        <v>sql_fuzz_347_25lz@test.com</v>
+        <v>sql_fuzz_347_x67k@test.com</v>
       </c>
       <c r="D357" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11913,7 +11913,7 @@
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="358">
@@ -11945,7 +11945,7 @@
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="359">
@@ -11977,7 +11977,7 @@
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="360">
@@ -12009,7 +12009,7 @@
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="361">
@@ -12041,7 +12041,7 @@
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="362">
@@ -12073,7 +12073,7 @@
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="363">
@@ -12084,7 +12084,7 @@
         <v>Fuzzing with database query snippets (353)</v>
       </c>
       <c r="C363" t="str">
-        <v>sql_fuzz_353_p7zr@test.com</v>
+        <v>sql_fuzz_353_384b@test.com</v>
       </c>
       <c r="D363" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12105,7 +12105,7 @@
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="364">
@@ -12137,7 +12137,7 @@
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="365">
@@ -12169,7 +12169,7 @@
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="366">
@@ -12201,7 +12201,7 @@
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="367">
@@ -12233,7 +12233,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="368">
@@ -12265,7 +12265,7 @@
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="369">
@@ -12276,7 +12276,7 @@
         <v>Fuzzing with database query snippets (359)</v>
       </c>
       <c r="C369" t="str">
-        <v>sql_fuzz_359_n0wk@test.com</v>
+        <v>sql_fuzz_359_7umz@test.com</v>
       </c>
       <c r="D369" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12297,7 +12297,7 @@
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="370">
@@ -12329,7 +12329,7 @@
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="371">
@@ -12361,7 +12361,7 @@
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="372">
@@ -12393,7 +12393,7 @@
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="373">
@@ -12425,7 +12425,7 @@
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="374">
@@ -12457,7 +12457,7 @@
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="375">
@@ -12468,7 +12468,7 @@
         <v>Fuzzing with database query snippets (365)</v>
       </c>
       <c r="C375" t="str">
-        <v>sql_fuzz_365_p68x@test.com</v>
+        <v>sql_fuzz_365_022m@test.com</v>
       </c>
       <c r="D375" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12489,7 +12489,7 @@
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="376">
@@ -12521,7 +12521,7 @@
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="377">
@@ -12553,7 +12553,7 @@
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="378">
@@ -12585,7 +12585,7 @@
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="379">
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="380">
@@ -12649,7 +12649,7 @@
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="381">
@@ -12660,7 +12660,7 @@
         <v>Fuzzing with database query snippets (371)</v>
       </c>
       <c r="C381" t="str">
-        <v>sql_fuzz_371_e9o5@test.com</v>
+        <v>sql_fuzz_371_8m7g@test.com</v>
       </c>
       <c r="D381" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12681,7 +12681,7 @@
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
     </row>
     <row r="382">
@@ -12713,7 +12713,7 @@
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="383">
@@ -12745,7 +12745,7 @@
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="384">
@@ -12777,7 +12777,7 @@
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="385">
@@ -12809,7 +12809,7 @@
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="386">
@@ -12841,7 +12841,7 @@
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="387">
@@ -12852,7 +12852,7 @@
         <v>Fuzzing with database query snippets (377)</v>
       </c>
       <c r="C387" t="str">
-        <v>sql_fuzz_377_mena@test.com</v>
+        <v>sql_fuzz_377_xwgx@test.com</v>
       </c>
       <c r="D387" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12873,7 +12873,7 @@
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="388">
@@ -12905,7 +12905,7 @@
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="389">
@@ -12937,7 +12937,7 @@
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="390">
@@ -12969,7 +12969,7 @@
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="391">
@@ -13001,7 +13001,7 @@
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="392">
@@ -13033,7 +13033,7 @@
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="393">
@@ -13044,7 +13044,7 @@
         <v>Fuzzing with database query snippets (383)</v>
       </c>
       <c r="C393" t="str">
-        <v>sql_fuzz_383_q5z4@test.com</v>
+        <v>sql_fuzz_383_s5fh@test.com</v>
       </c>
       <c r="D393" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13065,7 +13065,7 @@
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="394">
@@ -13097,7 +13097,7 @@
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="395">
@@ -13129,7 +13129,7 @@
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="396">
@@ -13161,7 +13161,7 @@
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="397">
@@ -13193,7 +13193,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="398">
@@ -13225,7 +13225,7 @@
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="399">
@@ -13236,7 +13236,7 @@
         <v>Fuzzing with database query snippets (389)</v>
       </c>
       <c r="C399" t="str">
-        <v>sql_fuzz_389_qtyz@test.com</v>
+        <v>sql_fuzz_389_4gd1@test.com</v>
       </c>
       <c r="D399" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13257,7 +13257,7 @@
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="400">
@@ -13289,7 +13289,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
     <row r="401">
@@ -13321,7 +13321,7 @@
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-09T14:55:01.796Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/reports/selenium-test-report-400.xlsx
+++ b/selenium-tests/reports/selenium-test-report-400.xlsx
@@ -449,7 +449,7 @@
         <v>Total Suite Duration (seconds)</v>
       </c>
       <c r="B6">
-        <v>4.33</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="7">
@@ -465,7 +465,7 @@
         <v>Executed At</v>
       </c>
       <c r="B8" t="str">
-        <v>9/8/2026, 11:49:32 pm</v>
+        <v>9/8/2026, 11:52:54 pm</v>
       </c>
     </row>
   </sheetData>
@@ -546,14 +546,14 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>4325</v>
+        <v>2502</v>
       </c>
       <c r="I2" t="str" xml:space="preserve">
         <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
   (Session info: chrome=151.0.7922.77)</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
     </row>
     <row r="6">
@@ -681,7 +681,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="9">
@@ -777,7 +777,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="10">
@@ -809,7 +809,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="11">
@@ -841,7 +841,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="12">
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="13">
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
     </row>
     <row r="14">
@@ -937,7 +937,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="15">
@@ -948,7 +948,7 @@
         <v>Fuzzing with database query snippets (5)</v>
       </c>
       <c r="C15" t="str">
-        <v>sql_fuzz_5_9j5n@test.com</v>
+        <v>sql_fuzz_5_r2mp@test.com</v>
       </c>
       <c r="D15" t="str">
         <v>'; DROP TABLE u...</v>
@@ -969,7 +969,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="16">
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="17">
@@ -1033,7 +1033,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="18">
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="19">
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="20">
@@ -1129,7 +1129,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="21">
@@ -1140,7 +1140,7 @@
         <v>Fuzzing with database query snippets (11)</v>
       </c>
       <c r="C21" t="str">
-        <v>sql_fuzz_11_nvbz@test.com</v>
+        <v>sql_fuzz_11_uzxh@test.com</v>
       </c>
       <c r="D21" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="22">
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="23">
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="25">
@@ -1289,7 +1289,7 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="26">
@@ -1321,7 +1321,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="27">
@@ -1332,7 +1332,7 @@
         <v>Fuzzing with database query snippets (17)</v>
       </c>
       <c r="C27" t="str">
-        <v>sql_fuzz_17_f89w@test.com</v>
+        <v>sql_fuzz_17_c2py@test.com</v>
       </c>
       <c r="D27" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1353,7 +1353,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="28">
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="29">
@@ -1417,7 +1417,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="30">
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="31">
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="32">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="33">
@@ -1524,7 +1524,7 @@
         <v>Fuzzing with database query snippets (23)</v>
       </c>
       <c r="C33" t="str">
-        <v>sql_fuzz_23_lejh@test.com</v>
+        <v>sql_fuzz_23_d1zm@test.com</v>
       </c>
       <c r="D33" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="34">
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="35">
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="36">
@@ -1641,7 +1641,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="37">
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="39">
@@ -1716,7 +1716,7 @@
         <v>Fuzzing with database query snippets (29)</v>
       </c>
       <c r="C39" t="str">
-        <v>sql_fuzz_29_9yu7@test.com</v>
+        <v>sql_fuzz_29_vgug@test.com</v>
       </c>
       <c r="D39" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1737,7 +1737,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="40">
@@ -1769,7 +1769,7 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="41">
@@ -1801,7 +1801,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
     </row>
     <row r="42">
@@ -1833,7 +1833,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="43">
@@ -1865,7 +1865,7 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="44">
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="45">
@@ -1908,7 +1908,7 @@
         <v>Fuzzing with database query snippets (35)</v>
       </c>
       <c r="C45" t="str">
-        <v>sql_fuzz_35_hgyl@test.com</v>
+        <v>sql_fuzz_35_4kff@test.com</v>
       </c>
       <c r="D45" t="str">
         <v>'; DROP TABLE u...</v>
@@ -1929,7 +1929,7 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="46">
@@ -1961,7 +1961,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="47">
@@ -1993,7 +1993,7 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="48">
@@ -2025,7 +2025,7 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="49">
@@ -2057,7 +2057,7 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="50">
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="51">
@@ -2100,7 +2100,7 @@
         <v>Fuzzing with database query snippets (41)</v>
       </c>
       <c r="C51" t="str">
-        <v>sql_fuzz_41_d57b@test.com</v>
+        <v>sql_fuzz_41_2wwx@test.com</v>
       </c>
       <c r="D51" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="52">
@@ -2153,7 +2153,7 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="53">
@@ -2185,7 +2185,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="54">
@@ -2217,7 +2217,7 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="55">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="56">
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="57">
@@ -2292,7 +2292,7 @@
         <v>Fuzzing with database query snippets (47)</v>
       </c>
       <c r="C57" t="str">
-        <v>sql_fuzz_47_pqii@test.com</v>
+        <v>sql_fuzz_47_xdim@test.com</v>
       </c>
       <c r="D57" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="58">
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="59">
@@ -2377,7 +2377,7 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="60">
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="61">
@@ -2441,7 +2441,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
     </row>
     <row r="62">
@@ -2473,7 +2473,7 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="63">
@@ -2484,7 +2484,7 @@
         <v>Fuzzing with database query snippets (53)</v>
       </c>
       <c r="C63" t="str">
-        <v>sql_fuzz_53_60jd@test.com</v>
+        <v>sql_fuzz_53_qb50@test.com</v>
       </c>
       <c r="D63" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2505,7 +2505,7 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="64">
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="65">
@@ -2569,7 +2569,7 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="66">
@@ -2601,7 +2601,7 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="67">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="68">
@@ -2665,7 +2665,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="69">
@@ -2676,7 +2676,7 @@
         <v>Fuzzing with database query snippets (59)</v>
       </c>
       <c r="C69" t="str">
-        <v>sql_fuzz_59_2cmq@test.com</v>
+        <v>sql_fuzz_59_1x3r@test.com</v>
       </c>
       <c r="D69" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2697,7 +2697,7 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="70">
@@ -2729,7 +2729,7 @@
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="71">
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="72">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="73">
@@ -2825,7 +2825,7 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="74">
@@ -2857,7 +2857,7 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="75">
@@ -2868,7 +2868,7 @@
         <v>Fuzzing with database query snippets (65)</v>
       </c>
       <c r="C75" t="str">
-        <v>sql_fuzz_65_mqrx@test.com</v>
+        <v>sql_fuzz_65_ur78@test.com</v>
       </c>
       <c r="D75" t="str">
         <v>'; DROP TABLE u...</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="76">
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="77">
@@ -2953,7 +2953,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="78">
@@ -2985,7 +2985,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="79">
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="80">
@@ -3049,7 +3049,7 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="81">
@@ -3060,7 +3060,7 @@
         <v>Fuzzing with database query snippets (71)</v>
       </c>
       <c r="C81" t="str">
-        <v>sql_fuzz_71_84x1@test.com</v>
+        <v>sql_fuzz_71_yis8@test.com</v>
       </c>
       <c r="D81" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3081,7 +3081,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="82">
@@ -3113,7 +3113,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="83">
@@ -3145,7 +3145,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="84">
@@ -3177,7 +3177,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="85">
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="86">
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="87">
@@ -3252,7 +3252,7 @@
         <v>Fuzzing with database query snippets (77)</v>
       </c>
       <c r="C87" t="str">
-        <v>sql_fuzz_77_mq2u@test.com</v>
+        <v>sql_fuzz_77_dvos@test.com</v>
       </c>
       <c r="D87" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3273,7 +3273,7 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="88">
@@ -3305,7 +3305,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
     </row>
     <row r="89">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="90">
@@ -3369,7 +3369,7 @@
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="91">
@@ -3401,7 +3401,7 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="92">
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="93">
@@ -3444,7 +3444,7 @@
         <v>Fuzzing with database query snippets (83)</v>
       </c>
       <c r="C93" t="str">
-        <v>sql_fuzz_83_xwm1@test.com</v>
+        <v>sql_fuzz_83_pzim@test.com</v>
       </c>
       <c r="D93" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="94">
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="95">
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="96">
@@ -3561,7 +3561,7 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="97">
@@ -3593,7 +3593,7 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="98">
@@ -3625,7 +3625,7 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="99">
@@ -3636,7 +3636,7 @@
         <v>Fuzzing with database query snippets (89)</v>
       </c>
       <c r="C99" t="str">
-        <v>sql_fuzz_89_kdfi@test.com</v>
+        <v>sql_fuzz_89_oexf@test.com</v>
       </c>
       <c r="D99" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3657,7 +3657,7 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="100">
@@ -3689,7 +3689,7 @@
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="101">
@@ -3721,7 +3721,7 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="102">
@@ -3753,7 +3753,7 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="103">
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="104">
@@ -3817,7 +3817,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="105">
@@ -3828,7 +3828,7 @@
         <v>Fuzzing with database query snippets (95)</v>
       </c>
       <c r="C105" t="str">
-        <v>sql_fuzz_95_shl5@test.com</v>
+        <v>sql_fuzz_95_rhpl@test.com</v>
       </c>
       <c r="D105" t="str">
         <v>'; DROP TABLE u...</v>
@@ -3849,7 +3849,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="106">
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="107">
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="108">
@@ -3945,7 +3945,7 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="109">
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="110">
@@ -4009,7 +4009,7 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="111">
@@ -4020,7 +4020,7 @@
         <v>Fuzzing with database query snippets (101)</v>
       </c>
       <c r="C111" t="str">
-        <v>sql_fuzz_101_vecw@test.com</v>
+        <v>sql_fuzz_101_gset@test.com</v>
       </c>
       <c r="D111" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4041,7 +4041,7 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
     </row>
     <row r="112">
@@ -4073,7 +4073,7 @@
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="113">
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="114">
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="115">
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="116">
@@ -4201,7 +4201,7 @@
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="117">
@@ -4212,7 +4212,7 @@
         <v>Fuzzing with database query snippets (107)</v>
       </c>
       <c r="C117" t="str">
-        <v>sql_fuzz_107_zjt7@test.com</v>
+        <v>sql_fuzz_107_lbq3@test.com</v>
       </c>
       <c r="D117" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4233,7 +4233,7 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="118">
@@ -4265,7 +4265,7 @@
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="119">
@@ -4297,7 +4297,7 @@
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="120">
@@ -4329,7 +4329,7 @@
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="121">
@@ -4361,7 +4361,7 @@
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="122">
@@ -4393,7 +4393,7 @@
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="123">
@@ -4404,7 +4404,7 @@
         <v>Fuzzing with database query snippets (113)</v>
       </c>
       <c r="C123" t="str">
-        <v>sql_fuzz_113_jblu@test.com</v>
+        <v>sql_fuzz_113_ocsi@test.com</v>
       </c>
       <c r="D123" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="124">
@@ -4457,7 +4457,7 @@
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="125">
@@ -4489,7 +4489,7 @@
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="126">
@@ -4521,7 +4521,7 @@
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="127">
@@ -4553,7 +4553,7 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="128">
@@ -4585,7 +4585,7 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="129">
@@ -4596,7 +4596,7 @@
         <v>Fuzzing with database query snippets (119)</v>
       </c>
       <c r="C129" t="str">
-        <v>sql_fuzz_119_hzoq@test.com</v>
+        <v>sql_fuzz_119_e7p4@test.com</v>
       </c>
       <c r="D129" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4617,7 +4617,7 @@
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="130">
@@ -4649,7 +4649,7 @@
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="131">
@@ -4681,7 +4681,7 @@
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="132">
@@ -4713,7 +4713,7 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="133">
@@ -4745,7 +4745,7 @@
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="134">
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="135">
@@ -4788,7 +4788,7 @@
         <v>Fuzzing with database query snippets (125)</v>
       </c>
       <c r="C135" t="str">
-        <v>sql_fuzz_125_9cc1@test.com</v>
+        <v>sql_fuzz_125_qusa@test.com</v>
       </c>
       <c r="D135" t="str">
         <v>'; DROP TABLE u...</v>
@@ -4809,7 +4809,7 @@
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="136">
@@ -4841,7 +4841,7 @@
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="137">
@@ -4873,7 +4873,7 @@
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="138">
@@ -4905,7 +4905,7 @@
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="139">
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="140">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="141">
@@ -4980,7 +4980,7 @@
         <v>Fuzzing with database query snippets (131)</v>
       </c>
       <c r="C141" t="str">
-        <v>sql_fuzz_131_u1ct@test.com</v>
+        <v>sql_fuzz_131_yur5@test.com</v>
       </c>
       <c r="D141" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5001,7 +5001,7 @@
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
     </row>
     <row r="142">
@@ -5033,7 +5033,7 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="143">
@@ -5065,7 +5065,7 @@
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="144">
@@ -5097,7 +5097,7 @@
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="145">
@@ -5129,7 +5129,7 @@
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="146">
@@ -5161,7 +5161,7 @@
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="147">
@@ -5172,7 +5172,7 @@
         <v>Fuzzing with database query snippets (137)</v>
       </c>
       <c r="C147" t="str">
-        <v>sql_fuzz_137_ucyq@test.com</v>
+        <v>sql_fuzz_137_zmx9@test.com</v>
       </c>
       <c r="D147" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5193,7 +5193,7 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="148">
@@ -5225,7 +5225,7 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="149">
@@ -5257,7 +5257,7 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="150">
@@ -5289,7 +5289,7 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="151">
@@ -5321,7 +5321,7 @@
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="152">
@@ -5353,7 +5353,7 @@
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="153">
@@ -5364,7 +5364,7 @@
         <v>Fuzzing with database query snippets (143)</v>
       </c>
       <c r="C153" t="str">
-        <v>sql_fuzz_143_uu2t@test.com</v>
+        <v>sql_fuzz_143_zhh9@test.com</v>
       </c>
       <c r="D153" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5385,7 +5385,7 @@
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="154">
@@ -5417,7 +5417,7 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="155">
@@ -5449,7 +5449,7 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="156">
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="157">
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="158">
@@ -5545,7 +5545,7 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="159">
@@ -5556,7 +5556,7 @@
         <v>Fuzzing with database query snippets (149)</v>
       </c>
       <c r="C159" t="str">
-        <v>sql_fuzz_149_th4k@test.com</v>
+        <v>sql_fuzz_149_jgy6@test.com</v>
       </c>
       <c r="D159" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="160">
@@ -5609,7 +5609,7 @@
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="161">
@@ -5641,7 +5641,7 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="162">
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="163">
@@ -5705,7 +5705,7 @@
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="164">
@@ -5737,7 +5737,7 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="165">
@@ -5748,7 +5748,7 @@
         <v>Fuzzing with database query snippets (155)</v>
       </c>
       <c r="C165" t="str">
-        <v>sql_fuzz_155_1era@test.com</v>
+        <v>sql_fuzz_155_lp36@test.com</v>
       </c>
       <c r="D165" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="166">
@@ -5801,7 +5801,7 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="167">
@@ -5833,7 +5833,7 @@
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="168">
@@ -5865,7 +5865,7 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="169">
@@ -5897,7 +5897,7 @@
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="170">
@@ -5929,7 +5929,7 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
     </row>
     <row r="171">
@@ -5940,7 +5940,7 @@
         <v>Fuzzing with database query snippets (161)</v>
       </c>
       <c r="C171" t="str">
-        <v>sql_fuzz_161_bvsn@test.com</v>
+        <v>sql_fuzz_161_m14u@test.com</v>
       </c>
       <c r="D171" t="str">
         <v>'; DROP TABLE u...</v>
@@ -5961,7 +5961,7 @@
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="172">
@@ -5993,7 +5993,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="173">
@@ -6025,7 +6025,7 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="174">
@@ -6057,7 +6057,7 @@
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="175">
@@ -6089,7 +6089,7 @@
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="176">
@@ -6121,7 +6121,7 @@
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="177">
@@ -6132,7 +6132,7 @@
         <v>Fuzzing with database query snippets (167)</v>
       </c>
       <c r="C177" t="str">
-        <v>sql_fuzz_167_xmj1@test.com</v>
+        <v>sql_fuzz_167_eldz@test.com</v>
       </c>
       <c r="D177" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6153,7 +6153,7 @@
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="178">
@@ -6185,7 +6185,7 @@
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="179">
@@ -6217,7 +6217,7 @@
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="180">
@@ -6249,7 +6249,7 @@
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="181">
@@ -6281,7 +6281,7 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="182">
@@ -6313,7 +6313,7 @@
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="183">
@@ -6324,7 +6324,7 @@
         <v>Fuzzing with database query snippets (173)</v>
       </c>
       <c r="C183" t="str">
-        <v>sql_fuzz_173_w1re@test.com</v>
+        <v>sql_fuzz_173_3f1u@test.com</v>
       </c>
       <c r="D183" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6345,7 +6345,7 @@
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="184">
@@ -6377,7 +6377,7 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="185">
@@ -6409,7 +6409,7 @@
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="186">
@@ -6441,7 +6441,7 @@
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="187">
@@ -6473,7 +6473,7 @@
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="188">
@@ -6505,7 +6505,7 @@
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="189">
@@ -6516,7 +6516,7 @@
         <v>Fuzzing with database query snippets (179)</v>
       </c>
       <c r="C189" t="str">
-        <v>sql_fuzz_179_h79s@test.com</v>
+        <v>sql_fuzz_179_3xba@test.com</v>
       </c>
       <c r="D189" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6537,7 +6537,7 @@
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="190">
@@ -6569,7 +6569,7 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="191">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="192">
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="193">
@@ -6665,7 +6665,7 @@
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="194">
@@ -6697,7 +6697,7 @@
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="195">
@@ -6708,7 +6708,7 @@
         <v>Fuzzing with database query snippets (185)</v>
       </c>
       <c r="C195" t="str">
-        <v>sql_fuzz_185_9wsf@test.com</v>
+        <v>sql_fuzz_185_1lgz@test.com</v>
       </c>
       <c r="D195" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6729,7 +6729,7 @@
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="196">
@@ -6761,7 +6761,7 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="197">
@@ -6793,7 +6793,7 @@
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="198">
@@ -6825,7 +6825,7 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="199">
@@ -6857,7 +6857,7 @@
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="200">
@@ -6889,7 +6889,7 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="201">
@@ -6900,7 +6900,7 @@
         <v>Fuzzing with database query snippets (191)</v>
       </c>
       <c r="C201" t="str">
-        <v>sql_fuzz_191_6ol7@test.com</v>
+        <v>sql_fuzz_191_wwmv@test.com</v>
       </c>
       <c r="D201" t="str">
         <v>'; DROP TABLE u...</v>
@@ -6921,7 +6921,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
     </row>
     <row r="202">
@@ -6953,7 +6953,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="203">
@@ -6985,7 +6985,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="204">
@@ -7017,7 +7017,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="205">
@@ -7049,7 +7049,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="206">
@@ -7081,7 +7081,7 @@
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="207">
@@ -7092,7 +7092,7 @@
         <v>Fuzzing with database query snippets (197)</v>
       </c>
       <c r="C207" t="str">
-        <v>sql_fuzz_197_8wzy@test.com</v>
+        <v>sql_fuzz_197_94p7@test.com</v>
       </c>
       <c r="D207" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7113,7 +7113,7 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="208">
@@ -7145,7 +7145,7 @@
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="209">
@@ -7177,7 +7177,7 @@
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="210">
@@ -7209,7 +7209,7 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="211">
@@ -7241,7 +7241,7 @@
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="212">
@@ -7273,7 +7273,7 @@
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="213">
@@ -7284,7 +7284,7 @@
         <v>Fuzzing with database query snippets (203)</v>
       </c>
       <c r="C213" t="str">
-        <v>sql_fuzz_203_ozk6@test.com</v>
+        <v>sql_fuzz_203_xw73@test.com</v>
       </c>
       <c r="D213" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7305,7 +7305,7 @@
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="214">
@@ -7337,7 +7337,7 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="215">
@@ -7369,7 +7369,7 @@
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="216">
@@ -7401,7 +7401,7 @@
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="217">
@@ -7433,7 +7433,7 @@
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="218">
@@ -7465,7 +7465,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="219">
@@ -7476,7 +7476,7 @@
         <v>Fuzzing with database query snippets (209)</v>
       </c>
       <c r="C219" t="str">
-        <v>sql_fuzz_209_fb2x@test.com</v>
+        <v>sql_fuzz_209_g9mc@test.com</v>
       </c>
       <c r="D219" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7497,7 +7497,7 @@
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="220">
@@ -7529,7 +7529,7 @@
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="221">
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="222">
@@ -7593,7 +7593,7 @@
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="223">
@@ -7625,7 +7625,7 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="224">
@@ -7657,7 +7657,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="225">
@@ -7668,7 +7668,7 @@
         <v>Fuzzing with database query snippets (215)</v>
       </c>
       <c r="C225" t="str">
-        <v>sql_fuzz_215_sglk@test.com</v>
+        <v>sql_fuzz_215_6squ@test.com</v>
       </c>
       <c r="D225" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7689,7 +7689,7 @@
         <v/>
       </c>
       <c r="J225" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="226">
@@ -7721,7 +7721,7 @@
         <v/>
       </c>
       <c r="J226" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="227">
@@ -7753,7 +7753,7 @@
         <v/>
       </c>
       <c r="J227" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="228">
@@ -7785,7 +7785,7 @@
         <v/>
       </c>
       <c r="J228" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="229">
@@ -7817,7 +7817,7 @@
         <v/>
       </c>
       <c r="J229" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="230">
@@ -7849,7 +7849,7 @@
         <v/>
       </c>
       <c r="J230" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="231">
@@ -7860,7 +7860,7 @@
         <v>Fuzzing with database query snippets (221)</v>
       </c>
       <c r="C231" t="str">
-        <v>sql_fuzz_221_a88i@test.com</v>
+        <v>sql_fuzz_221_3gbt@test.com</v>
       </c>
       <c r="D231" t="str">
         <v>'; DROP TABLE u...</v>
@@ -7881,7 +7881,7 @@
         <v/>
       </c>
       <c r="J231" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="232">
@@ -7913,7 +7913,7 @@
         <v/>
       </c>
       <c r="J232" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="233">
@@ -7945,7 +7945,7 @@
         <v/>
       </c>
       <c r="J233" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="234">
@@ -7977,7 +7977,7 @@
         <v/>
       </c>
       <c r="J234" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="235">
@@ -8009,7 +8009,7 @@
         <v/>
       </c>
       <c r="J235" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="236">
@@ -8041,7 +8041,7 @@
         <v/>
       </c>
       <c r="J236" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="237">
@@ -8052,7 +8052,7 @@
         <v>Fuzzing with database query snippets (227)</v>
       </c>
       <c r="C237" t="str">
-        <v>sql_fuzz_227_yxe5@test.com</v>
+        <v>sql_fuzz_227_fjr6@test.com</v>
       </c>
       <c r="D237" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8073,7 +8073,7 @@
         <v/>
       </c>
       <c r="J237" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="238">
@@ -8105,7 +8105,7 @@
         <v/>
       </c>
       <c r="J238" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="239">
@@ -8137,7 +8137,7 @@
         <v/>
       </c>
       <c r="J239" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="240">
@@ -8169,7 +8169,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="241">
@@ -8201,7 +8201,7 @@
         <v/>
       </c>
       <c r="J241" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
     </row>
     <row r="242">
@@ -8233,7 +8233,7 @@
         <v/>
       </c>
       <c r="J242" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="243">
@@ -8244,7 +8244,7 @@
         <v>Fuzzing with database query snippets (233)</v>
       </c>
       <c r="C243" t="str">
-        <v>sql_fuzz_233_sb07@test.com</v>
+        <v>sql_fuzz_233_jvoa@test.com</v>
       </c>
       <c r="D243" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8265,7 +8265,7 @@
         <v/>
       </c>
       <c r="J243" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="244">
@@ -8297,7 +8297,7 @@
         <v/>
       </c>
       <c r="J244" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="245">
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="J245" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="246">
@@ -8361,7 +8361,7 @@
         <v/>
       </c>
       <c r="J246" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="247">
@@ -8393,7 +8393,7 @@
         <v/>
       </c>
       <c r="J247" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="248">
@@ -8425,7 +8425,7 @@
         <v/>
       </c>
       <c r="J248" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="249">
@@ -8436,7 +8436,7 @@
         <v>Fuzzing with database query snippets (239)</v>
       </c>
       <c r="C249" t="str">
-        <v>sql_fuzz_239_1yxg@test.com</v>
+        <v>sql_fuzz_239_enwt@test.com</v>
       </c>
       <c r="D249" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8457,7 +8457,7 @@
         <v/>
       </c>
       <c r="J249" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="250">
@@ -8489,7 +8489,7 @@
         <v/>
       </c>
       <c r="J250" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="251">
@@ -8521,7 +8521,7 @@
         <v/>
       </c>
       <c r="J251" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="252">
@@ -8553,7 +8553,7 @@
         <v/>
       </c>
       <c r="J252" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="253">
@@ -8585,7 +8585,7 @@
         <v/>
       </c>
       <c r="J253" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="254">
@@ -8617,7 +8617,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="255">
@@ -8628,7 +8628,7 @@
         <v>Fuzzing with database query snippets (245)</v>
       </c>
       <c r="C255" t="str">
-        <v>sql_fuzz_245_58dg@test.com</v>
+        <v>sql_fuzz_245_eqq0@test.com</v>
       </c>
       <c r="D255" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8649,7 +8649,7 @@
         <v/>
       </c>
       <c r="J255" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="256">
@@ -8681,7 +8681,7 @@
         <v/>
       </c>
       <c r="J256" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="257">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="J257" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="258">
@@ -8745,7 +8745,7 @@
         <v/>
       </c>
       <c r="J258" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="259">
@@ -8777,7 +8777,7 @@
         <v/>
       </c>
       <c r="J259" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="260">
@@ -8809,7 +8809,7 @@
         <v/>
       </c>
       <c r="J260" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="261">
@@ -8820,7 +8820,7 @@
         <v>Fuzzing with database query snippets (251)</v>
       </c>
       <c r="C261" t="str">
-        <v>sql_fuzz_251_7ddy@test.com</v>
+        <v>sql_fuzz_251_6z0i@test.com</v>
       </c>
       <c r="D261" t="str">
         <v>'; DROP TABLE u...</v>
@@ -8841,7 +8841,7 @@
         <v/>
       </c>
       <c r="J261" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="262">
@@ -8873,7 +8873,7 @@
         <v/>
       </c>
       <c r="J262" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="263">
@@ -8905,7 +8905,7 @@
         <v/>
       </c>
       <c r="J263" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="264">
@@ -8937,7 +8937,7 @@
         <v/>
       </c>
       <c r="J264" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="265">
@@ -8969,7 +8969,7 @@
         <v/>
       </c>
       <c r="J265" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="266">
@@ -9001,7 +9001,7 @@
         <v/>
       </c>
       <c r="J266" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="267">
@@ -9012,7 +9012,7 @@
         <v>Fuzzing with database query snippets (257)</v>
       </c>
       <c r="C267" t="str">
-        <v>sql_fuzz_257_6bde@test.com</v>
+        <v>sql_fuzz_257_7zc4@test.com</v>
       </c>
       <c r="D267" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9033,7 +9033,7 @@
         <v/>
       </c>
       <c r="J267" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="268">
@@ -9065,7 +9065,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="269">
@@ -9097,7 +9097,7 @@
         <v/>
       </c>
       <c r="J269" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="270">
@@ -9129,7 +9129,7 @@
         <v/>
       </c>
       <c r="J270" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="271">
@@ -9161,7 +9161,7 @@
         <v/>
       </c>
       <c r="J271" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="272">
@@ -9193,7 +9193,7 @@
         <v/>
       </c>
       <c r="J272" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="273">
@@ -9204,7 +9204,7 @@
         <v>Fuzzing with database query snippets (263)</v>
       </c>
       <c r="C273" t="str">
-        <v>sql_fuzz_263_w2s0@test.com</v>
+        <v>sql_fuzz_263_k0ki@test.com</v>
       </c>
       <c r="D273" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9225,7 +9225,7 @@
         <v/>
       </c>
       <c r="J273" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="274">
@@ -9257,7 +9257,7 @@
         <v/>
       </c>
       <c r="J274" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="275">
@@ -9289,7 +9289,7 @@
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="276">
@@ -9321,7 +9321,7 @@
         <v/>
       </c>
       <c r="J276" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="277">
@@ -9353,7 +9353,7 @@
         <v/>
       </c>
       <c r="J277" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="278">
@@ -9385,7 +9385,7 @@
         <v/>
       </c>
       <c r="J278" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="279">
@@ -9396,7 +9396,7 @@
         <v>Fuzzing with database query snippets (269)</v>
       </c>
       <c r="C279" t="str">
-        <v>sql_fuzz_269_4wye@test.com</v>
+        <v>sql_fuzz_269_nnp6@test.com</v>
       </c>
       <c r="D279" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9417,7 +9417,7 @@
         <v/>
       </c>
       <c r="J279" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="280">
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="J280" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="281">
@@ -9481,7 +9481,7 @@
         <v/>
       </c>
       <c r="J281" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
     </row>
     <row r="282">
@@ -9513,7 +9513,7 @@
         <v/>
       </c>
       <c r="J282" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="283">
@@ -9545,7 +9545,7 @@
         <v/>
       </c>
       <c r="J283" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="284">
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="J284" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="285">
@@ -9588,7 +9588,7 @@
         <v>Fuzzing with database query snippets (275)</v>
       </c>
       <c r="C285" t="str">
-        <v>sql_fuzz_275_k7j0@test.com</v>
+        <v>sql_fuzz_275_adlj@test.com</v>
       </c>
       <c r="D285" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9609,7 +9609,7 @@
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="286">
@@ -9641,7 +9641,7 @@
         <v/>
       </c>
       <c r="J286" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="287">
@@ -9673,7 +9673,7 @@
         <v/>
       </c>
       <c r="J287" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="288">
@@ -9705,7 +9705,7 @@
         <v/>
       </c>
       <c r="J288" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="289">
@@ -9737,7 +9737,7 @@
         <v/>
       </c>
       <c r="J289" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="290">
@@ -9769,7 +9769,7 @@
         <v/>
       </c>
       <c r="J290" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="291">
@@ -9780,7 +9780,7 @@
         <v>Fuzzing with database query snippets (281)</v>
       </c>
       <c r="C291" t="str">
-        <v>sql_fuzz_281_bq3h@test.com</v>
+        <v>sql_fuzz_281_l97a@test.com</v>
       </c>
       <c r="D291" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9801,7 +9801,7 @@
         <v/>
       </c>
       <c r="J291" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="292">
@@ -9833,7 +9833,7 @@
         <v/>
       </c>
       <c r="J292" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="293">
@@ -9865,7 +9865,7 @@
         <v/>
       </c>
       <c r="J293" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="294">
@@ -9897,7 +9897,7 @@
         <v/>
       </c>
       <c r="J294" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="295">
@@ -9929,7 +9929,7 @@
         <v/>
       </c>
       <c r="J295" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="296">
@@ -9961,7 +9961,7 @@
         <v/>
       </c>
       <c r="J296" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="297">
@@ -9972,7 +9972,7 @@
         <v>Fuzzing with database query snippets (287)</v>
       </c>
       <c r="C297" t="str">
-        <v>sql_fuzz_287_8ip1@test.com</v>
+        <v>sql_fuzz_287_3umx@test.com</v>
       </c>
       <c r="D297" t="str">
         <v>'; DROP TABLE u...</v>
@@ -9993,7 +9993,7 @@
         <v/>
       </c>
       <c r="J297" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="298">
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="J298" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="299">
@@ -10057,7 +10057,7 @@
         <v/>
       </c>
       <c r="J299" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="300">
@@ -10089,7 +10089,7 @@
         <v/>
       </c>
       <c r="J300" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="301">
@@ -10121,7 +10121,7 @@
         <v/>
       </c>
       <c r="J301" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="302">
@@ -10153,7 +10153,7 @@
         <v/>
       </c>
       <c r="J302" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="303">
@@ -10164,7 +10164,7 @@
         <v>Fuzzing with database query snippets (293)</v>
       </c>
       <c r="C303" t="str">
-        <v>sql_fuzz_293_0ynq@test.com</v>
+        <v>sql_fuzz_293_paua@test.com</v>
       </c>
       <c r="D303" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10185,7 +10185,7 @@
         <v/>
       </c>
       <c r="J303" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="304">
@@ -10217,7 +10217,7 @@
         <v/>
       </c>
       <c r="J304" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="305">
@@ -10249,7 +10249,7 @@
         <v/>
       </c>
       <c r="J305" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="306">
@@ -10281,7 +10281,7 @@
         <v/>
       </c>
       <c r="J306" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="307">
@@ -10313,7 +10313,7 @@
         <v/>
       </c>
       <c r="J307" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="308">
@@ -10345,7 +10345,7 @@
         <v/>
       </c>
       <c r="J308" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="309">
@@ -10356,7 +10356,7 @@
         <v>Fuzzing with database query snippets (299)</v>
       </c>
       <c r="C309" t="str">
-        <v>sql_fuzz_299_hzd4@test.com</v>
+        <v>sql_fuzz_299_6r3k@test.com</v>
       </c>
       <c r="D309" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10377,7 +10377,7 @@
         <v/>
       </c>
       <c r="J309" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="310">
@@ -10409,7 +10409,7 @@
         <v/>
       </c>
       <c r="J310" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="311">
@@ -10441,7 +10441,7 @@
         <v/>
       </c>
       <c r="J311" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
     </row>
     <row r="312">
@@ -10473,7 +10473,7 @@
         <v/>
       </c>
       <c r="J312" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="313">
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="J313" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="314">
@@ -10537,7 +10537,7 @@
         <v/>
       </c>
       <c r="J314" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="315">
@@ -10548,7 +10548,7 @@
         <v>Fuzzing with database query snippets (305)</v>
       </c>
       <c r="C315" t="str">
-        <v>sql_fuzz_305_gkmq@test.com</v>
+        <v>sql_fuzz_305_y7pf@test.com</v>
       </c>
       <c r="D315" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10569,7 +10569,7 @@
         <v/>
       </c>
       <c r="J315" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="316">
@@ -10601,7 +10601,7 @@
         <v/>
       </c>
       <c r="J316" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="317">
@@ -10633,7 +10633,7 @@
         <v/>
       </c>
       <c r="J317" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="318">
@@ -10665,7 +10665,7 @@
         <v/>
       </c>
       <c r="J318" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="319">
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="J319" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="320">
@@ -10729,7 +10729,7 @@
         <v/>
       </c>
       <c r="J320" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="321">
@@ -10740,7 +10740,7 @@
         <v>Fuzzing with database query snippets (311)</v>
       </c>
       <c r="C321" t="str">
-        <v>sql_fuzz_311_kz2a@test.com</v>
+        <v>sql_fuzz_311_z4q0@test.com</v>
       </c>
       <c r="D321" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10761,7 +10761,7 @@
         <v/>
       </c>
       <c r="J321" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="322">
@@ -10793,7 +10793,7 @@
         <v/>
       </c>
       <c r="J322" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
     </row>
     <row r="323">
@@ -10825,7 +10825,7 @@
         <v/>
       </c>
       <c r="J323" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="324">
@@ -10857,7 +10857,7 @@
         <v/>
       </c>
       <c r="J324" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="325">
@@ -10889,7 +10889,7 @@
         <v/>
       </c>
       <c r="J325" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="326">
@@ -10921,7 +10921,7 @@
         <v/>
       </c>
       <c r="J326" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="327">
@@ -10932,7 +10932,7 @@
         <v>Fuzzing with database query snippets (317)</v>
       </c>
       <c r="C327" t="str">
-        <v>sql_fuzz_317_2qde@test.com</v>
+        <v>sql_fuzz_317_saq9@test.com</v>
       </c>
       <c r="D327" t="str">
         <v>'; DROP TABLE u...</v>
@@ -10953,7 +10953,7 @@
         <v/>
       </c>
       <c r="J327" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="328">
@@ -10985,7 +10985,7 @@
         <v/>
       </c>
       <c r="J328" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="329">
@@ -11017,7 +11017,7 @@
         <v/>
       </c>
       <c r="J329" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="330">
@@ -11049,7 +11049,7 @@
         <v/>
       </c>
       <c r="J330" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="331">
@@ -11081,7 +11081,7 @@
         <v/>
       </c>
       <c r="J331" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="332">
@@ -11113,7 +11113,7 @@
         <v/>
       </c>
       <c r="J332" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="333">
@@ -11124,7 +11124,7 @@
         <v>Fuzzing with database query snippets (323)</v>
       </c>
       <c r="C333" t="str">
-        <v>sql_fuzz_323_usri@test.com</v>
+        <v>sql_fuzz_323_g6w2@test.com</v>
       </c>
       <c r="D333" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11145,7 +11145,7 @@
         <v/>
       </c>
       <c r="J333" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="334">
@@ -11177,7 +11177,7 @@
         <v/>
       </c>
       <c r="J334" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="335">
@@ -11209,7 +11209,7 @@
         <v/>
       </c>
       <c r="J335" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="336">
@@ -11241,7 +11241,7 @@
         <v/>
       </c>
       <c r="J336" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="337">
@@ -11273,7 +11273,7 @@
         <v/>
       </c>
       <c r="J337" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="338">
@@ -11305,7 +11305,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="339">
@@ -11316,7 +11316,7 @@
         <v>Fuzzing with database query snippets (329)</v>
       </c>
       <c r="C339" t="str">
-        <v>sql_fuzz_329_6vun@test.com</v>
+        <v>sql_fuzz_329_drec@test.com</v>
       </c>
       <c r="D339" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11337,7 +11337,7 @@
         <v/>
       </c>
       <c r="J339" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="340">
@@ -11369,7 +11369,7 @@
         <v/>
       </c>
       <c r="J340" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="341">
@@ -11401,7 +11401,7 @@
         <v/>
       </c>
       <c r="J341" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="342">
@@ -11433,7 +11433,7 @@
         <v/>
       </c>
       <c r="J342" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="343">
@@ -11465,7 +11465,7 @@
         <v/>
       </c>
       <c r="J343" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="344">
@@ -11497,7 +11497,7 @@
         <v/>
       </c>
       <c r="J344" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="345">
@@ -11508,7 +11508,7 @@
         <v>Fuzzing with database query snippets (335)</v>
       </c>
       <c r="C345" t="str">
-        <v>sql_fuzz_335_6b1f@test.com</v>
+        <v>sql_fuzz_335_zu0a@test.com</v>
       </c>
       <c r="D345" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11529,7 +11529,7 @@
         <v/>
       </c>
       <c r="J345" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="346">
@@ -11561,7 +11561,7 @@
         <v/>
       </c>
       <c r="J346" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="347">
@@ -11593,7 +11593,7 @@
         <v/>
       </c>
       <c r="J347" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="348">
@@ -11625,7 +11625,7 @@
         <v/>
       </c>
       <c r="J348" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="349">
@@ -11657,7 +11657,7 @@
         <v/>
       </c>
       <c r="J349" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="350">
@@ -11689,7 +11689,7 @@
         <v/>
       </c>
       <c r="J350" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="351">
@@ -11700,7 +11700,7 @@
         <v>Fuzzing with database query snippets (341)</v>
       </c>
       <c r="C351" t="str">
-        <v>sql_fuzz_341_tsqw@test.com</v>
+        <v>sql_fuzz_341_k18q@test.com</v>
       </c>
       <c r="D351" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="J351" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="352">
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="J352" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="353">
@@ -11785,7 +11785,7 @@
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="354">
@@ -11817,7 +11817,7 @@
         <v/>
       </c>
       <c r="J354" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="355">
@@ -11849,7 +11849,7 @@
         <v/>
       </c>
       <c r="J355" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="356">
@@ -11881,7 +11881,7 @@
         <v/>
       </c>
       <c r="J356" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="357">
@@ -11892,7 +11892,7 @@
         <v>Fuzzing with database query snippets (347)</v>
       </c>
       <c r="C357" t="str">
-        <v>sql_fuzz_347_x67k@test.com</v>
+        <v>sql_fuzz_347_hyzp@test.com</v>
       </c>
       <c r="D357" t="str">
         <v>'; DROP TABLE u...</v>
@@ -11913,7 +11913,7 @@
         <v/>
       </c>
       <c r="J357" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="358">
@@ -11945,7 +11945,7 @@
         <v/>
       </c>
       <c r="J358" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="359">
@@ -11977,7 +11977,7 @@
         <v/>
       </c>
       <c r="J359" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="360">
@@ -12009,7 +12009,7 @@
         <v/>
       </c>
       <c r="J360" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="361">
@@ -12041,7 +12041,7 @@
         <v/>
       </c>
       <c r="J361" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
     </row>
     <row r="362">
@@ -12073,7 +12073,7 @@
         <v/>
       </c>
       <c r="J362" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="363">
@@ -12084,7 +12084,7 @@
         <v>Fuzzing with database query snippets (353)</v>
       </c>
       <c r="C363" t="str">
-        <v>sql_fuzz_353_384b@test.com</v>
+        <v>sql_fuzz_353_szqb@test.com</v>
       </c>
       <c r="D363" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12105,7 +12105,7 @@
         <v/>
       </c>
       <c r="J363" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="364">
@@ -12137,7 +12137,7 @@
         <v/>
       </c>
       <c r="J364" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="365">
@@ -12169,7 +12169,7 @@
         <v/>
       </c>
       <c r="J365" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="366">
@@ -12201,7 +12201,7 @@
         <v/>
       </c>
       <c r="J366" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="367">
@@ -12233,7 +12233,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="368">
@@ -12265,7 +12265,7 @@
         <v/>
       </c>
       <c r="J368" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="369">
@@ -12276,7 +12276,7 @@
         <v>Fuzzing with database query snippets (359)</v>
       </c>
       <c r="C369" t="str">
-        <v>sql_fuzz_359_7umz@test.com</v>
+        <v>sql_fuzz_359_zlkp@test.com</v>
       </c>
       <c r="D369" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12297,7 +12297,7 @@
         <v/>
       </c>
       <c r="J369" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="370">
@@ -12329,7 +12329,7 @@
         <v/>
       </c>
       <c r="J370" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="371">
@@ -12361,7 +12361,7 @@
         <v/>
       </c>
       <c r="J371" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="372">
@@ -12393,7 +12393,7 @@
         <v/>
       </c>
       <c r="J372" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="373">
@@ -12425,7 +12425,7 @@
         <v/>
       </c>
       <c r="J373" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="374">
@@ -12457,7 +12457,7 @@
         <v/>
       </c>
       <c r="J374" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="375">
@@ -12468,7 +12468,7 @@
         <v>Fuzzing with database query snippets (365)</v>
       </c>
       <c r="C375" t="str">
-        <v>sql_fuzz_365_022m@test.com</v>
+        <v>sql_fuzz_365_3qan@test.com</v>
       </c>
       <c r="D375" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12489,7 +12489,7 @@
         <v/>
       </c>
       <c r="J375" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="376">
@@ -12521,7 +12521,7 @@
         <v/>
       </c>
       <c r="J376" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="377">
@@ -12553,7 +12553,7 @@
         <v/>
       </c>
       <c r="J377" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="378">
@@ -12585,7 +12585,7 @@
         <v/>
       </c>
       <c r="J378" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="379">
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="J379" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="380">
@@ -12649,7 +12649,7 @@
         <v/>
       </c>
       <c r="J380" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="381">
@@ -12660,7 +12660,7 @@
         <v>Fuzzing with database query snippets (371)</v>
       </c>
       <c r="C381" t="str">
-        <v>sql_fuzz_371_8m7g@test.com</v>
+        <v>sql_fuzz_371_riw2@test.com</v>
       </c>
       <c r="D381" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12681,7 +12681,7 @@
         <v/>
       </c>
       <c r="J381" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="382">
@@ -12713,7 +12713,7 @@
         <v/>
       </c>
       <c r="J382" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="383">
@@ -12745,7 +12745,7 @@
         <v/>
       </c>
       <c r="J383" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="384">
@@ -12777,7 +12777,7 @@
         <v/>
       </c>
       <c r="J384" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="385">
@@ -12809,7 +12809,7 @@
         <v/>
       </c>
       <c r="J385" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="386">
@@ -12841,7 +12841,7 @@
         <v/>
       </c>
       <c r="J386" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="387">
@@ -12852,7 +12852,7 @@
         <v>Fuzzing with database query snippets (377)</v>
       </c>
       <c r="C387" t="str">
-        <v>sql_fuzz_377_xwgx@test.com</v>
+        <v>sql_fuzz_377_u5ue@test.com</v>
       </c>
       <c r="D387" t="str">
         <v>'; DROP TABLE u...</v>
@@ -12873,7 +12873,7 @@
         <v/>
       </c>
       <c r="J387" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="388">
@@ -12905,7 +12905,7 @@
         <v/>
       </c>
       <c r="J388" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="389">
@@ -12937,7 +12937,7 @@
         <v/>
       </c>
       <c r="J389" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
     </row>
     <row r="390">
@@ -12969,7 +12969,7 @@
         <v/>
       </c>
       <c r="J390" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="391">
@@ -13001,7 +13001,7 @@
         <v/>
       </c>
       <c r="J391" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="392">
@@ -13033,7 +13033,7 @@
         <v/>
       </c>
       <c r="J392" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="393">
@@ -13044,7 +13044,7 @@
         <v>Fuzzing with database query snippets (383)</v>
       </c>
       <c r="C393" t="str">
-        <v>sql_fuzz_383_s5fh@test.com</v>
+        <v>sql_fuzz_383_zfmi@test.com</v>
       </c>
       <c r="D393" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13065,7 +13065,7 @@
         <v/>
       </c>
       <c r="J393" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="394">
@@ -13097,7 +13097,7 @@
         <v/>
       </c>
       <c r="J394" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="395">
@@ -13129,7 +13129,7 @@
         <v/>
       </c>
       <c r="J395" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="396">
@@ -13161,7 +13161,7 @@
         <v/>
       </c>
       <c r="J396" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="397">
@@ -13193,7 +13193,7 @@
         <v/>
       </c>
       <c r="J397" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="398">
@@ -13225,7 +13225,7 @@
         <v/>
       </c>
       <c r="J398" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="399">
@@ -13236,7 +13236,7 @@
         <v>Fuzzing with database query snippets (389)</v>
       </c>
       <c r="C399" t="str">
-        <v>sql_fuzz_389_4gd1@test.com</v>
+        <v>sql_fuzz_389_zgop@test.com</v>
       </c>
       <c r="D399" t="str">
         <v>'; DROP TABLE u...</v>
@@ -13257,7 +13257,7 @@
         <v/>
       </c>
       <c r="J399" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="400">
@@ -13289,7 +13289,7 @@
         <v/>
       </c>
       <c r="J400" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
     <row r="401">
@@ -13321,7 +13321,7 @@
         <v/>
       </c>
       <c r="J401" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
     </row>
   </sheetData>
